--- a/data/lifes_set_alpha_complex.xlsx
+++ b/data/lifes_set_alpha_complex.xlsx
@@ -6,7 +6,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="lifes_set_alpha_complex" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -2576,10 +2576,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>1.31464288011792</v>
+        <v>1.22746435879107</v>
       </c>
       <c r="C2" t="n">
-        <v>0.966926792152533</v>
+        <v>0.820663549388168</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -2596,10 +2596,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.570046627835983</v>
+        <v>0.535839457157883</v>
       </c>
       <c r="C3" t="n">
-        <v>1.22498949069315</v>
+        <v>0.714697055946145</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2616,10 +2616,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>0.570046627835983</v>
+        <v>0.535839457157883</v>
       </c>
       <c r="C4" t="n">
-        <v>1.22498949069315</v>
+        <v>0.714697055946145</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -2636,10 +2636,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="n">
-        <v>1.53297889000605</v>
+        <v>1.42885578389542</v>
       </c>
       <c r="C5" t="n">
-        <v>0.806959117677372</v>
+        <v>0.904442101072587</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -2656,10 +2656,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="n">
-        <v>1.53297889000605</v>
+        <v>1.42885578389542</v>
       </c>
       <c r="C6" t="n">
-        <v>0.806959117677372</v>
+        <v>0.904442101072587</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -2676,10 +2676,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>1.68886027617353</v>
+        <v>1.56508066305522</v>
       </c>
       <c r="C7" t="n">
-        <v>0.989289799128566</v>
+        <v>0.775066681830786</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -2696,10 +2696,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="n">
-        <v>1.05355556809627</v>
+        <v>0.980853256708434</v>
       </c>
       <c r="C8" t="n">
-        <v>1.19472607372906</v>
+        <v>0.699124118169029</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -2716,10 +2716,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="n">
-        <v>1.01669133446404</v>
+        <v>0.943546576301525</v>
       </c>
       <c r="C9" t="n">
-        <v>1.19779415154058</v>
+        <v>0.687834070678328</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -2736,10 +2736,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="n">
-        <v>0.580288173696609</v>
+        <v>0.540235386562996</v>
       </c>
       <c r="C10" t="n">
-        <v>1.12833602117081</v>
+        <v>0.726482167349337</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -2756,10 +2756,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="n">
-        <v>0.602453308323948</v>
+        <v>0.56021582371032</v>
       </c>
       <c r="C11" t="n">
-        <v>1.18490472725669</v>
+        <v>0.698186022940451</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -2776,10 +2776,10 @@
         <v>32</v>
       </c>
       <c r="B12" t="n">
-        <v>1.44577128137417</v>
+        <v>1.34092436165669</v>
       </c>
       <c r="C12" t="n">
-        <v>0.927077160230237</v>
+        <v>0.809431173347896</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
@@ -2796,10 +2796,10 @@
         <v>33</v>
       </c>
       <c r="B13" t="n">
-        <v>1.24650475151356</v>
+        <v>1.16344231091589</v>
       </c>
       <c r="C13" t="n">
-        <v>1.05919562922779</v>
+        <v>0.770456998817388</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
@@ -2816,10 +2816,10 @@
         <v>36</v>
       </c>
       <c r="B14" t="n">
-        <v>1.36952958145267</v>
+        <v>1.27396285362785</v>
       </c>
       <c r="C14" t="n">
-        <v>1.05342734581082</v>
+        <v>0.759994651269169</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -2836,10 +2836,10 @@
         <v>37</v>
       </c>
       <c r="B15" t="n">
-        <v>1.20161536648615</v>
+        <v>1.12885619977111</v>
       </c>
       <c r="C15" t="n">
-        <v>1.01651770280858</v>
+        <v>0.821371899526395</v>
       </c>
       <c r="D15" t="s">
         <v>38</v>
@@ -2856,10 +2856,10 @@
         <v>37</v>
       </c>
       <c r="B16" t="n">
-        <v>1.20161536648615</v>
+        <v>1.12885619977111</v>
       </c>
       <c r="C16" t="n">
-        <v>1.01651770280858</v>
+        <v>0.821371899526395</v>
       </c>
       <c r="D16" t="s">
         <v>40</v>
@@ -2876,10 +2876,10 @@
         <v>42</v>
       </c>
       <c r="B17" t="n">
-        <v>0.867545669624546</v>
+        <v>0.794674646841484</v>
       </c>
       <c r="C17" t="n">
-        <v>1.44448813823586</v>
+        <v>0.570075654280597</v>
       </c>
       <c r="D17" t="s">
         <v>43</v>
@@ -2896,10 +2896,10 @@
         <v>45</v>
       </c>
       <c r="B18" t="n">
-        <v>1.52624290731098</v>
+        <v>1.40457171547763</v>
       </c>
       <c r="C18" t="n">
-        <v>0.979218592988982</v>
+        <v>0.748777585026487</v>
       </c>
       <c r="D18" t="s">
         <v>46</v>
@@ -2916,10 +2916,10 @@
         <v>48</v>
       </c>
       <c r="B19" t="n">
-        <v>1.5374189871499</v>
+        <v>1.43362818130322</v>
       </c>
       <c r="C19" t="n">
-        <v>0.881292187715891</v>
+        <v>0.858898391246712</v>
       </c>
       <c r="D19" t="s">
         <v>49</v>
@@ -2936,10 +2936,10 @@
         <v>51</v>
       </c>
       <c r="B20" t="n">
-        <v>1.3697538083785</v>
+        <v>1.27777531738562</v>
       </c>
       <c r="C20" t="n">
-        <v>0.923975504102544</v>
+        <v>0.841064495487627</v>
       </c>
       <c r="D20" t="s">
         <v>34</v>
@@ -2956,10 +2956,10 @@
         <v>52</v>
       </c>
       <c r="B21" t="n">
-        <v>0.984704665142799</v>
+        <v>0.910573425408301</v>
       </c>
       <c r="C21" t="n">
-        <v>1.27229374355198</v>
+        <v>0.647896211516558</v>
       </c>
       <c r="D21" t="s">
         <v>43</v>
@@ -2976,10 +2976,10 @@
         <v>53</v>
       </c>
       <c r="B22" t="n">
-        <v>0.10780923980244</v>
+        <v>0.10064143945273</v>
       </c>
       <c r="C22" t="n">
-        <v>2.48748134111069</v>
+        <v>0.381739707280289</v>
       </c>
       <c r="D22" t="s">
         <v>54</v>
@@ -2996,10 +2996,10 @@
         <v>53</v>
       </c>
       <c r="B23" t="n">
-        <v>0.10780923980244</v>
+        <v>0.10064143945273</v>
       </c>
       <c r="C23" t="n">
-        <v>2.48748134111069</v>
+        <v>0.381739707280289</v>
       </c>
       <c r="D23" t="s">
         <v>56</v>
@@ -3016,10 +3016,10 @@
         <v>58</v>
       </c>
       <c r="B24" t="n">
-        <v>1.31988841741104</v>
+        <v>1.22532104183093</v>
       </c>
       <c r="C24" t="n">
-        <v>0.989357643702784</v>
+        <v>0.783822517267758</v>
       </c>
       <c r="D24" t="s">
         <v>59</v>
@@ -3036,10 +3036,10 @@
         <v>61</v>
       </c>
       <c r="B25" t="n">
-        <v>0.877193156872631</v>
+        <v>0.827772330382965</v>
       </c>
       <c r="C25" t="n">
-        <v>0.92199332818451</v>
+        <v>0.898045246475783</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
@@ -3056,10 +3056,10 @@
         <v>62</v>
       </c>
       <c r="B26" t="n">
-        <v>1.19902585853493</v>
+        <v>1.11281078379532</v>
       </c>
       <c r="C26" t="n">
-        <v>1.23712606410116</v>
+        <v>0.6701015539932</v>
       </c>
       <c r="D26" t="s">
         <v>63</v>
@@ -3076,10 +3076,10 @@
         <v>62</v>
       </c>
       <c r="B27" t="n">
-        <v>1.19902585853493</v>
+        <v>1.11281078379532</v>
       </c>
       <c r="C27" t="n">
-        <v>1.23712606410116</v>
+        <v>0.6701015539932</v>
       </c>
       <c r="D27" t="s">
         <v>65</v>
@@ -3096,10 +3096,10 @@
         <v>62</v>
       </c>
       <c r="B28" t="n">
-        <v>1.19902585853493</v>
+        <v>1.11281078379532</v>
       </c>
       <c r="C28" t="n">
-        <v>1.23712606410116</v>
+        <v>0.6701015539932</v>
       </c>
       <c r="D28" t="s">
         <v>67</v>
@@ -3116,10 +3116,10 @@
         <v>69</v>
       </c>
       <c r="B29" t="n">
-        <v>1.35058846640749</v>
+        <v>1.2594356759185</v>
       </c>
       <c r="C29" t="n">
-        <v>1.05349906069638</v>
+        <v>0.768659252237392</v>
       </c>
       <c r="D29" t="s">
         <v>70</v>
@@ -3136,10 +3136,10 @@
         <v>69</v>
       </c>
       <c r="B30" t="n">
-        <v>1.35058846640749</v>
+        <v>1.2594356759185</v>
       </c>
       <c r="C30" t="n">
-        <v>1.05349906069638</v>
+        <v>0.768659252237392</v>
       </c>
       <c r="D30" t="s">
         <v>72</v>
@@ -3156,10 +3156,10 @@
         <v>74</v>
       </c>
       <c r="B31" t="n">
-        <v>1.33768531786047</v>
+        <v>1.25397393221847</v>
       </c>
       <c r="C31" t="n">
-        <v>0.927103489568158</v>
+        <v>0.863034961828438</v>
       </c>
       <c r="D31" t="s">
         <v>75</v>
@@ -3176,10 +3176,10 @@
         <v>77</v>
       </c>
       <c r="B32" t="n">
-        <v>1.04326122381311</v>
+        <v>0.967842194301905</v>
       </c>
       <c r="C32" t="n">
-        <v>1.50332083412557</v>
+        <v>0.578445589354269</v>
       </c>
       <c r="D32" t="s">
         <v>78</v>
@@ -3196,10 +3196,10 @@
         <v>80</v>
       </c>
       <c r="B33" t="n">
-        <v>1.2170202574756</v>
+        <v>1.12119523100589</v>
       </c>
       <c r="C33" t="n">
-        <v>1.10644955520718</v>
+        <v>0.697935559536595</v>
       </c>
       <c r="D33" t="s">
         <v>81</v>
@@ -3216,10 +3216,10 @@
         <v>83</v>
       </c>
       <c r="B34" t="n">
-        <v>1.49323012226286</v>
+        <v>1.39621258562606</v>
       </c>
       <c r="C34" t="n">
-        <v>0.915527237566415</v>
+        <v>0.854454859150993</v>
       </c>
       <c r="D34" t="s">
         <v>84</v>
@@ -3236,10 +3236,10 @@
         <v>86</v>
       </c>
       <c r="B35" t="n">
-        <v>1.23615698189601</v>
+        <v>1.15072046296881</v>
       </c>
       <c r="C35" t="n">
-        <v>1.10506986332941</v>
+        <v>0.738201162282992</v>
       </c>
       <c r="D35" t="s">
         <v>87</v>
@@ -3256,10 +3256,10 @@
         <v>89</v>
       </c>
       <c r="B36" t="n">
-        <v>1.36808725690276</v>
+        <v>1.27412405460696</v>
       </c>
       <c r="C36" t="n">
-        <v>0.955613807858167</v>
+        <v>0.814205940963254</v>
       </c>
       <c r="D36" t="s">
         <v>75</v>
@@ -3276,10 +3276,10 @@
         <v>90</v>
       </c>
       <c r="B37" t="n">
-        <v>1.03811006470628</v>
+        <v>0.972750945921356</v>
       </c>
       <c r="C37" t="n">
-        <v>0.894968602215021</v>
+        <v>0.877459087487792</v>
       </c>
       <c r="D37" t="s">
         <v>91</v>
@@ -3296,10 +3296,10 @@
         <v>93</v>
       </c>
       <c r="B38" t="n">
-        <v>1.16764656577514</v>
+        <v>1.08619765001535</v>
       </c>
       <c r="C38" t="n">
-        <v>1.01822577173608</v>
+        <v>0.773662116267202</v>
       </c>
       <c r="D38" t="s">
         <v>70</v>
@@ -3316,10 +3316,10 @@
         <v>93</v>
       </c>
       <c r="B39" t="n">
-        <v>1.16764656577514</v>
+        <v>1.08619765001535</v>
       </c>
       <c r="C39" t="n">
-        <v>1.01822577173608</v>
+        <v>0.773662116267202</v>
       </c>
       <c r="D39" t="s">
         <v>94</v>
@@ -3336,10 +3336,10 @@
         <v>96</v>
       </c>
       <c r="B40" t="n">
-        <v>1.14007271408563</v>
+        <v>1.08094801286677</v>
       </c>
       <c r="C40" t="n">
-        <v>0.812567232499998</v>
+        <v>1.0128207135597</v>
       </c>
       <c r="D40" t="s">
         <v>97</v>
@@ -3356,10 +3356,10 @@
         <v>96</v>
       </c>
       <c r="B41" t="n">
-        <v>1.14007271408563</v>
+        <v>1.08094801286677</v>
       </c>
       <c r="C41" t="n">
-        <v>0.812567232499998</v>
+        <v>1.0128207135597</v>
       </c>
       <c r="D41" t="s">
         <v>99</v>
@@ -3376,10 +3376,10 @@
         <v>96</v>
       </c>
       <c r="B42" t="n">
-        <v>1.14007271408563</v>
+        <v>1.08094801286677</v>
       </c>
       <c r="C42" t="n">
-        <v>0.812567232499998</v>
+        <v>1.0128207135597</v>
       </c>
       <c r="D42" t="s">
         <v>101</v>
@@ -3396,10 +3396,10 @@
         <v>103</v>
       </c>
       <c r="B43" t="n">
-        <v>1.16154850242073</v>
+        <v>1.09192452690471</v>
       </c>
       <c r="C43" t="n">
-        <v>0.971601621881354</v>
+        <v>0.850325551099107</v>
       </c>
       <c r="D43" t="s">
         <v>104</v>
@@ -3416,10 +3416,10 @@
         <v>106</v>
       </c>
       <c r="B44" t="n">
-        <v>1.09603269590137</v>
+        <v>1.02079068764739</v>
       </c>
       <c r="C44" t="n">
-        <v>0.96987397356292</v>
+        <v>0.806345056105908</v>
       </c>
       <c r="D44" t="s">
         <v>107</v>
@@ -3436,10 +3436,10 @@
         <v>109</v>
       </c>
       <c r="B45" t="n">
-        <v>0.926375363491906</v>
+        <v>0.875257684590578</v>
       </c>
       <c r="C45" t="n">
-        <v>1.07363554162092</v>
+        <v>0.811883233436013</v>
       </c>
       <c r="D45" t="s">
         <v>110</v>
@@ -3456,10 +3456,10 @@
         <v>112</v>
       </c>
       <c r="B46" t="n">
-        <v>1.17379765576742</v>
+        <v>1.10185111351294</v>
       </c>
       <c r="C46" t="n">
-        <v>0.975750990516445</v>
+        <v>0.839075571607877</v>
       </c>
       <c r="D46" t="s">
         <v>72</v>
@@ -3476,10 +3476,10 @@
         <v>112</v>
       </c>
       <c r="B47" t="n">
-        <v>1.17379765576742</v>
+        <v>1.10185111351294</v>
       </c>
       <c r="C47" t="n">
-        <v>0.975750990516445</v>
+        <v>0.839075571607877</v>
       </c>
       <c r="D47" t="s">
         <v>113</v>
@@ -3496,10 +3496,10 @@
         <v>115</v>
       </c>
       <c r="B48" t="n">
-        <v>1.21192380839196</v>
+        <v>1.14776157657598</v>
       </c>
       <c r="C48" t="n">
-        <v>0.982428740347646</v>
+        <v>0.881869874901747</v>
       </c>
       <c r="D48" t="s">
         <v>63</v>
@@ -3516,10 +3516,10 @@
         <v>116</v>
       </c>
       <c r="B49" t="n">
-        <v>1.14808312108218</v>
+        <v>1.0488331220302</v>
       </c>
       <c r="C49" t="n">
-        <v>1.43237659788901</v>
+        <v>0.56844123277775</v>
       </c>
       <c r="D49" t="s">
         <v>117</v>
@@ -3536,10 +3536,10 @@
         <v>119</v>
       </c>
       <c r="B50" t="n">
-        <v>1.21033300925603</v>
+        <v>1.12843336707439</v>
       </c>
       <c r="C50" t="n">
-        <v>1.03645090871675</v>
+        <v>0.776833979053902</v>
       </c>
       <c r="D50" t="s">
         <v>120</v>
@@ -3556,10 +3556,10 @@
         <v>119</v>
       </c>
       <c r="B51" t="n">
-        <v>1.21033300925603</v>
+        <v>1.12843336707439</v>
       </c>
       <c r="C51" t="n">
-        <v>1.03645090871675</v>
+        <v>0.776833979053902</v>
       </c>
       <c r="D51" t="s">
         <v>122</v>
@@ -3576,10 +3576,10 @@
         <v>119</v>
       </c>
       <c r="B52" t="n">
-        <v>1.21033300925603</v>
+        <v>1.12843336707439</v>
       </c>
       <c r="C52" t="n">
-        <v>1.03645090871675</v>
+        <v>0.776833979053902</v>
       </c>
       <c r="D52" t="s">
         <v>124</v>
@@ -3596,10 +3596,10 @@
         <v>126</v>
       </c>
       <c r="B53" t="n">
-        <v>1.39619137497092</v>
+        <v>1.29618313595857</v>
       </c>
       <c r="C53" t="n">
-        <v>0.989819327860753</v>
+        <v>0.780172497804118</v>
       </c>
       <c r="D53" t="s">
         <v>127</v>
@@ -3616,10 +3616,10 @@
         <v>126</v>
       </c>
       <c r="B54" t="n">
-        <v>1.39619137497092</v>
+        <v>1.29618313595857</v>
       </c>
       <c r="C54" t="n">
-        <v>0.989819327860753</v>
+        <v>0.780172497804118</v>
       </c>
       <c r="D54" t="s">
         <v>129</v>
@@ -3636,10 +3636,10 @@
         <v>126</v>
       </c>
       <c r="B55" t="n">
-        <v>1.39619137497092</v>
+        <v>1.29618313595857</v>
       </c>
       <c r="C55" t="n">
-        <v>0.989819327860753</v>
+        <v>0.780172497804118</v>
       </c>
       <c r="D55" t="s">
         <v>131</v>
@@ -3656,10 +3656,10 @@
         <v>133</v>
       </c>
       <c r="B56" t="n">
-        <v>1.24824705532911</v>
+        <v>1.17381886642257</v>
       </c>
       <c r="C56" t="n">
-        <v>0.888641379884452</v>
+        <v>0.903972046066545</v>
       </c>
       <c r="D56" t="s">
         <v>20</v>
@@ -3676,10 +3676,10 @@
         <v>134</v>
       </c>
       <c r="B57" t="n">
-        <v>1.02659570905571</v>
+        <v>0.942707567954156</v>
       </c>
       <c r="C57" t="n">
-        <v>1.19472318613354</v>
+        <v>0.654638725845482</v>
       </c>
       <c r="D57" t="s">
         <v>135</v>
@@ -3696,10 +3696,10 @@
         <v>137</v>
       </c>
       <c r="B58" t="n">
-        <v>1.22364269536</v>
+        <v>1.14403910659789</v>
       </c>
       <c r="C58" t="n">
-        <v>0.955965332726508</v>
+        <v>0.831646615348979</v>
       </c>
       <c r="D58" t="s">
         <v>138</v>
@@ -3716,10 +3716,10 @@
         <v>140</v>
       </c>
       <c r="B59" t="n">
-        <v>1.56025579252352</v>
+        <v>1.45157239555654</v>
       </c>
       <c r="C59" t="n">
-        <v>0.907850867365421</v>
+        <v>0.831813658801912</v>
       </c>
       <c r="D59" t="s">
         <v>141</v>
@@ -3736,10 +3736,10 @@
         <v>143</v>
       </c>
       <c r="B60" t="n">
-        <v>0.973569071191265</v>
+        <v>0.919640980483121</v>
       </c>
       <c r="C60" t="n">
-        <v>1.11836356117046</v>
+        <v>0.787329414155017</v>
       </c>
       <c r="D60" t="s">
         <v>12</v>
@@ -3756,10 +3756,10 @@
         <v>144</v>
       </c>
       <c r="B61" t="n">
-        <v>1.17549450817908</v>
+        <v>1.09459706945308</v>
       </c>
       <c r="C61" t="n">
-        <v>1.18956008901328</v>
+        <v>0.699925641761686</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -3776,10 +3776,10 @@
         <v>147</v>
       </c>
       <c r="B62" t="n">
-        <v>0.598682023752993</v>
+        <v>0.535228871546511</v>
       </c>
       <c r="C62" t="n">
-        <v>3.43946434214206</v>
+        <v>0.264012867376024</v>
       </c>
       <c r="D62" t="s">
         <v>148</v>
@@ -3796,10 +3796,10 @@
         <v>150</v>
       </c>
       <c r="B63" t="n">
-        <v>0.210236664754151</v>
+        <v>0.192929107041963</v>
       </c>
       <c r="C63" t="n">
-        <v>2.97160197627848</v>
+        <v>0.312603381016393</v>
       </c>
       <c r="D63" t="s">
         <v>151</v>
@@ -3816,10 +3816,10 @@
         <v>150</v>
       </c>
       <c r="B64" t="n">
-        <v>0.210236664754151</v>
+        <v>0.192929107041963</v>
       </c>
       <c r="C64" t="n">
-        <v>2.97160197627848</v>
+        <v>0.312603381016393</v>
       </c>
       <c r="D64" t="s">
         <v>153</v>
@@ -3836,10 +3836,10 @@
         <v>155</v>
       </c>
       <c r="B65" t="n">
-        <v>1.34687660175698</v>
+        <v>1.28568386166141</v>
       </c>
       <c r="C65" t="n">
-        <v>0.683365925106035</v>
+        <v>1.18480967898827</v>
       </c>
       <c r="D65" t="s">
         <v>156</v>
@@ -3856,10 +3856,10 @@
         <v>158</v>
       </c>
       <c r="B66" t="n">
-        <v>1.14113324684292</v>
+        <v>1.07283493727351</v>
       </c>
       <c r="C66" t="n">
-        <v>0.883853301121357</v>
+        <v>0.904683370302212</v>
       </c>
       <c r="D66" t="s">
         <v>117</v>
@@ -3876,10 +3876,10 @@
         <v>159</v>
       </c>
       <c r="B67" t="n">
-        <v>1.1137522192911</v>
+        <v>1.04437409455063</v>
       </c>
       <c r="C67" t="n">
-        <v>1.23236720914069</v>
+        <v>0.70474196069524</v>
       </c>
       <c r="D67" t="s">
         <v>160</v>
@@ -3896,10 +3896,10 @@
         <v>162</v>
       </c>
       <c r="B68" t="n">
-        <v>1.04356423317234</v>
+        <v>0.989317982637006</v>
       </c>
       <c r="C68" t="n">
-        <v>0.95063801263732</v>
+        <v>0.907221387344872</v>
       </c>
       <c r="D68" t="s">
         <v>163</v>
@@ -3916,10 +3916,10 @@
         <v>165</v>
       </c>
       <c r="B69" t="n">
-        <v>1.20617925595664</v>
+        <v>1.13837586167397</v>
       </c>
       <c r="C69" t="n">
-        <v>0.930984455466267</v>
+        <v>0.894228732805373</v>
       </c>
       <c r="D69" t="s">
         <v>94</v>
@@ -3936,10 +3936,10 @@
         <v>165</v>
       </c>
       <c r="B70" t="n">
-        <v>1.20617925595664</v>
+        <v>1.13837586167397</v>
       </c>
       <c r="C70" t="n">
-        <v>0.930984455466267</v>
+        <v>0.894228732805373</v>
       </c>
       <c r="D70" t="s">
         <v>113</v>
@@ -3956,10 +3956,10 @@
         <v>166</v>
       </c>
       <c r="B71" t="n">
-        <v>0.91569428357921</v>
+        <v>0.850850280704971</v>
       </c>
       <c r="C71" t="n">
-        <v>1.10282898226255</v>
+        <v>0.73151819340975</v>
       </c>
       <c r="D71" t="s">
         <v>23</v>
@@ -3976,10 +3976,10 @@
         <v>167</v>
       </c>
       <c r="B72" t="n">
-        <v>0.979932267734999</v>
+        <v>0.931571974002622</v>
       </c>
       <c r="C72" t="n">
-        <v>0.794161978923119</v>
+        <v>1.05111778894385</v>
       </c>
       <c r="D72" t="s">
         <v>168</v>
@@ -3996,10 +3996,10 @@
         <v>170</v>
       </c>
       <c r="B73" t="n">
-        <v>1.18072646978171</v>
+        <v>1.11419571480778</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9731161512016</v>
+        <v>0.869918344624026</v>
       </c>
       <c r="D73" t="s">
         <v>171</v>
@@ -4016,10 +4016,10 @@
         <v>173</v>
       </c>
       <c r="B74" t="n">
-        <v>1.23658119499893</v>
+        <v>1.17019184439264</v>
       </c>
       <c r="C74" t="n">
-        <v>0.993580267218514</v>
+        <v>0.868112339150522</v>
       </c>
       <c r="D74" t="s">
         <v>174</v>
@@ -4036,10 +4036,10 @@
         <v>176</v>
       </c>
       <c r="B75" t="n">
-        <v>1.06477488831812</v>
+        <v>0.990272462118566</v>
       </c>
       <c r="C75" t="n">
-        <v>0.921124723496436</v>
+        <v>0.82645917058894</v>
       </c>
       <c r="D75" t="s">
         <v>141</v>
@@ -4056,10 +4056,10 @@
         <v>176</v>
       </c>
       <c r="B76" t="n">
-        <v>1.06477488831812</v>
+        <v>0.990272462118566</v>
       </c>
       <c r="C76" t="n">
-        <v>0.921124723496436</v>
+        <v>0.82645917058894</v>
       </c>
       <c r="D76" t="s">
         <v>87</v>
@@ -4076,10 +4076,10 @@
         <v>176</v>
       </c>
       <c r="B77" t="n">
-        <v>1.06477488831812</v>
+        <v>0.990272462118566</v>
       </c>
       <c r="C77" t="n">
-        <v>0.921124723496436</v>
+        <v>0.82645917058894</v>
       </c>
       <c r="D77" t="s">
         <v>104</v>
@@ -4096,10 +4096,10 @@
         <v>177</v>
       </c>
       <c r="B78" t="n">
-        <v>0.200228584576156</v>
+        <v>0.18402364404478</v>
       </c>
       <c r="C78" t="n">
-        <v>2.42291469050863</v>
+        <v>0.37701559998376</v>
       </c>
       <c r="D78" t="s">
         <v>178</v>
@@ -4116,10 +4116,10 @@
         <v>180</v>
       </c>
       <c r="B79" t="n">
-        <v>1.10592355930093</v>
+        <v>1.02472917140288</v>
       </c>
       <c r="C79" t="n">
-        <v>1.16013433277573</v>
+        <v>0.696797146101876</v>
       </c>
       <c r="D79" t="s">
         <v>181</v>
@@ -4136,10 +4136,10 @@
         <v>180</v>
       </c>
       <c r="B80" t="n">
-        <v>1.10592355930093</v>
+        <v>1.02472917140288</v>
       </c>
       <c r="C80" t="n">
-        <v>1.16013433277573</v>
+        <v>0.696797146101876</v>
       </c>
       <c r="D80" t="s">
         <v>20</v>
@@ -4156,10 +4156,10 @@
         <v>183</v>
       </c>
       <c r="B81" t="n">
-        <v>1.16419983431396</v>
+        <v>1.09240176664549</v>
       </c>
       <c r="C81" t="n">
-        <v>1.07141747542551</v>
+        <v>0.786056374265192</v>
       </c>
       <c r="D81" t="s">
         <v>78</v>
@@ -4176,10 +4176,10 @@
         <v>184</v>
       </c>
       <c r="B82" t="n">
-        <v>1.29597102940711</v>
+        <v>1.2188702979522</v>
       </c>
       <c r="C82" t="n">
-        <v>1.10413938677757</v>
+        <v>0.777134498142927</v>
       </c>
       <c r="D82" t="s">
         <v>185</v>
@@ -4196,10 +4196,10 @@
         <v>187</v>
       </c>
       <c r="B83" t="n">
-        <v>0.967205874647531</v>
+        <v>0.890529356295539</v>
       </c>
       <c r="C83" t="n">
-        <v>1.34835707352586</v>
+        <v>0.609605756097918</v>
       </c>
       <c r="D83" t="s">
         <v>38</v>
@@ -4216,10 +4216,10 @@
         <v>187</v>
       </c>
       <c r="B84" t="n">
-        <v>0.967205874647531</v>
+        <v>0.890529356295539</v>
       </c>
       <c r="C84" t="n">
-        <v>1.34835707352586</v>
+        <v>0.609605756097918</v>
       </c>
       <c r="D84" t="s">
         <v>40</v>
@@ -4236,10 +4236,10 @@
         <v>188</v>
       </c>
       <c r="B85" t="n">
-        <v>0.682116744990953</v>
+        <v>0.623190527327444</v>
       </c>
       <c r="C85" t="n">
-        <v>2.15917509612021</v>
+        <v>0.411247885561441</v>
       </c>
       <c r="D85" t="s">
         <v>189</v>
@@ -4256,10 +4256,10 @@
         <v>191</v>
       </c>
       <c r="B86" t="n">
-        <v>1.21112840882399</v>
+        <v>1.13583058305648</v>
       </c>
       <c r="C86" t="n">
-        <v>0.915793964809916</v>
+        <v>0.873377936463129</v>
       </c>
       <c r="D86" t="s">
         <v>192</v>
@@ -4276,10 +4276,10 @@
         <v>191</v>
       </c>
       <c r="B87" t="n">
-        <v>1.21112840882399</v>
+        <v>1.13583058305648</v>
       </c>
       <c r="C87" t="n">
-        <v>0.915793964809916</v>
+        <v>0.873377936463129</v>
       </c>
       <c r="D87" t="s">
         <v>194</v>
@@ -4296,10 +4296,10 @@
         <v>191</v>
       </c>
       <c r="B88" t="n">
-        <v>1.21112840882399</v>
+        <v>1.13583058305648</v>
       </c>
       <c r="C88" t="n">
-        <v>0.915793964809916</v>
+        <v>0.873377936463129</v>
       </c>
       <c r="D88" t="s">
         <v>196</v>
@@ -4316,10 +4316,10 @@
         <v>198</v>
       </c>
       <c r="B89" t="n">
-        <v>1.20370467952297</v>
+        <v>1.13487610357492</v>
       </c>
       <c r="C89" t="n">
-        <v>0.755300945063687</v>
+        <v>1.00610052347659</v>
       </c>
       <c r="D89" t="s">
         <v>199</v>
@@ -4336,10 +4336,10 @@
         <v>201</v>
       </c>
       <c r="B90" t="n">
-        <v>1.3447555362424</v>
+        <v>1.24845916188056</v>
       </c>
       <c r="C90" t="n">
-        <v>0.790211315020392</v>
+        <v>0.884288415964999</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -4356,10 +4356,10 @@
         <v>201</v>
       </c>
       <c r="B91" t="n">
-        <v>1.3447555362424</v>
+        <v>1.24845916188056</v>
       </c>
       <c r="C91" t="n">
-        <v>0.790211315020392</v>
+        <v>0.884288415964999</v>
       </c>
       <c r="D91" t="s">
         <v>202</v>
@@ -4376,10 +4376,10 @@
         <v>204</v>
       </c>
       <c r="B92" t="n">
-        <v>1.16658603301786</v>
+        <v>1.08906108846003</v>
       </c>
       <c r="C92" t="n">
-        <v>0.989202331996299</v>
+        <v>0.805774369358815</v>
       </c>
       <c r="D92" t="s">
         <v>107</v>
@@ -4396,10 +4396,10 @@
         <v>205</v>
       </c>
       <c r="B93" t="n">
-        <v>1.37179912155327</v>
+        <v>1.29570589621779</v>
       </c>
       <c r="C93" t="n">
-        <v>0.771174997793954</v>
+        <v>1.01351663760077</v>
       </c>
       <c r="D93" t="s">
         <v>38</v>
@@ -4416,10 +4416,10 @@
         <v>206</v>
       </c>
       <c r="B94" t="n">
-        <v>1.49959331880659</v>
+        <v>1.42599234545074</v>
       </c>
       <c r="C94" t="n">
-        <v>1.06225012374038</v>
+        <v>0.844623746276879</v>
       </c>
       <c r="D94" t="s">
         <v>207</v>
@@ -4436,10 +4436,10 @@
         <v>209</v>
       </c>
       <c r="B95" t="n">
-        <v>1.39050994948544</v>
+        <v>1.29481959384205</v>
       </c>
       <c r="C95" t="n">
-        <v>0.953212486183531</v>
+        <v>0.813401221308545</v>
       </c>
       <c r="D95" t="s">
         <v>129</v>
@@ -4456,10 +4456,10 @@
         <v>209</v>
       </c>
       <c r="B96" t="n">
-        <v>1.39050994948544</v>
+        <v>1.29481959384205</v>
       </c>
       <c r="C96" t="n">
-        <v>0.953212486183531</v>
+        <v>0.813401221308545</v>
       </c>
       <c r="D96" t="s">
         <v>120</v>
@@ -4476,10 +4476,10 @@
         <v>210</v>
       </c>
       <c r="B97" t="n">
-        <v>0.983909265574832</v>
+        <v>0.916538922168051</v>
       </c>
       <c r="C97" t="n">
-        <v>0.953173922771026</v>
+        <v>0.813828389870516</v>
       </c>
       <c r="D97" t="s">
         <v>211</v>
@@ -4496,10 +4496,10 @@
         <v>213</v>
       </c>
       <c r="B98" t="n">
-        <v>1.27900250529049</v>
+        <v>1.18482719644323</v>
       </c>
       <c r="C98" t="n">
-        <v>1.42589795428838</v>
+        <v>0.599993506910903</v>
       </c>
       <c r="D98" t="s">
         <v>214</v>
@@ -4516,10 +4516,10 @@
         <v>216</v>
       </c>
       <c r="B99" t="n">
-        <v>1.15103155257762</v>
+        <v>1.07156229796476</v>
       </c>
       <c r="C99" t="n">
-        <v>0.822925514027894</v>
+        <v>0.886937181795123</v>
       </c>
       <c r="D99" t="s">
         <v>217</v>
@@ -4536,10 +4536,10 @@
         <v>219</v>
       </c>
       <c r="B100" t="n">
-        <v>0.971751015035912</v>
+        <v>0.911118842254906</v>
       </c>
       <c r="C100" t="n">
-        <v>0.984358867980636</v>
+        <v>0.829026517390012</v>
       </c>
       <c r="D100" t="s">
         <v>220</v>
@@ -4556,10 +4556,10 @@
         <v>222</v>
       </c>
       <c r="B101" t="n">
-        <v>1.51868290843779</v>
+        <v>1.42981026337698</v>
       </c>
       <c r="C101" t="n">
-        <v>0.682894280869647</v>
+        <v>1.06615533474522</v>
       </c>
       <c r="D101" t="s">
         <v>223</v>
@@ -4576,10 +4576,10 @@
         <v>225</v>
       </c>
       <c r="B102" t="n">
-        <v>0.412193731666309</v>
+        <v>0.386246030204639</v>
       </c>
       <c r="C102" t="n">
-        <v>1.34242336095369</v>
+        <v>0.657611656220838</v>
       </c>
       <c r="D102" t="s">
         <v>226</v>
@@ -4596,10 +4596,10 @@
         <v>228</v>
       </c>
       <c r="B103" t="n">
-        <v>1.36172406035902</v>
+        <v>1.26754875151176</v>
       </c>
       <c r="C103" t="n">
-        <v>0.998386643674996</v>
+        <v>0.787022657233727</v>
       </c>
       <c r="D103" t="s">
         <v>229</v>
@@ -4616,10 +4616,10 @@
         <v>231</v>
       </c>
       <c r="B104" t="n">
-        <v>1.25567078463013</v>
+        <v>1.18482719644323</v>
       </c>
       <c r="C104" t="n">
-        <v>0.853754796873538</v>
+        <v>0.94226390698819</v>
       </c>
       <c r="D104" t="s">
         <v>232</v>
@@ -4636,10 +4636,10 @@
         <v>231</v>
       </c>
       <c r="B105" t="n">
-        <v>1.25567078463013</v>
+        <v>1.18482719644323</v>
       </c>
       <c r="C105" t="n">
-        <v>0.853754796873538</v>
+        <v>0.94226390698819</v>
       </c>
       <c r="D105" t="s">
         <v>234</v>
@@ -4656,10 +4656,10 @@
         <v>236</v>
       </c>
       <c r="B106" t="n">
-        <v>0.312503652481147</v>
+        <v>0.288252803431139</v>
       </c>
       <c r="C106" t="n">
-        <v>2.00350852424522</v>
+        <v>0.448814684585524</v>
       </c>
       <c r="D106" t="s">
         <v>237</v>
@@ -4676,10 +4676,10 @@
         <v>236</v>
       </c>
       <c r="B107" t="n">
-        <v>0.312503652481147</v>
+        <v>0.288252803431139</v>
       </c>
       <c r="C107" t="n">
-        <v>2.00350852424522</v>
+        <v>0.448814684585524</v>
       </c>
       <c r="D107" t="s">
         <v>239</v>
@@ -4696,10 +4696,10 @@
         <v>241</v>
       </c>
       <c r="B108" t="n">
-        <v>1.12521333938519</v>
+        <v>1.05860451591207</v>
       </c>
       <c r="C108" t="n">
-        <v>1.04910222976315</v>
+        <v>0.80944343096333</v>
       </c>
       <c r="D108" t="s">
         <v>242</v>
@@ -4716,10 +4716,10 @@
         <v>244</v>
       </c>
       <c r="B109" t="n">
-        <v>0.926905629870551</v>
+        <v>0.845986980489403</v>
       </c>
       <c r="C109" t="n">
-        <v>1.6947297595972</v>
+        <v>0.498159323539115</v>
       </c>
       <c r="D109" t="s">
         <v>245</v>
@@ -4736,10 +4736,10 @@
         <v>244</v>
       </c>
       <c r="B110" t="n">
-        <v>0.926905629870551</v>
+        <v>0.845986980489403</v>
       </c>
       <c r="C110" t="n">
-        <v>1.6947297595972</v>
+        <v>0.498159323539115</v>
       </c>
       <c r="D110" t="s">
         <v>247</v>
@@ -4756,10 +4756,10 @@
         <v>249</v>
       </c>
       <c r="B111" t="n">
-        <v>1.40573616978652</v>
+        <v>1.31145480766353</v>
       </c>
       <c r="C111" t="n">
-        <v>0.842062814419399</v>
+        <v>0.884562113114552</v>
       </c>
       <c r="D111" t="s">
         <v>250</v>
@@ -4776,10 +4776,10 @@
         <v>252</v>
       </c>
       <c r="B112" t="n">
-        <v>1.0089201631009</v>
+        <v>0.95384316190569</v>
       </c>
       <c r="C112" t="n">
-        <v>0.729441030168519</v>
+        <v>1.05204728514012</v>
       </c>
       <c r="D112" t="s">
         <v>253</v>
@@ -4796,10 +4796,10 @@
         <v>255</v>
       </c>
       <c r="B113" t="n">
-        <v>1.09659087103678</v>
+        <v>1.05183638867919</v>
       </c>
       <c r="C113" t="n">
-        <v>0.544012574587583</v>
+        <v>1.43507585892575</v>
       </c>
       <c r="D113" t="s">
         <v>153</v>
@@ -4816,10 +4816,10 @@
         <v>256</v>
       </c>
       <c r="B114" t="n">
-        <v>1.52875796963204</v>
+        <v>1.41453859167201</v>
       </c>
       <c r="C114" t="n">
-        <v>0.971062617573851</v>
+        <v>0.776673313169241</v>
       </c>
       <c r="D114" t="s">
         <v>20</v>
@@ -4836,10 +4836,10 @@
         <v>257</v>
       </c>
       <c r="B115" t="n">
-        <v>0.267254254836818</v>
+        <v>0.25035527385182</v>
       </c>
       <c r="C115" t="n">
-        <v>1.08554141773117</v>
+        <v>0.793298367646948</v>
       </c>
       <c r="D115" t="s">
         <v>20</v>
@@ -4856,10 +4856,10 @@
         <v>258</v>
       </c>
       <c r="B116" t="n">
-        <v>1.05523009350251</v>
+        <v>1.00506689408275</v>
       </c>
       <c r="C116" t="n">
-        <v>1.20922040777214</v>
+        <v>0.764641179758885</v>
       </c>
       <c r="D116" t="s">
         <v>38</v>
@@ -4876,10 +4876,10 @@
         <v>258</v>
       </c>
       <c r="B117" t="n">
-        <v>1.05523009350251</v>
+        <v>1.00506689408275</v>
       </c>
       <c r="C117" t="n">
-        <v>1.20922040777214</v>
+        <v>0.764641179758885</v>
       </c>
       <c r="D117" t="s">
         <v>259</v>
@@ -4896,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="B118" t="n">
-        <v>1.35323979830071</v>
+        <v>1.26373083358552</v>
       </c>
       <c r="C118" t="n">
-        <v>0.593892099714939</v>
+        <v>1.05775789075026</v>
       </c>
       <c r="D118" t="s">
         <v>262</v>
@@ -4916,10 +4916,10 @@
         <v>264</v>
       </c>
       <c r="B119" t="n">
-        <v>1.16446496750328</v>
+        <v>1.10210564137469</v>
       </c>
       <c r="C119" t="n">
-        <v>0.980925469872054</v>
+        <v>0.877626982851184</v>
       </c>
       <c r="D119" t="s">
         <v>192</v>
@@ -4936,10 +4936,10 @@
         <v>265</v>
       </c>
       <c r="B120" t="n">
-        <v>1.41899282925263</v>
+        <v>1.32672647936849</v>
       </c>
       <c r="C120" t="n">
-        <v>1.08485762873017</v>
+        <v>0.761365125026382</v>
       </c>
       <c r="D120" t="s">
         <v>266</v>
@@ -4956,10 +4956,10 @@
         <v>268</v>
       </c>
       <c r="B121" t="n">
-        <v>0.454615041957867</v>
+        <v>0.418698332577681</v>
       </c>
       <c r="C121" t="n">
-        <v>1.50529262358599</v>
+        <v>0.562775665021918</v>
       </c>
       <c r="D121" t="s">
         <v>269</v>
@@ -4976,10 +4976,10 @@
         <v>271</v>
       </c>
       <c r="B122" t="n">
-        <v>1.17507029507617</v>
+        <v>1.11292307549903</v>
       </c>
       <c r="C122" t="n">
-        <v>0.911958519527035</v>
+        <v>0.927433008452195</v>
       </c>
       <c r="D122" t="s">
         <v>194</v>
@@ -4996,10 +4996,10 @@
         <v>272</v>
       </c>
       <c r="B123" t="n">
-        <v>1.19840201573652</v>
+        <v>1.11101411653591</v>
       </c>
       <c r="C123" t="n">
-        <v>0.879604971713196</v>
+        <v>0.822805707566389</v>
       </c>
       <c r="D123" t="s">
         <v>273</v>
@@ -5016,10 +5016,10 @@
         <v>275</v>
       </c>
       <c r="B124" t="n">
-        <v>0.891908048880015</v>
+        <v>0.824193032327115</v>
       </c>
       <c r="C124" t="n">
-        <v>1.15980566997123</v>
+        <v>0.685950414858539</v>
       </c>
       <c r="D124" t="s">
         <v>276</v>
@@ -5036,10 +5036,10 @@
         <v>278</v>
       </c>
       <c r="B125" t="n">
-        <v>1.15456666176858</v>
+        <v>1.07601653554538</v>
       </c>
       <c r="C125" t="n">
-        <v>1.01171845451754</v>
+        <v>0.78580913568638</v>
       </c>
       <c r="D125" t="s">
         <v>279</v>
@@ -5056,10 +5056,10 @@
         <v>278</v>
       </c>
       <c r="B126" t="n">
-        <v>1.15456666176858</v>
+        <v>1.07601653554538</v>
       </c>
       <c r="C126" t="n">
-        <v>1.01171845451754</v>
+        <v>0.78580913568638</v>
       </c>
       <c r="D126" t="s">
         <v>281</v>
@@ -5076,10 +5076,10 @@
         <v>283</v>
       </c>
       <c r="B127" t="n">
-        <v>1.21918845777939</v>
+        <v>1.1457571696647</v>
       </c>
       <c r="C127" t="n">
-        <v>0.953239245993209</v>
+        <v>0.85605752397091</v>
       </c>
       <c r="D127" t="s">
         <v>284</v>
@@ -5096,10 +5096,10 @@
         <v>286</v>
       </c>
       <c r="B128" t="n">
-        <v>1.10083300206594</v>
+        <v>1.02892888112175</v>
       </c>
       <c r="C128" t="n">
-        <v>0.858444452376381</v>
+        <v>0.886280143921114</v>
       </c>
       <c r="D128" t="s">
         <v>287</v>
@@ -5116,10 +5116,10 @@
         <v>289</v>
       </c>
       <c r="B129" t="n">
-        <v>1.10825673136696</v>
+        <v>1.04849571049373</v>
       </c>
       <c r="C129" t="n">
-        <v>1.02776415515904</v>
+        <v>0.846652068524507</v>
       </c>
       <c r="D129" t="s">
         <v>75</v>
@@ -5136,10 +5136,10 @@
         <v>290</v>
       </c>
       <c r="B130" t="n">
-        <v>0.924784564355973</v>
+        <v>0.854259135996257</v>
       </c>
       <c r="C130" t="n">
-        <v>1.43503381644711</v>
+        <v>0.589213035262332</v>
       </c>
       <c r="D130" t="s">
         <v>291</v>
@@ -5156,10 +5156,10 @@
         <v>293</v>
       </c>
       <c r="B131" t="n">
-        <v>1.45505094300045</v>
+        <v>1.33818023314721</v>
       </c>
       <c r="C131" t="n">
-        <v>0.919165303437433</v>
+        <v>0.766296404622555</v>
       </c>
       <c r="D131" t="s">
         <v>294</v>
@@ -5176,10 +5176,10 @@
         <v>296</v>
       </c>
       <c r="B132" t="n">
-        <v>0.193016961826591</v>
+        <v>0.179442142533292</v>
       </c>
       <c r="C132" t="n">
-        <v>1.70390815090604</v>
+        <v>0.525265664770607</v>
       </c>
       <c r="D132" t="s">
         <v>297</v>
@@ -5196,10 +5196,10 @@
         <v>296</v>
       </c>
       <c r="B133" t="n">
-        <v>0.193016961826591</v>
+        <v>0.179442142533292</v>
       </c>
       <c r="C133" t="n">
-        <v>1.70390815090604</v>
+        <v>0.525265664770607</v>
       </c>
       <c r="D133" t="s">
         <v>299</v>
@@ -5216,10 +5216,10 @@
         <v>301</v>
       </c>
       <c r="B134" t="n">
-        <v>1.30233422595084</v>
+        <v>1.21600685950752</v>
       </c>
       <c r="C134" t="n">
-        <v>0.839373759665121</v>
+        <v>0.883945578187622</v>
       </c>
       <c r="D134" t="s">
         <v>302</v>
@@ -5236,10 +5236,10 @@
         <v>304</v>
       </c>
       <c r="B135" t="n">
-        <v>1.03507997111402</v>
+        <v>0.969751153265025</v>
       </c>
       <c r="C135" t="n">
-        <v>1.12508779413864</v>
+        <v>0.753140803835784</v>
       </c>
       <c r="D135" t="s">
         <v>305</v>
@@ -5256,10 +5256,10 @@
         <v>304</v>
       </c>
       <c r="B136" t="n">
-        <v>1.03507997111402</v>
+        <v>0.969751153265025</v>
       </c>
       <c r="C136" t="n">
-        <v>1.12508779413864</v>
+        <v>0.753140803835784</v>
       </c>
       <c r="D136" t="s">
         <v>307</v>
@@ -5276,10 +5276,10 @@
         <v>309</v>
       </c>
       <c r="B137" t="n">
-        <v>1.07255212853823</v>
+        <v>0.984386505315612</v>
       </c>
       <c r="C137" t="n">
-        <v>1.01215501988861</v>
+        <v>0.722452118851987</v>
       </c>
       <c r="D137" t="s">
         <v>310</v>
@@ -5296,10 +5296,10 @@
         <v>312</v>
       </c>
       <c r="B138" t="n">
-        <v>0.732474624367575</v>
+        <v>0.690406824995113</v>
       </c>
       <c r="C138" t="n">
-        <v>0.760493834001201</v>
+        <v>1.00256399594042</v>
       </c>
       <c r="D138" t="s">
         <v>313</v>
@@ -5316,10 +5316,10 @@
         <v>315</v>
       </c>
       <c r="B139" t="n">
-        <v>1.728668394381</v>
+        <v>1.59493521368687</v>
       </c>
       <c r="C139" t="n">
-        <v>1.07363587211362</v>
+        <v>0.715086627157835</v>
       </c>
       <c r="D139" t="s">
         <v>131</v>
@@ -5336,10 +5336,10 @@
         <v>315</v>
       </c>
       <c r="B140" t="n">
-        <v>1.728668394381</v>
+        <v>1.59493521368687</v>
       </c>
       <c r="C140" t="n">
-        <v>1.07363587211362</v>
+        <v>0.715086627157835</v>
       </c>
       <c r="D140" t="s">
         <v>124</v>
@@ -5356,10 +5356,10 @@
         <v>316</v>
       </c>
       <c r="B141" t="n">
-        <v>0.960312411725153</v>
+        <v>0.889097637073199</v>
       </c>
       <c r="C141" t="n">
-        <v>1.03176497274869</v>
+        <v>0.748293120813006</v>
       </c>
       <c r="D141" t="s">
         <v>63</v>
@@ -5376,10 +5376,10 @@
         <v>316</v>
       </c>
       <c r="B142" t="n">
-        <v>0.960312411725153</v>
+        <v>0.889097637073199</v>
       </c>
       <c r="C142" t="n">
-        <v>1.03176497274869</v>
+        <v>0.748293120813006</v>
       </c>
       <c r="D142" t="s">
         <v>65</v>
@@ -5396,10 +5396,10 @@
         <v>316</v>
       </c>
       <c r="B143" t="n">
-        <v>0.960312411725153</v>
+        <v>0.889097637073199</v>
       </c>
       <c r="C143" t="n">
-        <v>1.03176497274869</v>
+        <v>0.748293120813006</v>
       </c>
       <c r="D143" t="s">
         <v>67</v>
@@ -5416,10 +5416,10 @@
         <v>317</v>
       </c>
       <c r="B144" t="n">
-        <v>0.516125941880627</v>
+        <v>0.475330781816912</v>
       </c>
       <c r="C144" t="n">
-        <v>2.88131450771605</v>
+        <v>0.323523449288753</v>
       </c>
       <c r="D144" t="s">
         <v>318</v>
@@ -5436,10 +5436,10 @@
         <v>317</v>
       </c>
       <c r="B145" t="n">
-        <v>0.516125941880627</v>
+        <v>0.475330781816912</v>
       </c>
       <c r="C145" t="n">
-        <v>2.88131450771605</v>
+        <v>0.323523449288753</v>
       </c>
       <c r="D145" t="s">
         <v>320</v>
@@ -5456,10 +5456,10 @@
         <v>322</v>
       </c>
       <c r="B146" t="n">
-        <v>1.43596135336925</v>
+        <v>1.33818023314721</v>
       </c>
       <c r="C146" t="n">
-        <v>0.861034793491606</v>
+        <v>0.866261533689472</v>
       </c>
       <c r="D146" t="s">
         <v>223</v>
@@ -5476,10 +5476,10 @@
         <v>323</v>
       </c>
       <c r="B147" t="n">
-        <v>0.921602966084106</v>
+        <v>0.843759861699096</v>
       </c>
       <c r="C147" t="n">
-        <v>1.54565952609555</v>
+        <v>0.53939808014696</v>
       </c>
       <c r="D147" t="s">
         <v>324</v>
@@ -5496,10 +5496,10 @@
         <v>326</v>
       </c>
       <c r="B148" t="n">
-        <v>1.31437439196006</v>
+        <v>1.21470072969065</v>
       </c>
       <c r="C148" t="n">
-        <v>0.994854616617673</v>
+        <v>0.767492666160892</v>
       </c>
       <c r="D148" t="s">
         <v>327</v>
@@ -5516,10 +5516,10 @@
         <v>329</v>
       </c>
       <c r="B149" t="n">
-        <v>1.02871677457029</v>
+        <v>0.979295948080625</v>
       </c>
       <c r="C149" t="n">
-        <v>0.735252948706422</v>
+        <v>1.11403193606065</v>
       </c>
       <c r="D149" t="s">
         <v>330</v>
@@ -5536,10 +5536,10 @@
         <v>329</v>
       </c>
       <c r="B150" t="n">
-        <v>1.02871677457029</v>
+        <v>0.979295948080625</v>
       </c>
       <c r="C150" t="n">
-        <v>0.735252948706422</v>
+        <v>1.11403193606065</v>
       </c>
       <c r="D150" t="s">
         <v>332</v>
@@ -5556,10 +5556,10 @@
         <v>334</v>
       </c>
       <c r="B151" t="n">
-        <v>1.52822770325339</v>
+        <v>1.42026546856137</v>
       </c>
       <c r="C151" t="n">
-        <v>1.1831982070122</v>
+        <v>0.696164480090135</v>
       </c>
       <c r="D151" t="s">
         <v>207</v>
@@ -5576,10 +5576,10 @@
         <v>335</v>
       </c>
       <c r="B152" t="n">
-        <v>1.14113324684292</v>
+        <v>1.06201750314916</v>
       </c>
       <c r="C152" t="n">
-        <v>1.17083926842534</v>
+        <v>0.707013073137862</v>
       </c>
       <c r="D152" t="s">
         <v>160</v>
@@ -5596,10 +5596,10 @@
         <v>336</v>
       </c>
       <c r="B153" t="n">
-        <v>1.57170954630224</v>
+        <v>1.4412640171557</v>
       </c>
       <c r="C153" t="n">
-        <v>0.699604543686607</v>
+        <v>0.846673399593913</v>
       </c>
       <c r="D153" t="s">
         <v>337</v>
@@ -5616,10 +5616,10 @@
         <v>339</v>
       </c>
       <c r="B154" t="n">
-        <v>0.725934672364293</v>
+        <v>0.672908034499845</v>
       </c>
       <c r="C154" t="n">
-        <v>1.86001935286736</v>
+        <v>0.48484761810227</v>
       </c>
       <c r="D154" t="s">
         <v>340</v>
@@ -5636,10 +5636,10 @@
         <v>342</v>
       </c>
       <c r="B155" t="n">
-        <v>1.23552066224164</v>
+        <v>1.14442089839052</v>
       </c>
       <c r="C155" t="n">
-        <v>1.03953166061981</v>
+        <v>0.745906375323473</v>
       </c>
       <c r="D155" t="s">
         <v>343</v>
@@ -5656,10 +5656,10 @@
         <v>345</v>
       </c>
       <c r="B156" t="n">
-        <v>1.23658119499893</v>
+        <v>1.15969257009548</v>
       </c>
       <c r="C156" t="n">
-        <v>0.965203765597936</v>
+        <v>0.84393733837977</v>
       </c>
       <c r="D156" t="s">
         <v>346</v>
@@ -5676,10 +5676,10 @@
         <v>348</v>
       </c>
       <c r="B157" t="n">
-        <v>1.36278459311631</v>
+        <v>1.28759282062453</v>
       </c>
       <c r="C157" t="n">
-        <v>0.861849782805443</v>
+        <v>0.948339559358728</v>
       </c>
       <c r="D157" t="s">
         <v>245</v>
@@ -5696,10 +5696,10 @@
         <v>349</v>
       </c>
       <c r="B158" t="n">
-        <v>0.352096875419935</v>
+        <v>0.321977745112928</v>
       </c>
       <c r="C158" t="n">
-        <v>2.02646219669464</v>
+        <v>0.433986038344563</v>
       </c>
       <c r="D158" t="s">
         <v>350</v>
@@ -5716,10 +5716,10 @@
         <v>349</v>
       </c>
       <c r="B159" t="n">
-        <v>0.352096875419935</v>
+        <v>0.321977745112928</v>
       </c>
       <c r="C159" t="n">
-        <v>2.02646219669464</v>
+        <v>0.433986038344563</v>
       </c>
       <c r="D159" t="s">
         <v>352</v>
@@ -5736,10 +5736,10 @@
         <v>354</v>
       </c>
       <c r="B160" t="n">
-        <v>0.676619899150356</v>
+        <v>0.637592293682122</v>
       </c>
       <c r="C160" t="n">
-        <v>1.13686002537569</v>
+        <v>0.767729175386207</v>
       </c>
       <c r="D160" t="s">
         <v>355</v>
@@ -5756,10 +5756,10 @@
         <v>357</v>
       </c>
       <c r="B161" t="n">
-        <v>0.470876544236298</v>
+        <v>0.432379205146709</v>
       </c>
       <c r="C161" t="n">
-        <v>2.16391249768553</v>
+        <v>0.415125185338721</v>
       </c>
       <c r="D161" t="s">
         <v>358</v>
@@ -5776,10 +5776,10 @@
         <v>360</v>
       </c>
       <c r="B162" t="n">
-        <v>1.20617925595664</v>
+        <v>1.13074002582149</v>
       </c>
       <c r="C162" t="n">
-        <v>0.986053442179956</v>
+        <v>0.827773694812288</v>
       </c>
       <c r="D162" t="s">
         <v>361</v>
@@ -5796,10 +5796,10 @@
         <v>363</v>
       </c>
       <c r="B163" t="n">
-        <v>0.666014571577467</v>
+        <v>0.630910937311202</v>
       </c>
       <c r="C163" t="n">
-        <v>0.985892957782162</v>
+        <v>0.879049840662434</v>
       </c>
       <c r="D163" t="s">
         <v>364</v>
@@ -5816,10 +5816,10 @@
         <v>363</v>
       </c>
       <c r="B164" t="n">
-        <v>0.666014571577467</v>
+        <v>0.630910937311202</v>
       </c>
       <c r="C164" t="n">
-        <v>0.985892957782162</v>
+        <v>0.879049840662434</v>
       </c>
       <c r="D164" t="s">
         <v>366</v>
@@ -5836,10 +5836,10 @@
         <v>363</v>
       </c>
       <c r="B165" t="n">
-        <v>0.666014571577467</v>
+        <v>0.630910937311202</v>
       </c>
       <c r="C165" t="n">
-        <v>0.985892957782162</v>
+        <v>0.879049840662434</v>
       </c>
       <c r="D165" t="s">
         <v>15</v>
@@ -5856,10 +5856,10 @@
         <v>363</v>
       </c>
       <c r="B166" t="n">
-        <v>0.666014571577467</v>
+        <v>0.630910937311202</v>
       </c>
       <c r="C166" t="n">
-        <v>0.985892957782162</v>
+        <v>0.879049840662434</v>
       </c>
       <c r="D166" t="s">
         <v>17</v>
@@ -5876,10 +5876,10 @@
         <v>368</v>
       </c>
       <c r="B167" t="n">
-        <v>1.30392502508678</v>
+        <v>1.23652816836106</v>
       </c>
       <c r="C167" t="n">
-        <v>0.744814467955949</v>
+        <v>1.07830081418833</v>
       </c>
       <c r="D167" t="s">
         <v>369</v>
@@ -5896,10 +5896,10 @@
         <v>371</v>
       </c>
       <c r="B168" t="n">
-        <v>1.13901218132834</v>
+        <v>1.07856181416287</v>
       </c>
       <c r="C168" t="n">
-        <v>0.931123656928562</v>
+        <v>0.894234233022679</v>
       </c>
       <c r="D168" t="s">
         <v>372</v>
@@ -5916,10 +5916,10 @@
         <v>374</v>
       </c>
       <c r="B169" t="n">
-        <v>1.24400492429995</v>
+        <v>1.1686010452567</v>
       </c>
       <c r="C169" t="n">
-        <v>0.921152170216067</v>
+        <v>0.87664758259241</v>
       </c>
       <c r="D169" t="s">
         <v>375</v>
@@ -5936,10 +5936,10 @@
         <v>374</v>
       </c>
       <c r="B170" t="n">
-        <v>1.24400492429995</v>
+        <v>1.1686010452567</v>
       </c>
       <c r="C170" t="n">
-        <v>0.921152170216067</v>
+        <v>0.87664758259241</v>
       </c>
       <c r="D170" t="s">
         <v>377</v>
@@ -5956,10 +5956,10 @@
         <v>379</v>
       </c>
       <c r="B171" t="n">
-        <v>0.949176817773619</v>
+        <v>0.883847999924619</v>
       </c>
       <c r="C171" t="n">
-        <v>1.04678258863765</v>
+        <v>0.764347692063462</v>
       </c>
       <c r="D171" t="s">
         <v>380</v>
@@ -5976,10 +5976,10 @@
         <v>382</v>
       </c>
       <c r="B172" t="n">
-        <v>1.12628578824088</v>
+        <v>1.03847367593735</v>
       </c>
       <c r="C172" t="n">
-        <v>1.03423508846745</v>
+        <v>0.730405080747854</v>
       </c>
       <c r="D172" t="s">
         <v>171</v>
@@ -5996,10 +5996,10 @@
         <v>383</v>
       </c>
       <c r="B173" t="n">
-        <v>0.230489119250801</v>
+        <v>0.211894444906334</v>
       </c>
       <c r="C173" t="n">
-        <v>2.29376190767974</v>
+        <v>0.395763260498764</v>
       </c>
       <c r="D173" t="s">
         <v>151</v>
@@ -6016,10 +6016,10 @@
         <v>383</v>
       </c>
       <c r="B174" t="n">
-        <v>0.230489119250801</v>
+        <v>0.211894444906334</v>
       </c>
       <c r="C174" t="n">
-        <v>2.29376190767974</v>
+        <v>0.395763260498764</v>
       </c>
       <c r="D174" t="s">
         <v>153</v>
@@ -6036,10 +6036,10 @@
         <v>384</v>
       </c>
       <c r="B175" t="n">
-        <v>0.939632022958018</v>
+        <v>0.872394246145898</v>
       </c>
       <c r="C175" t="n">
-        <v>1.22358644660665</v>
+        <v>0.671370390826057</v>
       </c>
       <c r="D175" t="s">
         <v>385</v>
@@ -6056,10 +6056,10 @@
         <v>387</v>
       </c>
       <c r="B176" t="n">
-        <v>0.994779726337044</v>
+        <v>0.941116768818223</v>
       </c>
       <c r="C176" t="n">
-        <v>1.38108206258787</v>
+        <v>0.666260165897137</v>
       </c>
       <c r="D176" t="s">
         <v>192</v>
@@ -6076,10 +6076,10 @@
         <v>388</v>
       </c>
       <c r="B177" t="n">
-        <v>1.29809209492169</v>
+        <v>1.21982477743376</v>
       </c>
       <c r="C177" t="n">
-        <v>1.09611521289708</v>
+        <v>0.776107742894113</v>
       </c>
       <c r="D177" t="s">
         <v>223</v>
@@ -6096,10 +6096,10 @@
         <v>389</v>
       </c>
       <c r="B178" t="n">
-        <v>0.78479424039383</v>
+        <v>0.74258503665373</v>
       </c>
       <c r="C178" t="n">
-        <v>0.827559026607802</v>
+        <v>0.983772819607084</v>
       </c>
       <c r="D178" t="s">
         <v>390</v>
@@ -6116,10 +6116,10 @@
         <v>392</v>
       </c>
       <c r="B179" t="n">
-        <v>0.647985514703554</v>
+        <v>0.5998903541605</v>
       </c>
       <c r="C179" t="n">
-        <v>1.39822592823202</v>
+        <v>0.607836929320926</v>
       </c>
       <c r="D179" t="s">
         <v>393</v>
@@ -6136,10 +6136,10 @@
         <v>395</v>
       </c>
       <c r="B180" t="n">
-        <v>0.78002184298603</v>
+        <v>0.717291330392388</v>
       </c>
       <c r="C180" t="n">
-        <v>1.56967111473504</v>
+        <v>0.542488823537749</v>
       </c>
       <c r="D180" t="s">
         <v>245</v>
@@ -6156,10 +6156,10 @@
         <v>396</v>
       </c>
       <c r="B181" t="n">
-        <v>0.9990218573662</v>
+        <v>0.931571974002622</v>
       </c>
       <c r="C181" t="n">
-        <v>1.23227060332332</v>
+        <v>0.685258762783606</v>
       </c>
       <c r="D181" t="s">
         <v>232</v>
@@ -6176,10 +6176,10 @@
         <v>396</v>
       </c>
       <c r="B182" t="n">
-        <v>0.9990218573662</v>
+        <v>0.931571974002622</v>
       </c>
       <c r="C182" t="n">
-        <v>1.23227060332332</v>
+        <v>0.685258762783606</v>
       </c>
       <c r="D182" t="s">
         <v>397</v>
@@ -6196,10 +6196,10 @@
         <v>396</v>
       </c>
       <c r="B183" t="n">
-        <v>0.9990218573662</v>
+        <v>0.931571974002622</v>
       </c>
       <c r="C183" t="n">
-        <v>1.23227060332332</v>
+        <v>0.685258762783606</v>
       </c>
       <c r="D183" t="s">
         <v>330</v>
@@ -6216,10 +6216,10 @@
         <v>396</v>
       </c>
       <c r="B184" t="n">
-        <v>0.9990218573662</v>
+        <v>0.931571974002622</v>
       </c>
       <c r="C184" t="n">
-        <v>1.23227060332332</v>
+        <v>0.685258762783606</v>
       </c>
       <c r="D184" t="s">
         <v>399</v>
@@ -6236,10 +6236,10 @@
         <v>401</v>
       </c>
       <c r="B185" t="n">
-        <v>1.13052791927003</v>
+        <v>1.04229159386359</v>
       </c>
       <c r="C185" t="n">
-        <v>0.853538483267696</v>
+        <v>0.809620817427451</v>
       </c>
       <c r="D185" t="s">
         <v>192</v>
@@ -6256,10 +6256,10 @@
         <v>402</v>
       </c>
       <c r="B186" t="n">
-        <v>1.25673131738742</v>
+        <v>1.17400976231888</v>
       </c>
       <c r="C186" t="n">
-        <v>0.941660963921205</v>
+        <v>0.82907044689723</v>
       </c>
       <c r="D186" t="s">
         <v>403</v>
@@ -6276,10 +6276,10 @@
         <v>405</v>
       </c>
       <c r="B187" t="n">
-        <v>0.786915305908408</v>
+        <v>0.757856708358691</v>
       </c>
       <c r="C187" t="n">
-        <v>0.919153390238162</v>
+        <v>1.01505571189615</v>
       </c>
       <c r="D187" t="s">
         <v>406</v>
@@ -6296,10 +6296,10 @@
         <v>408</v>
       </c>
       <c r="B188" t="n">
-        <v>1.44868774645672</v>
+        <v>1.36108774070465</v>
       </c>
       <c r="C188" t="n">
-        <v>0.976332794634547</v>
+        <v>0.841309172372682</v>
       </c>
       <c r="D188" t="s">
         <v>409</v>
@@ -6316,10 +6316,10 @@
         <v>411</v>
       </c>
       <c r="B189" t="n">
-        <v>1.17825189334803</v>
+        <v>1.09097004742315</v>
       </c>
       <c r="C189" t="n">
-        <v>1.211749471348</v>
+        <v>0.674350172748632</v>
       </c>
       <c r="D189" t="s">
         <v>412</v>
@@ -6336,10 +6336,10 @@
         <v>414</v>
       </c>
       <c r="B190" t="n">
-        <v>1.49110905674828</v>
+        <v>1.39354004307769</v>
       </c>
       <c r="C190" t="n">
-        <v>0.960738660095575</v>
+        <v>0.818970913122989</v>
       </c>
       <c r="D190" t="s">
         <v>415</v>
@@ -6356,10 +6356,10 @@
         <v>417</v>
       </c>
       <c r="B191" t="n">
-        <v>1.2387022605135</v>
+        <v>1.17782768024512</v>
       </c>
       <c r="C191" t="n">
-        <v>0.683024621610825</v>
+        <v>1.156866580415</v>
       </c>
       <c r="D191" t="s">
         <v>327</v>
@@ -6376,10 +6376,10 @@
         <v>418</v>
       </c>
       <c r="B192" t="n">
-        <v>1.27051824323217</v>
+        <v>1.19882622883944</v>
       </c>
       <c r="C192" t="n">
-        <v>1.16803407547327</v>
+        <v>0.754438818703039</v>
       </c>
       <c r="D192" t="s">
         <v>419</v>
@@ -6396,10 +6396,10 @@
         <v>418</v>
       </c>
       <c r="B193" t="n">
-        <v>1.27051824323217</v>
+        <v>1.19882622883944</v>
       </c>
       <c r="C193" t="n">
-        <v>1.16803407547327</v>
+        <v>0.754438818703039</v>
       </c>
       <c r="D193" t="s">
         <v>397</v>
@@ -6416,10 +6416,10 @@
         <v>418</v>
       </c>
       <c r="B194" t="n">
-        <v>1.27051824323217</v>
+        <v>1.19882622883944</v>
       </c>
       <c r="C194" t="n">
-        <v>1.16803407547327</v>
+        <v>0.754438818703039</v>
       </c>
       <c r="D194" t="s">
         <v>421</v>
@@ -6436,10 +6436,10 @@
         <v>418</v>
       </c>
       <c r="B195" t="n">
-        <v>1.27051824323217</v>
+        <v>1.19882622883944</v>
       </c>
       <c r="C195" t="n">
-        <v>1.16803407547327</v>
+        <v>0.754438818703039</v>
       </c>
       <c r="D195" t="s">
         <v>399</v>
@@ -6456,10 +6456,10 @@
         <v>418</v>
       </c>
       <c r="B196" t="n">
-        <v>1.27051824323217</v>
+        <v>1.19882622883944</v>
       </c>
       <c r="C196" t="n">
-        <v>1.16803407547327</v>
+        <v>0.754438818703039</v>
       </c>
       <c r="D196" t="s">
         <v>423</v>
@@ -6476,10 +6476,10 @@
         <v>425</v>
       </c>
       <c r="B197" t="n">
-        <v>1.21324947433857</v>
+        <v>1.13583058305648</v>
       </c>
       <c r="C197" t="n">
-        <v>1.10097760514635</v>
+        <v>0.760426139935753</v>
       </c>
       <c r="D197" t="s">
         <v>426</v>
@@ -6496,10 +6496,10 @@
         <v>425</v>
       </c>
       <c r="B198" t="n">
-        <v>1.21324947433857</v>
+        <v>1.13583058305648</v>
       </c>
       <c r="C198" t="n">
-        <v>1.10097760514635</v>
+        <v>0.760426139935753</v>
       </c>
       <c r="D198" t="s">
         <v>428</v>
@@ -6516,10 +6516,10 @@
         <v>430</v>
       </c>
       <c r="B199" t="n">
-        <v>1.28112357080506</v>
+        <v>1.18737247506072</v>
       </c>
       <c r="C199" t="n">
-        <v>1.23180507026553</v>
+        <v>0.668134988266577</v>
       </c>
       <c r="D199" t="s">
         <v>185</v>
@@ -6536,10 +6536,10 @@
         <v>431</v>
       </c>
       <c r="B200" t="n">
-        <v>0.766765183519918</v>
+        <v>0.705360336872887</v>
       </c>
       <c r="C200" t="n">
-        <v>2.15719618456158</v>
+        <v>0.418295909557244</v>
       </c>
       <c r="D200" t="s">
         <v>340</v>
@@ -6556,10 +6556,10 @@
         <v>432</v>
       </c>
       <c r="B201" t="n">
-        <v>0.79539956796672</v>
+        <v>0.767401503174291</v>
       </c>
       <c r="C201" t="n">
-        <v>0.660840691554937</v>
+        <v>1.33470305543592</v>
       </c>
       <c r="D201" t="s">
         <v>433</v>
@@ -6576,10 +6576,10 @@
         <v>435</v>
       </c>
       <c r="B202" t="n">
-        <v>1.12840685375545</v>
+        <v>1.05756326556855</v>
       </c>
       <c r="C202" t="n">
-        <v>1.0255718993594</v>
+        <v>0.802616941402962</v>
       </c>
       <c r="D202" t="s">
         <v>436</v>
@@ -6596,10 +6596,10 @@
         <v>438</v>
       </c>
       <c r="B203" t="n">
-        <v>1.30975795525187</v>
+        <v>1.23652816836106</v>
       </c>
       <c r="C203" t="n">
-        <v>0.926166097810048</v>
+        <v>0.903297031527028</v>
       </c>
       <c r="D203" t="s">
         <v>237</v>
@@ -6616,10 +6616,10 @@
         <v>438</v>
       </c>
       <c r="B204" t="n">
-        <v>1.30975795525187</v>
+        <v>1.23652816836106</v>
       </c>
       <c r="C204" t="n">
-        <v>0.926166097810048</v>
+        <v>0.903297031527028</v>
       </c>
       <c r="D204" t="s">
         <v>239</v>
@@ -6636,10 +6636,10 @@
         <v>439</v>
       </c>
       <c r="B205" t="n">
-        <v>0.939632022958018</v>
+        <v>0.866667369256538</v>
       </c>
       <c r="C205" t="n">
-        <v>1.42796519235477</v>
+        <v>0.588684681339004</v>
       </c>
       <c r="D205" t="s">
         <v>107</v>
@@ -6656,10 +6656,10 @@
         <v>440</v>
       </c>
       <c r="B206" t="n">
-        <v>1.25567078463013</v>
+        <v>1.18164559817136</v>
       </c>
       <c r="C206" t="n">
-        <v>0.755660442743484</v>
+        <v>1.00769861157149</v>
       </c>
       <c r="D206" t="s">
         <v>441</v>
@@ -6676,10 +6676,10 @@
         <v>443</v>
       </c>
       <c r="B207" t="n">
-        <v>1.18037295886261</v>
+        <v>1.10337828068343</v>
       </c>
       <c r="C207" t="n">
-        <v>0.893029398048666</v>
+        <v>0.863909011581849</v>
       </c>
       <c r="D207" t="s">
         <v>250</v>
@@ -6696,10 +6696,10 @@
         <v>444</v>
       </c>
       <c r="B208" t="n">
-        <v>0.137282580752043</v>
+        <v>0.126063327753216</v>
       </c>
       <c r="C208" t="n">
-        <v>2.94333754388323</v>
+        <v>0.319524662176353</v>
       </c>
       <c r="D208" t="s">
         <v>151</v>
@@ -6716,10 +6716,10 @@
         <v>444</v>
       </c>
       <c r="B209" t="n">
-        <v>0.137282580752043</v>
+        <v>0.126063327753216</v>
       </c>
       <c r="C209" t="n">
-        <v>2.94333754388323</v>
+        <v>0.319524662176353</v>
       </c>
       <c r="D209" t="s">
         <v>153</v>
@@ -6736,10 +6736,10 @@
         <v>445</v>
       </c>
       <c r="B210" t="n">
-        <v>0.480421339051899</v>
+        <v>0.439537801258409</v>
       </c>
       <c r="C210" t="n">
-        <v>1.69958182300593</v>
+        <v>0.500925787991356</v>
       </c>
       <c r="D210" t="s">
         <v>127</v>
@@ -6756,10 +6756,10 @@
         <v>445</v>
       </c>
       <c r="B211" t="n">
-        <v>0.480421339051899</v>
+        <v>0.439537801258409</v>
       </c>
       <c r="C211" t="n">
-        <v>1.69958182300593</v>
+        <v>0.500925787991356</v>
       </c>
       <c r="D211" t="s">
         <v>129</v>
@@ -6776,10 +6776,10 @@
         <v>445</v>
       </c>
       <c r="B212" t="n">
-        <v>0.480421339051899</v>
+        <v>0.439537801258409</v>
       </c>
       <c r="C212" t="n">
-        <v>1.69958182300593</v>
+        <v>0.500925787991356</v>
       </c>
       <c r="D212" t="s">
         <v>120</v>
@@ -6796,10 +6796,10 @@
         <v>445</v>
       </c>
       <c r="B213" t="n">
-        <v>0.480421339051899</v>
+        <v>0.439537801258409</v>
       </c>
       <c r="C213" t="n">
-        <v>1.69958182300593</v>
+        <v>0.500925787991356</v>
       </c>
       <c r="D213" t="s">
         <v>122</v>
@@ -6816,10 +6816,10 @@
         <v>446</v>
       </c>
       <c r="B214" t="n">
-        <v>0.918421367812239</v>
+        <v>0.85012305824283</v>
       </c>
       <c r="C214" t="n">
-        <v>1.34869661095923</v>
+        <v>0.623842838946173</v>
       </c>
       <c r="D214" t="s">
         <v>447</v>
@@ -6836,10 +6836,10 @@
         <v>449</v>
       </c>
       <c r="B215" t="n">
-        <v>1.15810177095954</v>
+        <v>1.09956036275719</v>
       </c>
       <c r="C215" t="n">
-        <v>0.933345437028156</v>
+        <v>0.926089256993261</v>
       </c>
       <c r="D215" t="s">
         <v>450</v>
@@ -6856,10 +6856,10 @@
         <v>452</v>
       </c>
       <c r="B216" t="n">
-        <v>1.25779185014471</v>
+        <v>1.1854635160976</v>
       </c>
       <c r="C216" t="n">
-        <v>0.787681427521626</v>
+        <v>0.985423504653401</v>
       </c>
       <c r="D216" t="s">
         <v>242</v>
@@ -6876,10 +6876,10 @@
         <v>453</v>
       </c>
       <c r="B217" t="n">
-        <v>0.238771375069629</v>
+        <v>0.216169437513885</v>
       </c>
       <c r="C217" t="n">
-        <v>2.35481810657146</v>
+        <v>0.378846336836367</v>
       </c>
       <c r="D217" t="s">
         <v>151</v>
@@ -6896,10 +6896,10 @@
         <v>453</v>
       </c>
       <c r="B218" t="n">
-        <v>0.238771375069629</v>
+        <v>0.216169437513885</v>
       </c>
       <c r="C218" t="n">
-        <v>2.35481810657146</v>
+        <v>0.378846336836367</v>
       </c>
       <c r="D218" t="s">
         <v>153</v>
@@ -6916,10 +6916,10 @@
         <v>454</v>
       </c>
       <c r="B219" t="n">
-        <v>1.25991291565928</v>
+        <v>1.18355455713448</v>
       </c>
       <c r="C219" t="n">
-        <v>0.920348364528742</v>
+        <v>0.873618192795342</v>
       </c>
       <c r="D219" t="s">
         <v>455</v>
@@ -6936,10 +6936,10 @@
         <v>457</v>
       </c>
       <c r="B220" t="n">
-        <v>1.48050372917539</v>
+        <v>1.40499379685641</v>
       </c>
       <c r="C220" t="n">
-        <v>0.751653415235356</v>
+        <v>1.07346874976891</v>
       </c>
       <c r="D220" t="s">
         <v>458</v>
@@ -6956,10 +6956,10 @@
         <v>460</v>
       </c>
       <c r="B221" t="n">
-        <v>1.21324947433857</v>
+        <v>1.12437682927775</v>
       </c>
       <c r="C221" t="n">
-        <v>0.884732489759041</v>
+        <v>0.815419794554726</v>
       </c>
       <c r="D221" t="s">
         <v>461</v>
@@ -6976,10 +6976,10 @@
         <v>460</v>
       </c>
       <c r="B222" t="n">
-        <v>1.21324947433857</v>
+        <v>1.12437682927775</v>
       </c>
       <c r="C222" t="n">
-        <v>0.884732489759041</v>
+        <v>0.815419794554726</v>
       </c>
       <c r="D222" t="s">
         <v>463</v>
@@ -6996,10 +6996,10 @@
         <v>465</v>
       </c>
       <c r="B223" t="n">
-        <v>1.31930275006747</v>
+        <v>1.25036812084368</v>
       </c>
       <c r="C223" t="n">
-        <v>0.689657232531408</v>
+        <v>1.11647128870508</v>
       </c>
       <c r="D223" t="s">
         <v>466</v>
@@ -7016,10 +7016,10 @@
         <v>468</v>
       </c>
       <c r="B224" t="n">
-        <v>0.571581046058867</v>
+        <v>0.524591839735349</v>
       </c>
       <c r="C224" t="n">
-        <v>1.11021455316185</v>
+        <v>0.689170455566436</v>
       </c>
       <c r="D224" t="s">
         <v>469</v>
@@ -7036,10 +7036,10 @@
         <v>471</v>
       </c>
       <c r="B225" t="n">
-        <v>0.557840230333993</v>
+        <v>0.519236837968675</v>
       </c>
       <c r="C225" t="n">
-        <v>1.15606749652027</v>
+        <v>0.71307213347863</v>
       </c>
       <c r="D225" t="s">
         <v>472</v>
@@ -7056,10 +7056,10 @@
         <v>474</v>
       </c>
       <c r="B226" t="n">
-        <v>0.801762764510453</v>
+        <v>0.761674626284931</v>
       </c>
       <c r="C226" t="n">
-        <v>1.02855486089456</v>
+        <v>0.86072272658443</v>
       </c>
       <c r="D226" t="s">
         <v>475</v>
@@ -7076,10 +7076,10 @@
         <v>474</v>
       </c>
       <c r="B227" t="n">
-        <v>0.801762764510453</v>
+        <v>0.761674626284931</v>
       </c>
       <c r="C227" t="n">
-        <v>1.02855486089456</v>
+        <v>0.86072272658443</v>
       </c>
       <c r="D227" t="s">
         <v>477</v>
@@ -7096,10 +7096,10 @@
         <v>479</v>
       </c>
       <c r="B228" t="n">
-        <v>0.820852354141655</v>
+        <v>0.74449399561685</v>
       </c>
       <c r="C228" t="n">
-        <v>1.10719399799178</v>
+        <v>0.639239882246271</v>
       </c>
       <c r="D228" t="s">
         <v>480</v>
@@ -7116,10 +7116,10 @@
         <v>482</v>
       </c>
       <c r="B229" t="n">
-        <v>1.53353036703984</v>
+        <v>1.4412640171557</v>
       </c>
       <c r="C229" t="n">
-        <v>0.763772740373615</v>
+        <v>0.981641531167542</v>
       </c>
       <c r="D229" t="s">
         <v>483</v>
@@ -7136,10 +7136,10 @@
         <v>482</v>
       </c>
       <c r="B230" t="n">
-        <v>1.53353036703984</v>
+        <v>1.4412640171557</v>
       </c>
       <c r="C230" t="n">
-        <v>0.763772740373615</v>
+        <v>0.981641531167542</v>
       </c>
       <c r="D230" t="s">
         <v>485</v>
@@ -7156,10 +7156,10 @@
         <v>487</v>
       </c>
       <c r="B231" t="n">
-        <v>1.46247467230148</v>
+        <v>1.34104367159189</v>
       </c>
       <c r="C231" t="n">
-        <v>1.03311246988454</v>
+        <v>0.707837152443811</v>
       </c>
       <c r="D231" t="s">
         <v>361</v>
@@ -7176,10 +7176,10 @@
         <v>488</v>
       </c>
       <c r="B232" t="n">
-        <v>1.42853762406823</v>
+        <v>1.33054439729473</v>
       </c>
       <c r="C232" t="n">
-        <v>1.00131936289999</v>
+        <v>0.790587362697871</v>
       </c>
       <c r="D232" t="s">
         <v>361</v>
@@ -7196,10 +7196,10 @@
         <v>489</v>
       </c>
       <c r="B233" t="n">
-        <v>0.17453339091384</v>
+        <v>0.160548343564975</v>
       </c>
       <c r="C233" t="n">
-        <v>1.5384627316384</v>
+        <v>0.553526694703766</v>
       </c>
       <c r="D233" t="s">
         <v>20</v>
@@ -7216,10 +7216,10 @@
         <v>490</v>
       </c>
       <c r="B234" t="n">
-        <v>1.29916756476006</v>
+        <v>1.20433562939123</v>
       </c>
       <c r="C234" t="n">
-        <v>1.09188357178479</v>
+        <v>0.728670577749332</v>
       </c>
       <c r="D234" t="s">
         <v>491</v>
@@ -7236,10 +7236,10 @@
         <v>493</v>
       </c>
       <c r="B235" t="n">
-        <v>1.11850854802076</v>
+        <v>1.05819958522292</v>
       </c>
       <c r="C235" t="n">
-        <v>1.08190922261405</v>
+        <v>0.813622933644024</v>
       </c>
       <c r="D235" t="s">
         <v>491</v>
@@ -7256,10 +7256,10 @@
         <v>494</v>
       </c>
       <c r="B236" t="n">
-        <v>0.982053333249577</v>
+        <v>0.9010286305927</v>
       </c>
       <c r="C236" t="n">
-        <v>0.960781866977342</v>
+        <v>0.73690055834466</v>
       </c>
       <c r="D236" t="s">
         <v>495</v>
@@ -7276,10 +7276,10 @@
         <v>497</v>
       </c>
       <c r="B237" t="n">
-        <v>1.03138325693147</v>
+        <v>0.94860576167354</v>
       </c>
       <c r="C237" t="n">
-        <v>1.49103422758248</v>
+        <v>0.566701296890267</v>
       </c>
       <c r="D237" t="s">
         <v>20</v>
@@ -7296,10 +7296,10 @@
         <v>498</v>
       </c>
       <c r="B238" t="n">
-        <v>0.909937105753927</v>
+        <v>0.833260587401936</v>
       </c>
       <c r="C238" t="n">
-        <v>1.30749265697196</v>
+        <v>0.608107838120163</v>
       </c>
       <c r="D238" t="s">
         <v>343</v>
@@ -7316,10 +7316,10 @@
         <v>499</v>
       </c>
       <c r="B239" t="n">
-        <v>1.44550614818485</v>
+        <v>1.35249742537061</v>
       </c>
       <c r="C239" t="n">
-        <v>0.857928722486993</v>
+        <v>0.888101791766342</v>
       </c>
       <c r="D239" t="s">
         <v>500</v>
@@ -7336,10 +7336,10 @@
         <v>502</v>
       </c>
       <c r="B240" t="n">
-        <v>1.16446496750328</v>
+        <v>1.10242380120187</v>
       </c>
       <c r="C240" t="n">
-        <v>1.04099356049463</v>
+        <v>0.841396787800446</v>
       </c>
       <c r="D240" t="s">
         <v>503</v>
@@ -7356,10 +7356,10 @@
         <v>505</v>
       </c>
       <c r="B241" t="n">
-        <v>1.04356423317234</v>
+        <v>0.977386989117505</v>
       </c>
       <c r="C241" t="n">
-        <v>1.27031506499523</v>
+        <v>0.685376747718879</v>
       </c>
       <c r="D241" t="s">
         <v>506</v>
@@ -7376,10 +7376,10 @@
         <v>508</v>
       </c>
       <c r="B242" t="n">
-        <v>1.02235357802656</v>
+        <v>0.981204907043745</v>
       </c>
       <c r="C242" t="n">
-        <v>0.745834018726518</v>
+        <v>1.171852887951</v>
       </c>
       <c r="D242" t="s">
         <v>509</v>
@@ -7396,10 +7396,10 @@
         <v>511</v>
       </c>
       <c r="B243" t="n">
-        <v>0.499864439602196</v>
+        <v>0.471512863890671</v>
       </c>
       <c r="C243" t="n">
-        <v>0.815185096524768</v>
+        <v>0.972647100461969</v>
       </c>
       <c r="D243" t="s">
         <v>512</v>
@@ -7416,10 +7416,10 @@
         <v>511</v>
       </c>
       <c r="B244" t="n">
-        <v>0.499864439602196</v>
+        <v>0.471512863890671</v>
       </c>
       <c r="C244" t="n">
-        <v>0.815185096524768</v>
+        <v>0.972647100461969</v>
       </c>
       <c r="D244" t="s">
         <v>514</v>
@@ -7436,10 +7436,10 @@
         <v>511</v>
       </c>
       <c r="B245" t="n">
-        <v>0.499864439602196</v>
+        <v>0.471512863890671</v>
       </c>
       <c r="C245" t="n">
-        <v>0.815185096524768</v>
+        <v>0.972647100461969</v>
       </c>
       <c r="D245" t="s">
         <v>516</v>
@@ -7456,10 +7456,10 @@
         <v>511</v>
       </c>
       <c r="B246" t="n">
-        <v>0.499864439602196</v>
+        <v>0.471512863890671</v>
       </c>
       <c r="C246" t="n">
-        <v>0.815185096524768</v>
+        <v>0.972647100461969</v>
       </c>
       <c r="D246" t="s">
         <v>518</v>
@@ -7476,10 +7476,10 @@
         <v>511</v>
       </c>
       <c r="B247" t="n">
-        <v>0.499864439602196</v>
+        <v>0.471512863890671</v>
       </c>
       <c r="C247" t="n">
-        <v>0.815185096524768</v>
+        <v>0.972647100461969</v>
       </c>
       <c r="D247" t="s">
         <v>520</v>
@@ -7496,10 +7496,10 @@
         <v>511</v>
       </c>
       <c r="B248" t="n">
-        <v>0.499864439602196</v>
+        <v>0.471512863890671</v>
       </c>
       <c r="C248" t="n">
-        <v>0.815185096524768</v>
+        <v>0.972647100461969</v>
       </c>
       <c r="D248" t="s">
         <v>522</v>
@@ -7516,10 +7516,10 @@
         <v>511</v>
       </c>
       <c r="B249" t="n">
-        <v>0.499864439602196</v>
+        <v>0.471512863890671</v>
       </c>
       <c r="C249" t="n">
-        <v>0.815185096524768</v>
+        <v>0.972647100461969</v>
       </c>
       <c r="D249" t="s">
         <v>524</v>
@@ -7536,10 +7536,10 @@
         <v>511</v>
       </c>
       <c r="B250" t="n">
-        <v>0.499864439602196</v>
+        <v>0.471512863890671</v>
       </c>
       <c r="C250" t="n">
-        <v>0.815185096524768</v>
+        <v>0.972647100461969</v>
       </c>
       <c r="D250" t="s">
         <v>526</v>
@@ -7556,10 +7556,10 @@
         <v>511</v>
       </c>
       <c r="B251" t="n">
-        <v>0.499864439602196</v>
+        <v>0.471512863890671</v>
       </c>
       <c r="C251" t="n">
-        <v>0.815185096524768</v>
+        <v>0.972647100461969</v>
       </c>
       <c r="D251" t="s">
         <v>528</v>
@@ -7576,10 +7576,10 @@
         <v>511</v>
       </c>
       <c r="B252" t="n">
-        <v>0.499864439602196</v>
+        <v>0.471512863890671</v>
       </c>
       <c r="C252" t="n">
-        <v>0.815185096524768</v>
+        <v>0.972647100461969</v>
       </c>
       <c r="D252" t="s">
         <v>530</v>
@@ -7596,10 +7596,10 @@
         <v>532</v>
       </c>
       <c r="B253" t="n">
-        <v>0.831457681714544</v>
+        <v>0.772173900582092</v>
       </c>
       <c r="C253" t="n">
-        <v>1.14198734628415</v>
+        <v>0.708556546639866</v>
       </c>
       <c r="D253" t="s">
         <v>138</v>
@@ -7616,10 +7616,10 @@
         <v>533</v>
       </c>
       <c r="B254" t="n">
-        <v>0.960842678103797</v>
+        <v>0.914391343334541</v>
       </c>
       <c r="C254" t="n">
-        <v>1.03326769360662</v>
+        <v>0.866130300281177</v>
       </c>
       <c r="D254" t="s">
         <v>534</v>
@@ -7636,10 +7636,10 @@
         <v>536</v>
       </c>
       <c r="B255" t="n">
-        <v>1.12946738651274</v>
+        <v>1.05947222453167</v>
       </c>
       <c r="C255" t="n">
-        <v>1.0950687683381</v>
+        <v>0.770823443759821</v>
       </c>
       <c r="D255" t="s">
         <v>346</v>
@@ -7656,10 +7656,10 @@
         <v>537</v>
       </c>
       <c r="B256" t="n">
-        <v>0.895089647151882</v>
+        <v>0.853304656514697</v>
       </c>
       <c r="C256" t="n">
-        <v>0.848788665469878</v>
+        <v>1.0161903313269</v>
       </c>
       <c r="D256" t="s">
         <v>189</v>
@@ -7676,10 +7676,10 @@
         <v>538</v>
       </c>
       <c r="B257" t="n">
-        <v>0.814489157597921</v>
+        <v>0.74449399561685</v>
       </c>
       <c r="C257" t="n">
-        <v>1.01950687750864</v>
+        <v>0.698709070358607</v>
       </c>
       <c r="D257" t="s">
         <v>539</v>
@@ -7696,10 +7696,10 @@
         <v>541</v>
       </c>
       <c r="B258" t="n">
-        <v>1.04568529868691</v>
+        <v>0.968796673783465</v>
       </c>
       <c r="C258" t="n">
-        <v>1.04815012777655</v>
+        <v>0.739139744283286</v>
       </c>
       <c r="D258" t="s">
         <v>447</v>
@@ -7716,10 +7716,10 @@
         <v>542</v>
       </c>
       <c r="B259" t="n">
-        <v>1.08810660897847</v>
+        <v>1.00983929149055</v>
       </c>
       <c r="C259" t="n">
-        <v>1.11099906960855</v>
+        <v>0.722950859654846</v>
       </c>
       <c r="D259" t="s">
         <v>543</v>
@@ -7736,10 +7736,10 @@
         <v>542</v>
       </c>
       <c r="B260" t="n">
-        <v>1.08810660897847</v>
+        <v>1.00983929149055</v>
       </c>
       <c r="C260" t="n">
-        <v>1.11099906960855</v>
+        <v>0.722950859654846</v>
       </c>
       <c r="D260" t="s">
         <v>545</v>
@@ -7756,10 +7756,10 @@
         <v>542</v>
       </c>
       <c r="B261" t="n">
-        <v>1.08810660897847</v>
+        <v>1.00983929149055</v>
       </c>
       <c r="C261" t="n">
-        <v>1.11099906960855</v>
+        <v>0.722950859654846</v>
       </c>
       <c r="D261" t="s">
         <v>547</v>
@@ -7776,10 +7776,10 @@
         <v>549</v>
       </c>
       <c r="B262" t="n">
-        <v>0.505874125226834</v>
+        <v>0.461968069075071</v>
       </c>
       <c r="C262" t="n">
-        <v>1.69077975114144</v>
+        <v>0.49918811526289</v>
       </c>
       <c r="D262" t="s">
         <v>291</v>
@@ -7796,10 +7796,10 @@
         <v>550</v>
       </c>
       <c r="B263" t="n">
-        <v>0.315712443900636</v>
+        <v>0.289635153025123</v>
       </c>
       <c r="C263" t="n">
-        <v>1.73714284845477</v>
+        <v>0.499309307304545</v>
       </c>
       <c r="D263" t="s">
         <v>358</v>
@@ -7816,10 +7816,10 @@
         <v>551</v>
       </c>
       <c r="B264" t="n">
-        <v>1.25991291565928</v>
+        <v>1.18737247506072</v>
       </c>
       <c r="C264" t="n">
-        <v>1.47945694266616</v>
+        <v>0.62018300336159</v>
       </c>
       <c r="D264" t="s">
         <v>552</v>
@@ -7836,10 +7836,10 @@
         <v>554</v>
       </c>
       <c r="B265" t="n">
-        <v>0.456029085634253</v>
+        <v>0.429515766702029</v>
       </c>
       <c r="C265" t="n">
-        <v>1.01778093609489</v>
+        <v>0.828381448011425</v>
       </c>
       <c r="D265" t="s">
         <v>555</v>
@@ -7856,10 +7856,10 @@
         <v>557</v>
       </c>
       <c r="B266" t="n">
-        <v>0.704193750839869</v>
+        <v>0.657318202967697</v>
       </c>
       <c r="C266" t="n">
-        <v>1.28155055824576</v>
+        <v>0.671725407663103</v>
       </c>
       <c r="D266" t="s">
         <v>512</v>
@@ -7876,10 +7876,10 @@
         <v>558</v>
       </c>
       <c r="B267" t="n">
-        <v>1.05098796247336</v>
+        <v>0.994567619785586</v>
       </c>
       <c r="C267" t="n">
-        <v>1.04334960502475</v>
+        <v>0.832388815206832</v>
       </c>
       <c r="D267" t="s">
         <v>151</v>
@@ -7896,10 +7896,10 @@
         <v>559</v>
       </c>
       <c r="B268" t="n">
-        <v>1.10719619860967</v>
+        <v>1.03179231956643</v>
       </c>
       <c r="C268" t="n">
-        <v>0.9410777324221</v>
+        <v>0.820841691997674</v>
       </c>
       <c r="D268" t="s">
         <v>375</v>
@@ -7916,10 +7916,10 @@
         <v>560</v>
       </c>
       <c r="B269" t="n">
-        <v>0.967205874647531</v>
+        <v>0.912482384371421</v>
       </c>
       <c r="C269" t="n">
-        <v>1.31998826790357</v>
+        <v>0.676729934192495</v>
       </c>
       <c r="D269" t="s">
         <v>561</v>
@@ -7936,10 +7936,10 @@
         <v>563</v>
       </c>
       <c r="B270" t="n">
-        <v>1.22973904817771</v>
+        <v>1.15754844952096</v>
       </c>
       <c r="C270" t="n">
-        <v>0.787765877822771</v>
+        <v>0.975351295117452</v>
       </c>
       <c r="D270" t="s">
         <v>81</v>
@@ -7956,10 +7956,10 @@
         <v>564</v>
       </c>
       <c r="B271" t="n">
-        <v>1.16446496750328</v>
+        <v>1.10337828068343</v>
       </c>
       <c r="C271" t="n">
-        <v>0.994544793371612</v>
+        <v>0.873576693244109</v>
       </c>
       <c r="D271" t="s">
         <v>565</v>
@@ -7976,10 +7976,10 @@
         <v>567</v>
       </c>
       <c r="B272" t="n">
-        <v>1.0372010366286</v>
+        <v>0.971660112228145</v>
       </c>
       <c r="C272" t="n">
-        <v>0.893349551721862</v>
+        <v>0.878110113664596</v>
       </c>
       <c r="D272" t="s">
         <v>20</v>
@@ -7996,10 +7996,10 @@
         <v>568</v>
       </c>
       <c r="B273" t="n">
-        <v>1.18567562264906</v>
+        <v>1.08047077312599</v>
       </c>
       <c r="C273" t="n">
-        <v>1.74519100060724</v>
+        <v>0.483077333189976</v>
       </c>
       <c r="D273" t="s">
         <v>569</v>
@@ -8016,10 +8016,10 @@
         <v>571</v>
       </c>
       <c r="B274" t="n">
-        <v>1.05416956074523</v>
+        <v>0.986931783933106</v>
       </c>
       <c r="C274" t="n">
-        <v>1.51526467403966</v>
+        <v>0.593923383201874</v>
       </c>
       <c r="D274" t="s">
         <v>189</v>
@@ -8036,10 +8036,10 @@
         <v>572</v>
       </c>
       <c r="B275" t="n">
-        <v>1.0562906262598</v>
+        <v>1.00411241460119</v>
       </c>
       <c r="C275" t="n">
-        <v>1.28440647090302</v>
+        <v>0.721526060968055</v>
       </c>
       <c r="D275" t="s">
         <v>573</v>
@@ -8056,10 +8056,10 @@
         <v>575</v>
       </c>
       <c r="B276" t="n">
-        <v>1.16967121922088</v>
+        <v>1.09345169407521</v>
       </c>
       <c r="C276" t="n">
-        <v>1.31445406871867</v>
+        <v>0.679465219924238</v>
       </c>
       <c r="D276" t="s">
         <v>237</v>
@@ -8076,10 +8076,10 @@
         <v>576</v>
       </c>
       <c r="B277" t="n">
-        <v>0.989187826344066</v>
+        <v>0.922408970979645</v>
       </c>
       <c r="C277" t="n">
-        <v>1.27811653069539</v>
+        <v>0.69145912629269</v>
       </c>
       <c r="D277" t="s">
         <v>569</v>
@@ -8096,10 +8096,10 @@
         <v>577</v>
       </c>
       <c r="B278" t="n">
-        <v>1.09871193655136</v>
+        <v>1.05183638867919</v>
       </c>
       <c r="C278" t="n">
-        <v>0.775006216583832</v>
+        <v>1.12019640954929</v>
       </c>
       <c r="D278" t="s">
         <v>43</v>
@@ -8116,10 +8116,10 @@
         <v>578</v>
       </c>
       <c r="B279" t="n">
-        <v>1.09234874000763</v>
+        <v>1.03656471697423</v>
       </c>
       <c r="C279" t="n">
-        <v>0.845299619517487</v>
+        <v>0.991107192524647</v>
       </c>
       <c r="D279" t="s">
         <v>163</v>
@@ -8136,10 +8136,10 @@
         <v>579</v>
       </c>
       <c r="B280" t="n">
-        <v>1.1050751330951</v>
+        <v>1.03465575801111</v>
       </c>
       <c r="C280" t="n">
-        <v>0.967225019870943</v>
+        <v>0.831771767955143</v>
       </c>
       <c r="D280" t="s">
         <v>580</v>
@@ -8156,10 +8156,10 @@
         <v>582</v>
       </c>
       <c r="B281" t="n">
-        <v>0.709142903707218</v>
+        <v>0.674498833635778</v>
       </c>
       <c r="C281" t="n">
-        <v>0.796732121027145</v>
+        <v>1.04654327151968</v>
       </c>
       <c r="D281" t="s">
         <v>364</v>
@@ -8176,10 +8176,10 @@
         <v>582</v>
       </c>
       <c r="B282" t="n">
-        <v>0.709142903707218</v>
+        <v>0.674498833635778</v>
       </c>
       <c r="C282" t="n">
-        <v>0.796732121027145</v>
+        <v>1.04654327151968</v>
       </c>
       <c r="D282" t="s">
         <v>583</v>
@@ -8196,10 +8196,10 @@
         <v>585</v>
       </c>
       <c r="B283" t="n">
-        <v>1.00962718493909</v>
+        <v>0.947798125189143</v>
       </c>
       <c r="C283" t="n">
-        <v>1.27616002176831</v>
+        <v>0.687581330470791</v>
       </c>
       <c r="D283" t="s">
         <v>181</v>
@@ -8216,10 +8216,10 @@
         <v>585</v>
       </c>
       <c r="B284" t="n">
-        <v>1.00962718493909</v>
+        <v>0.947798125189143</v>
       </c>
       <c r="C284" t="n">
-        <v>1.27616002176831</v>
+        <v>0.687581330470791</v>
       </c>
       <c r="D284" t="s">
         <v>20</v>
@@ -8236,10 +8236,10 @@
         <v>586</v>
       </c>
       <c r="B285" t="n">
-        <v>1.00008239012349</v>
+        <v>0.939207809855103</v>
       </c>
       <c r="C285" t="n">
-        <v>1.17758265324599</v>
+        <v>0.734804997547035</v>
       </c>
       <c r="D285" t="s">
         <v>181</v>
@@ -8256,10 +8256,10 @@
         <v>586</v>
       </c>
       <c r="B286" t="n">
-        <v>1.00008239012349</v>
+        <v>0.939207809855103</v>
       </c>
       <c r="C286" t="n">
-        <v>1.17758265324599</v>
+        <v>0.734804997547035</v>
       </c>
       <c r="D286" t="s">
         <v>20</v>
@@ -8276,10 +8276,10 @@
         <v>587</v>
       </c>
       <c r="B287" t="n">
-        <v>1.14537537787208</v>
+        <v>1.08428869105223</v>
       </c>
       <c r="C287" t="n">
-        <v>1.16649889082207</v>
+        <v>0.767906814137633</v>
       </c>
       <c r="D287" t="s">
         <v>500</v>
@@ -8296,10 +8296,10 @@
         <v>588</v>
       </c>
       <c r="B288" t="n">
-        <v>0.449665889090519</v>
+        <v>0.413289615515508</v>
       </c>
       <c r="C288" t="n">
-        <v>1.22866979002775</v>
+        <v>0.644919080324552</v>
       </c>
       <c r="D288" t="s">
         <v>181</v>
@@ -8316,10 +8316,10 @@
         <v>588</v>
       </c>
       <c r="B289" t="n">
-        <v>0.449665889090519</v>
+        <v>0.413289615515508</v>
       </c>
       <c r="C289" t="n">
-        <v>1.22866979002775</v>
+        <v>0.644919080324552</v>
       </c>
       <c r="D289" t="s">
         <v>20</v>
@@ -8336,10 +8336,10 @@
         <v>589</v>
       </c>
       <c r="B290" t="n">
-        <v>0.15271671704961</v>
+        <v>0.139990323962143</v>
       </c>
       <c r="C290" t="n">
-        <v>1.32529803691998</v>
+        <v>0.618873687734322</v>
       </c>
       <c r="D290" t="s">
         <v>20</v>
@@ -8356,10 +8356,10 @@
         <v>590</v>
       </c>
       <c r="B291" t="n">
-        <v>1.02659570905571</v>
+        <v>0.959251878967864</v>
       </c>
       <c r="C291" t="n">
-        <v>1.10001533186803</v>
+        <v>0.753692916138411</v>
       </c>
       <c r="D291" t="s">
         <v>393</v>
@@ -8376,10 +8376,10 @@
         <v>591</v>
       </c>
       <c r="B292" t="n">
-        <v>1.19203881919279</v>
+        <v>1.13010370616712</v>
       </c>
       <c r="C292" t="n">
-        <v>1.2185322303361</v>
+        <v>0.745918321938052</v>
       </c>
       <c r="D292" t="s">
         <v>592</v>
@@ -8396,10 +8396,10 @@
         <v>594</v>
       </c>
       <c r="B293" t="n">
-        <v>1.21537053985315</v>
+        <v>1.15587465216924</v>
       </c>
       <c r="C293" t="n">
-        <v>1.02172193901377</v>
+        <v>0.872527856832504</v>
       </c>
       <c r="D293" t="s">
         <v>595</v>
@@ -8416,10 +8416,10 @@
         <v>597</v>
       </c>
       <c r="B294" t="n">
-        <v>0.929026695385129</v>
+        <v>0.8914838357771</v>
       </c>
       <c r="C294" t="n">
-        <v>0.923127386695279</v>
+        <v>0.991983377743166</v>
       </c>
       <c r="D294" t="s">
         <v>43</v>
@@ -8436,10 +8436,10 @@
         <v>598</v>
       </c>
       <c r="B295" t="n">
-        <v>1.16446496750328</v>
+        <v>1.07856181416287</v>
       </c>
       <c r="C295" t="n">
-        <v>1.32838042871647</v>
+        <v>0.630811440181013</v>
       </c>
       <c r="D295" t="s">
         <v>599</v>
@@ -8456,10 +8456,10 @@
         <v>598</v>
       </c>
       <c r="B296" t="n">
-        <v>1.16446496750328</v>
+        <v>1.07856181416287</v>
       </c>
       <c r="C296" t="n">
-        <v>1.32838042871647</v>
+        <v>0.630811440181013</v>
       </c>
       <c r="D296" t="s">
         <v>569</v>
@@ -8476,10 +8476,10 @@
         <v>601</v>
       </c>
       <c r="B297" t="n">
-        <v>0.918421367812239</v>
+        <v>0.862849451330298</v>
       </c>
       <c r="C297" t="n">
-        <v>0.816329963783435</v>
+        <v>0.93550747888244</v>
       </c>
       <c r="D297" t="s">
         <v>279</v>
@@ -8496,10 +8496,10 @@
         <v>602</v>
       </c>
       <c r="B298" t="n">
-        <v>1.10931726412425</v>
+        <v>1.03656471697423</v>
       </c>
       <c r="C298" t="n">
-        <v>1.1579480724973</v>
+        <v>0.72607820441754</v>
       </c>
       <c r="D298" t="s">
         <v>603</v>
@@ -8516,10 +8516,10 @@
         <v>605</v>
       </c>
       <c r="B299" t="n">
-        <v>0.935389891928862</v>
+        <v>0.870485287182778</v>
       </c>
       <c r="C299" t="n">
-        <v>1.34895472447138</v>
+        <v>0.634698554003312</v>
       </c>
       <c r="D299" t="s">
         <v>343</v>
@@ -8536,10 +8536,10 @@
         <v>606</v>
       </c>
       <c r="B300" t="n">
-        <v>1.1718886968043</v>
+        <v>1.09478796534939</v>
       </c>
       <c r="C300" t="n">
-        <v>1.09091736484806</v>
+        <v>0.758177119220383</v>
       </c>
       <c r="D300" t="s">
         <v>75</v>
@@ -8556,10 +8556,10 @@
         <v>607</v>
       </c>
       <c r="B301" t="n">
-        <v>0.79539956796672</v>
+        <v>0.761674626284931</v>
       </c>
       <c r="C301" t="n">
-        <v>0.6699404754225</v>
+        <v>1.23355069800751</v>
       </c>
       <c r="D301" t="s">
         <v>608</v>
@@ -8576,10 +8576,10 @@
         <v>610</v>
       </c>
       <c r="B302" t="n">
-        <v>0.820852354141655</v>
+        <v>0.75212983146933</v>
       </c>
       <c r="C302" t="n">
-        <v>1.57824050166817</v>
+        <v>0.531595046267442</v>
       </c>
       <c r="D302" t="s">
         <v>189</v>
@@ -8596,10 +8596,10 @@
         <v>611</v>
       </c>
       <c r="B303" t="n">
-        <v>0.74449399561685</v>
+        <v>0.691043144649486</v>
       </c>
       <c r="C303" t="n">
-        <v>1.22921521272735</v>
+        <v>0.673727801940819</v>
       </c>
       <c r="D303" t="s">
         <v>612</v>
@@ -8616,10 +8616,10 @@
         <v>614</v>
       </c>
       <c r="B304" t="n">
-        <v>1.00538505390993</v>
+        <v>0.933480932965742</v>
       </c>
       <c r="C304" t="n">
-        <v>0.903712786781843</v>
+        <v>0.812370789000049</v>
       </c>
       <c r="D304" t="s">
         <v>343</v>
@@ -8636,10 +8636,10 @@
         <v>615</v>
       </c>
       <c r="B305" t="n">
-        <v>0.872818459248814</v>
+        <v>0.824670272067895</v>
       </c>
       <c r="C305" t="n">
-        <v>0.925330894138975</v>
+        <v>0.908091173330377</v>
       </c>
       <c r="D305" t="s">
         <v>75</v>
@@ -8656,10 +8656,10 @@
         <v>615</v>
       </c>
       <c r="B306" t="n">
-        <v>0.872818459248814</v>
+        <v>0.824670272067895</v>
       </c>
       <c r="C306" t="n">
-        <v>0.925330894138975</v>
+        <v>0.908091173330377</v>
       </c>
       <c r="D306" t="s">
         <v>211</v>
@@ -8676,10 +8676,10 @@
         <v>616</v>
       </c>
       <c r="B307" t="n">
-        <v>1.12840685375545</v>
+        <v>1.04229159386359</v>
       </c>
       <c r="C307" t="n">
-        <v>1.25629676556959</v>
+        <v>0.648339210969694</v>
       </c>
       <c r="D307" t="s">
         <v>617</v>
@@ -8696,10 +8696,10 @@
         <v>619</v>
       </c>
       <c r="B308" t="n">
-        <v>0.799641698995875</v>
+        <v>0.763583585248051</v>
       </c>
       <c r="C308" t="n">
-        <v>1.20092089637588</v>
+        <v>0.778066198967647</v>
       </c>
       <c r="D308" t="s">
         <v>620</v>
@@ -8716,10 +8716,10 @@
         <v>619</v>
       </c>
       <c r="B309" t="n">
-        <v>0.799641698995875</v>
+        <v>0.763583585248051</v>
       </c>
       <c r="C309" t="n">
-        <v>1.20092089637588</v>
+        <v>0.778066198967647</v>
       </c>
       <c r="D309" t="s">
         <v>622</v>
@@ -8736,10 +8736,10 @@
         <v>624</v>
       </c>
       <c r="B310" t="n">
-        <v>0.620684371437344</v>
+        <v>0.570729782307197</v>
       </c>
       <c r="C310" t="n">
-        <v>1.10066640610311</v>
+        <v>0.697689839699978</v>
       </c>
       <c r="D310" t="s">
         <v>101</v>
@@ -8756,10 +8756,10 @@
         <v>625</v>
       </c>
       <c r="B311" t="n">
-        <v>1.11886205893985</v>
+        <v>1.04515503230827</v>
       </c>
       <c r="C311" t="n">
-        <v>1.23181865259339</v>
+        <v>0.693593220272634</v>
       </c>
       <c r="D311" t="s">
         <v>327</v>
@@ -8776,10 +8776,10 @@
         <v>626</v>
       </c>
       <c r="B312" t="n">
-        <v>0.973569071191265</v>
+        <v>0.914391343334541</v>
       </c>
       <c r="C312" t="n">
-        <v>1.1637933187501</v>
+        <v>0.74186858794887</v>
       </c>
       <c r="D312" t="s">
         <v>627</v>
@@ -8796,10 +8796,10 @@
         <v>629</v>
       </c>
       <c r="B313" t="n">
-        <v>0.869636860976947</v>
+        <v>0.811307559326054</v>
       </c>
       <c r="C313" t="n">
-        <v>1.251629045902</v>
+        <v>0.675846275986519</v>
       </c>
       <c r="D313" t="s">
         <v>569</v>
@@ -8816,10 +8816,10 @@
         <v>630</v>
       </c>
       <c r="B314" t="n">
-        <v>1.35323979830071</v>
+        <v>1.25609499773304</v>
       </c>
       <c r="C314" t="n">
-        <v>1.19451611992418</v>
+        <v>0.687667954306187</v>
       </c>
       <c r="D314" t="s">
         <v>631</v>
@@ -8836,10 +8836,10 @@
         <v>633</v>
       </c>
       <c r="B315" t="n">
-        <v>1.08598554346389</v>
+        <v>1.02511096319551</v>
       </c>
       <c r="C315" t="n">
-        <v>1.05875297009139</v>
+        <v>0.816725802608127</v>
       </c>
       <c r="D315" t="s">
         <v>634</v>
@@ -8856,10 +8856,10 @@
         <v>636</v>
       </c>
       <c r="B316" t="n">
-        <v>1.1050751330951</v>
+        <v>1.02701992215863</v>
       </c>
       <c r="C316" t="n">
-        <v>1.06301901015276</v>
+        <v>0.749071843391402</v>
       </c>
       <c r="D316" t="s">
         <v>156</v>
@@ -8876,10 +8876,10 @@
         <v>637</v>
       </c>
       <c r="B317" t="n">
-        <v>0.854789402374901</v>
+        <v>0.788400051768612</v>
       </c>
       <c r="C317" t="n">
-        <v>0.888481745846602</v>
+        <v>0.794721224515951</v>
       </c>
       <c r="D317" t="s">
         <v>185</v>
@@ -8896,10 +8896,10 @@
         <v>638</v>
       </c>
       <c r="B318" t="n">
-        <v>1.10931726412425</v>
+        <v>1.05183638867919</v>
       </c>
       <c r="C318" t="n">
-        <v>1.26028578762903</v>
+        <v>0.725811903186457</v>
       </c>
       <c r="D318" t="s">
         <v>450</v>
@@ -8916,10 +8916,10 @@
         <v>639</v>
       </c>
       <c r="B319" t="n">
-        <v>0.651167112975421</v>
+        <v>0.60132207338284</v>
       </c>
       <c r="C319" t="n">
-        <v>1.65787635168429</v>
+        <v>0.526251573887728</v>
       </c>
       <c r="D319" t="s">
         <v>43</v>
@@ -8936,10 +8936,10 @@
         <v>640</v>
       </c>
       <c r="B320" t="n">
-        <v>0.806004895539609</v>
+        <v>0.771219421100531</v>
       </c>
       <c r="C320" t="n">
-        <v>0.805171102264085</v>
+        <v>1.08539973012874</v>
       </c>
       <c r="D320" t="s">
         <v>599</v>
@@ -8956,10 +8956,10 @@
         <v>640</v>
       </c>
       <c r="B321" t="n">
-        <v>0.806004895539609</v>
+        <v>0.771219421100531</v>
       </c>
       <c r="C321" t="n">
-        <v>0.805171102264085</v>
+        <v>1.08539973012874</v>
       </c>
       <c r="D321" t="s">
         <v>641</v>
@@ -8976,10 +8976,10 @@
         <v>643</v>
       </c>
       <c r="B322" t="n">
-        <v>0.475118675265454</v>
+        <v>0.440969520480749</v>
       </c>
       <c r="C322" t="n">
-        <v>1.35134323276907</v>
+        <v>0.62825601311979</v>
       </c>
       <c r="D322" t="s">
         <v>644</v>
@@ -8996,10 +8996,10 @@
         <v>646</v>
       </c>
       <c r="B323" t="n">
-        <v>1.06689595383269</v>
+        <v>1.01747512734303</v>
       </c>
       <c r="C323" t="n">
-        <v>0.871600892057001</v>
+        <v>1.00067778890636</v>
       </c>
       <c r="D323" t="s">
         <v>433</v>
@@ -9016,10 +9016,10 @@
         <v>647</v>
       </c>
       <c r="B324" t="n">
-        <v>1.15173857441581</v>
+        <v>1.07665285519975</v>
       </c>
       <c r="C324" t="n">
-        <v>0.865047508496314</v>
+        <v>0.883475432088611</v>
       </c>
       <c r="D324" t="s">
         <v>648</v>
@@ -9036,10 +9036,10 @@
         <v>650</v>
       </c>
       <c r="B325" t="n">
-        <v>0.929026695385129</v>
+        <v>0.90484654851894</v>
       </c>
       <c r="C325" t="n">
-        <v>0.657829475341216</v>
+        <v>1.43781524586491</v>
       </c>
       <c r="D325" t="s">
         <v>491</v>
@@ -9056,10 +9056,10 @@
         <v>651</v>
       </c>
       <c r="B326" t="n">
-        <v>1.05841169177438</v>
+        <v>1.00793033252743</v>
       </c>
       <c r="C326" t="n">
-        <v>0.920715135657324</v>
+        <v>0.952508967035993</v>
       </c>
       <c r="D326" t="s">
         <v>652</v>
@@ -9076,10 +9076,10 @@
         <v>654</v>
       </c>
       <c r="B327" t="n">
-        <v>0.176048437709967</v>
+        <v>0.162261511865211</v>
       </c>
       <c r="C327" t="n">
-        <v>1.51497858774675</v>
+        <v>0.560660882028015</v>
       </c>
       <c r="D327" t="s">
         <v>652</v>
@@ -9096,10 +9096,10 @@
         <v>655</v>
       </c>
       <c r="B328" t="n">
-        <v>0.562082361363149</v>
+        <v>0.528781632784275</v>
       </c>
       <c r="C328" t="n">
-        <v>0.815899029745424</v>
+        <v>0.953991749747812</v>
       </c>
       <c r="D328" t="s">
         <v>652</v>
@@ -9116,10 +9116,10 @@
         <v>656</v>
       </c>
       <c r="B329" t="n">
-        <v>0.659651375033733</v>
+        <v>0.618502704050921</v>
       </c>
       <c r="C329" t="n">
-        <v>0.773158461227774</v>
+        <v>0.925512992702761</v>
       </c>
       <c r="D329" t="s">
         <v>652</v>
@@ -9136,10 +9136,10 @@
         <v>657</v>
       </c>
       <c r="B330" t="n">
-        <v>0.829336616199966</v>
+        <v>0.763583585248051</v>
       </c>
       <c r="C330" t="n">
-        <v>1.07735821093618</v>
+        <v>0.704243178338893</v>
       </c>
       <c r="D330" t="s">
         <v>253</v>
@@ -9156,10 +9156,10 @@
         <v>658</v>
       </c>
       <c r="B331" t="n">
-        <v>1.19309935195008</v>
+        <v>1.12437682927775</v>
       </c>
       <c r="C331" t="n">
-        <v>0.923646291937683</v>
+        <v>0.892738834618782</v>
       </c>
       <c r="D331" t="s">
         <v>659</v>
@@ -9176,10 +9176,10 @@
         <v>661</v>
       </c>
       <c r="B332" t="n">
-        <v>0.670256702606623</v>
+        <v>0.614684786124681</v>
       </c>
       <c r="C332" t="n">
-        <v>1.76928099966577</v>
+        <v>0.487976092494056</v>
       </c>
       <c r="D332" t="s">
         <v>415</v>
@@ -9196,10 +9196,10 @@
         <v>662</v>
       </c>
       <c r="B333" t="n">
-        <v>0.801762764510453</v>
+        <v>0.736858159764369</v>
       </c>
       <c r="C333" t="n">
-        <v>1.41712540007652</v>
+        <v>0.582080421111257</v>
       </c>
       <c r="D333" t="s">
         <v>663</v>
@@ -9216,10 +9216,10 @@
         <v>665</v>
       </c>
       <c r="B334" t="n">
-        <v>1.09871193655136</v>
+        <v>1.01556616837991</v>
       </c>
       <c r="C334" t="n">
-        <v>1.39275483831496</v>
+        <v>0.599524230093244</v>
       </c>
       <c r="D334" t="s">
         <v>43</v>
@@ -9236,10 +9236,10 @@
         <v>666</v>
       </c>
       <c r="B335" t="n">
-        <v>0.865394729947791</v>
+        <v>0.830397148957255</v>
       </c>
       <c r="C335" t="n">
-        <v>0.744971807351901</v>
+        <v>1.17212201106126</v>
       </c>
       <c r="D335" t="s">
         <v>276</v>
@@ -9256,10 +9256,10 @@
         <v>667</v>
       </c>
       <c r="B336" t="n">
-        <v>1.11780152618256</v>
+        <v>1.06901701934727</v>
       </c>
       <c r="C336" t="n">
-        <v>0.881414523013331</v>
+        <v>1.00823280197116</v>
       </c>
       <c r="D336" t="s">
         <v>668</v>
@@ -9276,10 +9276,10 @@
         <v>667</v>
       </c>
       <c r="B337" t="n">
-        <v>1.11780152618256</v>
+        <v>1.06901701934727</v>
       </c>
       <c r="C337" t="n">
-        <v>0.881414523013331</v>
+        <v>1.00823280197116</v>
       </c>
       <c r="D337" t="s">
         <v>355</v>
@@ -9296,10 +9296,10 @@
         <v>670</v>
       </c>
       <c r="B338" t="n">
-        <v>1.26309451393115</v>
+        <v>1.18260007765292</v>
       </c>
       <c r="C338" t="n">
-        <v>0.900743017938483</v>
+        <v>0.864476851587946</v>
       </c>
       <c r="D338" t="s">
         <v>671</v>
@@ -9316,10 +9316,10 @@
         <v>673</v>
       </c>
       <c r="B339" t="n">
-        <v>0.856910467889479</v>
+        <v>0.806535161918254</v>
       </c>
       <c r="C339" t="n">
-        <v>1.05255626038628</v>
+        <v>0.808754794010101</v>
       </c>
       <c r="D339" t="s">
         <v>674</v>
@@ -9336,10 +9336,10 @@
         <v>676</v>
       </c>
       <c r="B340" t="n">
-        <v>1.13052791927003</v>
+        <v>1.02701992215863</v>
       </c>
       <c r="C340" t="n">
-        <v>1.20824043415544</v>
+        <v>0.613378592852399</v>
       </c>
       <c r="D340" t="s">
         <v>677</v>
@@ -9356,10 +9356,10 @@
         <v>676</v>
       </c>
       <c r="B341" t="n">
-        <v>1.13052791927003</v>
+        <v>1.02701992215863</v>
       </c>
       <c r="C341" t="n">
-        <v>1.20824043415544</v>
+        <v>0.613378592852399</v>
       </c>
       <c r="D341" t="s">
         <v>679</v>
@@ -9376,10 +9376,10 @@
         <v>681</v>
       </c>
       <c r="B342" t="n">
-        <v>1.09765140379407</v>
+        <v>1.02797440164019</v>
       </c>
       <c r="C342" t="n">
-        <v>1.04872685557959</v>
+        <v>0.787414123926961</v>
       </c>
       <c r="D342" t="s">
         <v>547</v>
@@ -9396,10 +9396,10 @@
         <v>682</v>
       </c>
       <c r="B343" t="n">
-        <v>0.287466761505149</v>
+        <v>0.264240109105576</v>
       </c>
       <c r="C343" t="n">
-        <v>2.62075747739679</v>
+        <v>0.353373204401041</v>
       </c>
       <c r="D343" t="s">
         <v>683</v>
@@ -9416,10 +9416,10 @@
         <v>685</v>
       </c>
       <c r="B344" t="n">
-        <v>1.35005820002885</v>
+        <v>1.28568386166141</v>
       </c>
       <c r="C344" t="n">
-        <v>0.629818431715508</v>
+        <v>1.23723867956945</v>
       </c>
       <c r="D344" t="s">
         <v>377</v>
@@ -9436,10 +9436,10 @@
         <v>686</v>
       </c>
       <c r="B345" t="n">
-        <v>1.11143832963883</v>
+        <v>1.08047077312599</v>
       </c>
       <c r="C345" t="n">
-        <v>0.480474110343529</v>
+        <v>1.74349304123258</v>
       </c>
       <c r="D345" t="s">
         <v>565</v>
@@ -9456,10 +9456,10 @@
         <v>687</v>
       </c>
       <c r="B346" t="n">
-        <v>1.12455037100167</v>
+        <v>1.05374534764231</v>
       </c>
       <c r="C346" t="n">
-        <v>0.872389702533445</v>
+        <v>0.921412493444545</v>
       </c>
       <c r="D346" t="s">
         <v>688</v>
@@ -9476,10 +9476,10 @@
         <v>690</v>
       </c>
       <c r="B347" t="n">
-        <v>0.963156567756064</v>
+        <v>0.914773135127165</v>
       </c>
       <c r="C347" t="n">
-        <v>1.13514182271285</v>
+        <v>0.816811013762477</v>
       </c>
       <c r="D347" t="s">
         <v>691</v>
@@ -9496,10 +9496,10 @@
         <v>693</v>
       </c>
       <c r="B348" t="n">
-        <v>0.937125309168063</v>
+        <v>0.87353962152377</v>
       </c>
       <c r="C348" t="n">
-        <v>1.17781553157866</v>
+        <v>0.723893939306947</v>
       </c>
       <c r="D348" t="s">
         <v>694</v>
@@ -9516,10 +9516,10 @@
         <v>696</v>
       </c>
       <c r="B349" t="n">
-        <v>1.03257325732407</v>
+        <v>0.957533815901056</v>
       </c>
       <c r="C349" t="n">
-        <v>1.53747693027181</v>
+        <v>0.581888130721356</v>
       </c>
       <c r="D349" t="s">
         <v>697</v>
@@ -9536,10 +9536,10 @@
         <v>699</v>
       </c>
       <c r="B350" t="n">
-        <v>1.15937441026829</v>
+        <v>1.04543576156755</v>
       </c>
       <c r="C350" t="n">
-        <v>1.89621022236702</v>
+        <v>0.451030712712832</v>
       </c>
       <c r="D350" t="s">
         <v>700</v>
@@ -9556,10 +9556,10 @@
         <v>702</v>
       </c>
       <c r="B351" t="n">
-        <v>1.39180462583849</v>
+        <v>1.28892909189871</v>
       </c>
       <c r="C351" t="n">
-        <v>1.18883769522518</v>
+        <v>0.705781540735103</v>
       </c>
       <c r="D351" t="s">
         <v>703</v>
@@ -9576,10 +9576,10 @@
         <v>705</v>
       </c>
       <c r="B352" t="n">
-        <v>1.26859000185528</v>
+        <v>1.16522855108853</v>
       </c>
       <c r="C352" t="n">
-        <v>1.11264798983701</v>
+        <v>0.709134196173487</v>
       </c>
       <c r="D352" t="s">
         <v>706</v>
@@ -9596,10 +9596,10 @@
         <v>708</v>
       </c>
       <c r="B353" t="n">
-        <v>0.320705105804181</v>
+        <v>0.293813683888924</v>
       </c>
       <c r="C353" t="n">
-        <v>3.03109385258919</v>
+        <v>0.31456963710387</v>
       </c>
       <c r="D353" t="s">
         <v>709</v>
@@ -9616,10 +9616,10 @@
         <v>711</v>
       </c>
       <c r="B354" t="n">
-        <v>1.02023251251198</v>
+        <v>0.958297399486304</v>
       </c>
       <c r="C354" t="n">
-        <v>1.08165115071224</v>
+        <v>0.780833972450944</v>
       </c>
       <c r="D354" t="s">
         <v>712</v>
@@ -9636,10 +9636,10 @@
         <v>714</v>
       </c>
       <c r="B355" t="n">
-        <v>1.08386447794932</v>
+        <v>0.994567619785586</v>
       </c>
       <c r="C355" t="n">
-        <v>1.34293212920452</v>
+        <v>0.600910115095261</v>
       </c>
       <c r="D355" t="s">
         <v>715</v>
@@ -9656,10 +9656,10 @@
         <v>717</v>
       </c>
       <c r="B356" t="n">
-        <v>0.372701511847263</v>
+        <v>0.345203412497556</v>
       </c>
       <c r="C356" t="n">
-        <v>1.52300260906789</v>
+        <v>0.590405625001366</v>
       </c>
       <c r="D356" t="s">
         <v>178</v>
@@ -9676,10 +9676,10 @@
         <v>718</v>
       </c>
       <c r="B357" t="n">
-        <v>0.753304575446635</v>
+        <v>0.713555695180075</v>
       </c>
       <c r="C357" t="n">
-        <v>1.01578263576304</v>
+        <v>0.864313062569099</v>
       </c>
       <c r="D357" t="s">
         <v>652</v>
@@ -9696,10 +9696,10 @@
         <v>719</v>
       </c>
       <c r="B358" t="n">
-        <v>0.128854730010609</v>
+        <v>0.118779668816363</v>
       </c>
       <c r="C358" t="n">
-        <v>2.32908066286568</v>
+        <v>0.397919366464278</v>
       </c>
       <c r="D358" t="s">
         <v>151</v>
@@ -9716,10 +9716,10 @@
         <v>719</v>
       </c>
       <c r="B359" t="n">
-        <v>0.128854730010609</v>
+        <v>0.118779668816363</v>
       </c>
       <c r="C359" t="n">
-        <v>2.32908066286568</v>
+        <v>0.397919366464278</v>
       </c>
       <c r="D359" t="s">
         <v>153</v>
@@ -9736,10 +9736,10 @@
         <v>720</v>
       </c>
       <c r="B360" t="n">
-        <v>0.492693218100528</v>
+        <v>0.450196155469163</v>
       </c>
       <c r="C360" t="n">
-        <v>2.13697913165796</v>
+        <v>0.427059076961884</v>
       </c>
       <c r="D360" t="s">
         <v>706</v>
@@ -9756,10 +9756,10 @@
         <v>721</v>
       </c>
       <c r="B361" t="n">
-        <v>0.977811202220421</v>
+        <v>0.931571974002622</v>
       </c>
       <c r="C361" t="n">
-        <v>1.38687154820403</v>
+        <v>0.680231117746813</v>
       </c>
       <c r="D361" t="s">
         <v>722</v>
@@ -9776,10 +9776,10 @@
         <v>724</v>
       </c>
       <c r="B362" t="n">
-        <v>1.08598554346389</v>
+        <v>1.02129304526927</v>
       </c>
       <c r="C362" t="n">
-        <v>1.26300494411729</v>
+        <v>0.698661864837192</v>
       </c>
       <c r="D362" t="s">
         <v>725</v>
@@ -9796,10 +9796,10 @@
         <v>727</v>
       </c>
       <c r="B363" t="n">
-        <v>0.908876572996638</v>
+        <v>0.845668820662216</v>
       </c>
       <c r="C363" t="n">
-        <v>1.05900996597548</v>
+        <v>0.753536146808781</v>
       </c>
       <c r="D363" t="s">
         <v>528</v>
@@ -9816,10 +9816,10 @@
         <v>728</v>
       </c>
       <c r="B364" t="n">
-        <v>0.730707069772093</v>
+        <v>0.675771472944525</v>
       </c>
       <c r="C364" t="n">
-        <v>1.09021504765775</v>
+        <v>0.71524364116792</v>
       </c>
       <c r="D364" t="s">
         <v>729</v>
@@ -9836,10 +9836,10 @@
         <v>731</v>
       </c>
       <c r="B365" t="n">
-        <v>0.26232790912554</v>
+        <v>0.236710911426896</v>
       </c>
       <c r="C365" t="n">
-        <v>3.16154796749401</v>
+        <v>0.290187802494818</v>
       </c>
       <c r="D365" t="s">
         <v>151</v>
@@ -9856,10 +9856,10 @@
         <v>731</v>
       </c>
       <c r="B366" t="n">
-        <v>0.26232790912554</v>
+        <v>0.236710911426896</v>
       </c>
       <c r="C366" t="n">
-        <v>3.16154796749401</v>
+        <v>0.290187802494818</v>
       </c>
       <c r="D366" t="s">
         <v>153</v>
@@ -9876,10 +9876,10 @@
         <v>732</v>
       </c>
       <c r="B367" t="n">
-        <v>0.221439239721935</v>
+        <v>0.20264333608506</v>
       </c>
       <c r="C367" t="n">
-        <v>1.96050152461274</v>
+        <v>0.448586962664169</v>
       </c>
       <c r="D367" t="s">
         <v>151</v>
@@ -9896,10 +9896,10 @@
         <v>732</v>
       </c>
       <c r="B368" t="n">
-        <v>0.221439239721935</v>
+        <v>0.20264333608506</v>
       </c>
       <c r="C368" t="n">
-        <v>1.96050152461274</v>
+        <v>0.448586962664169</v>
       </c>
       <c r="D368" t="s">
         <v>153</v>
@@ -9916,10 +9916,10 @@
         <v>733</v>
       </c>
       <c r="B369" t="n">
-        <v>0.203985900630551</v>
+        <v>0.18698008305433</v>
       </c>
       <c r="C369" t="n">
-        <v>2.15052925659234</v>
+        <v>0.416863783143874</v>
       </c>
       <c r="D369" t="s">
         <v>151</v>
@@ -9936,10 +9936,10 @@
         <v>733</v>
       </c>
       <c r="B370" t="n">
-        <v>0.203985900630551</v>
+        <v>0.18698008305433</v>
       </c>
       <c r="C370" t="n">
-        <v>2.15052925659234</v>
+        <v>0.416863783143874</v>
       </c>
       <c r="D370" t="s">
         <v>153</v>
@@ -9956,10 +9956,10 @@
         <v>734</v>
       </c>
       <c r="B371" t="n">
-        <v>1.28536570183422</v>
+        <v>1.19882622883944</v>
       </c>
       <c r="C371" t="n">
-        <v>0.693619921446683</v>
+        <v>0.975433880164265</v>
       </c>
       <c r="D371" t="s">
         <v>735</v>

--- a/data/lifes_set_alpha_complex.xlsx
+++ b/data/lifes_set_alpha_complex.xlsx
@@ -2579,7 +2579,7 @@
         <v>1.22746435879107</v>
       </c>
       <c r="C2" t="n">
-        <v>0.820663549388168</v>
+        <v>0.996164461299997</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -2599,7 +2599,7 @@
         <v>0.535839457157883</v>
       </c>
       <c r="C3" t="n">
-        <v>0.714697055946145</v>
+        <v>0.867536773456153</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2619,7 +2619,7 @@
         <v>0.535839457157883</v>
       </c>
       <c r="C4" t="n">
-        <v>0.714697055946145</v>
+        <v>0.867536773456153</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -2639,7 +2639,7 @@
         <v>1.42885578389542</v>
       </c>
       <c r="C5" t="n">
-        <v>0.904442101072587</v>
+        <v>1.09785926164714</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -2659,7 +2659,7 @@
         <v>1.42885578389542</v>
       </c>
       <c r="C6" t="n">
-        <v>0.904442101072587</v>
+        <v>1.09785926164714</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -2679,7 +2679,7 @@
         <v>1.56508066305522</v>
       </c>
       <c r="C7" t="n">
-        <v>0.775066681830786</v>
+        <v>0.940816591833721</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -2699,7 +2699,7 @@
         <v>0.980853256708434</v>
       </c>
       <c r="C8" t="n">
-        <v>0.699124118169029</v>
+        <v>0.848633524757993</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -2719,7 +2719,7 @@
         <v>0.943546576301525</v>
       </c>
       <c r="C9" t="n">
-        <v>0.687834070678328</v>
+        <v>0.8349290729336</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -2739,7 +2739,7 @@
         <v>0.540235386562996</v>
       </c>
       <c r="C10" t="n">
-        <v>0.726482167349337</v>
+        <v>0.881842159824383</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -2759,7 +2759,7 @@
         <v>0.56021582371032</v>
       </c>
       <c r="C11" t="n">
-        <v>0.698186022940451</v>
+        <v>0.847494815565022</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -2779,7 +2779,7 @@
         <v>1.34092436165669</v>
       </c>
       <c r="C12" t="n">
-        <v>0.809431173347896</v>
+        <v>0.982530014107091</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
@@ -2799,7 +2799,7 @@
         <v>1.16344231091589</v>
       </c>
       <c r="C13" t="n">
-        <v>0.770456998817388</v>
+        <v>0.935221116807166</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
@@ -2819,7 +2819,7 @@
         <v>1.27396285362785</v>
       </c>
       <c r="C14" t="n">
-        <v>0.759994651269169</v>
+        <v>0.92252137058708</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -2839,7 +2839,7 @@
         <v>1.12885619977111</v>
       </c>
       <c r="C15" t="n">
-        <v>0.821371899526395</v>
+        <v>0.997024293851821</v>
       </c>
       <c r="D15" t="s">
         <v>38</v>
@@ -2859,7 +2859,7 @@
         <v>1.12885619977111</v>
       </c>
       <c r="C16" t="n">
-        <v>0.821371899526395</v>
+        <v>0.997024293851821</v>
       </c>
       <c r="D16" t="s">
         <v>40</v>
@@ -2879,7 +2879,7 @@
         <v>0.794674646841484</v>
       </c>
       <c r="C17" t="n">
-        <v>0.570075654280597</v>
+        <v>0.691987730501806</v>
       </c>
       <c r="D17" t="s">
         <v>43</v>
@@ -2899,7 +2899,7 @@
         <v>1.40457171547763</v>
       </c>
       <c r="C18" t="n">
-        <v>0.748777585026487</v>
+        <v>0.908905507229511</v>
       </c>
       <c r="D18" t="s">
         <v>46</v>
@@ -2919,7 +2919,7 @@
         <v>1.43362818130322</v>
       </c>
       <c r="C19" t="n">
-        <v>0.858898391246712</v>
+        <v>1.04257591782357</v>
       </c>
       <c r="D19" t="s">
         <v>49</v>
@@ -2939,7 +2939,7 @@
         <v>1.27777531738562</v>
       </c>
       <c r="C20" t="n">
-        <v>0.841064495487627</v>
+        <v>1.0209281997362</v>
       </c>
       <c r="D20" t="s">
         <v>34</v>
@@ -2959,7 +2959,7 @@
         <v>0.910573425408301</v>
       </c>
       <c r="C21" t="n">
-        <v>0.647896211516558</v>
+        <v>0.786450404681525</v>
       </c>
       <c r="D21" t="s">
         <v>43</v>
@@ -2979,7 +2979,7 @@
         <v>0.10064143945273</v>
       </c>
       <c r="C22" t="n">
-        <v>0.381739707280289</v>
+        <v>0.463375679525667</v>
       </c>
       <c r="D22" t="s">
         <v>54</v>
@@ -2999,7 +2999,7 @@
         <v>0.10064143945273</v>
       </c>
       <c r="C23" t="n">
-        <v>0.381739707280289</v>
+        <v>0.463375679525667</v>
       </c>
       <c r="D23" t="s">
         <v>56</v>
@@ -3019,7 +3019,7 @@
         <v>1.22532104183093</v>
       </c>
       <c r="C24" t="n">
-        <v>0.783822517267758</v>
+        <v>0.951444884144018</v>
       </c>
       <c r="D24" t="s">
         <v>59</v>
@@ -3039,7 +3039,7 @@
         <v>0.827772330382965</v>
       </c>
       <c r="C25" t="n">
-        <v>0.898045246475783</v>
+        <v>1.09009442401277</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
@@ -3059,7 +3059,7 @@
         <v>1.11281078379532</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6701015539932</v>
+        <v>0.813404414083693</v>
       </c>
       <c r="D26" t="s">
         <v>63</v>
@@ -3079,7 +3079,7 @@
         <v>1.11281078379532</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6701015539932</v>
+        <v>0.813404414083693</v>
       </c>
       <c r="D27" t="s">
         <v>65</v>
@@ -3099,7 +3099,7 @@
         <v>1.11281078379532</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6701015539932</v>
+        <v>0.813404414083693</v>
       </c>
       <c r="D28" t="s">
         <v>67</v>
@@ -3119,7 +3119,7 @@
         <v>1.2594356759185</v>
       </c>
       <c r="C29" t="n">
-        <v>0.768659252237392</v>
+        <v>0.933038917713823</v>
       </c>
       <c r="D29" t="s">
         <v>70</v>
@@ -3139,7 +3139,7 @@
         <v>1.2594356759185</v>
       </c>
       <c r="C30" t="n">
-        <v>0.768659252237392</v>
+        <v>0.933038917713823</v>
       </c>
       <c r="D30" t="s">
         <v>72</v>
@@ -3159,7 +3159,7 @@
         <v>1.25397393221847</v>
       </c>
       <c r="C31" t="n">
-        <v>0.863034961828438</v>
+        <v>1.04759710416509</v>
       </c>
       <c r="D31" t="s">
         <v>75</v>
@@ -3179,7 +3179,7 @@
         <v>0.967842194301905</v>
       </c>
       <c r="C32" t="n">
-        <v>0.578445589354269</v>
+        <v>0.702147596710066</v>
       </c>
       <c r="D32" t="s">
         <v>78</v>
@@ -3199,7 +3199,7 @@
         <v>1.12119523100589</v>
       </c>
       <c r="C33" t="n">
-        <v>0.697935559536595</v>
+        <v>0.847190789948235</v>
       </c>
       <c r="D33" t="s">
         <v>81</v>
@@ -3219,7 +3219,7 @@
         <v>1.39621258562606</v>
       </c>
       <c r="C34" t="n">
-        <v>0.854454859150993</v>
+        <v>1.03718212549576</v>
       </c>
       <c r="D34" t="s">
         <v>84</v>
@@ -3239,7 +3239,7 @@
         <v>1.15072046296881</v>
       </c>
       <c r="C35" t="n">
-        <v>0.738201162282992</v>
+        <v>0.896067290553981</v>
       </c>
       <c r="D35" t="s">
         <v>87</v>
@@ -3259,7 +3259,7 @@
         <v>1.27412405460696</v>
       </c>
       <c r="C36" t="n">
-        <v>0.814205940963254</v>
+        <v>0.988325877482443</v>
       </c>
       <c r="D36" t="s">
         <v>75</v>
@@ -3279,7 +3279,7 @@
         <v>0.972750945921356</v>
       </c>
       <c r="C37" t="n">
-        <v>0.877459087487792</v>
+        <v>1.06510586445777</v>
       </c>
       <c r="D37" t="s">
         <v>91</v>
@@ -3299,7 +3299,7 @@
         <v>1.08619765001535</v>
       </c>
       <c r="C38" t="n">
-        <v>0.773662116267202</v>
+        <v>0.939111656481041</v>
       </c>
       <c r="D38" t="s">
         <v>70</v>
@@ -3319,7 +3319,7 @@
         <v>1.08619765001535</v>
       </c>
       <c r="C39" t="n">
-        <v>0.773662116267202</v>
+        <v>0.939111656481041</v>
       </c>
       <c r="D39" t="s">
         <v>94</v>
@@ -3339,7 +3339,7 @@
         <v>1.08094801286677</v>
       </c>
       <c r="C40" t="n">
-        <v>1.0128207135597</v>
+        <v>1.22941490610723</v>
       </c>
       <c r="D40" t="s">
         <v>97</v>
@@ -3359,7 +3359,7 @@
         <v>1.08094801286677</v>
       </c>
       <c r="C41" t="n">
-        <v>1.0128207135597</v>
+        <v>1.22941490610723</v>
       </c>
       <c r="D41" t="s">
         <v>99</v>
@@ -3379,7 +3379,7 @@
         <v>1.08094801286677</v>
       </c>
       <c r="C42" t="n">
-        <v>1.0128207135597</v>
+        <v>1.22941490610723</v>
       </c>
       <c r="D42" t="s">
         <v>101</v>
@@ -3399,7 +3399,7 @@
         <v>1.09192452690471</v>
       </c>
       <c r="C43" t="n">
-        <v>0.850325551099107</v>
+        <v>1.03216975479389</v>
       </c>
       <c r="D43" t="s">
         <v>104</v>
@@ -3419,7 +3419,7 @@
         <v>1.02079068764739</v>
       </c>
       <c r="C44" t="n">
-        <v>0.806345056105908</v>
+        <v>0.978783923127217</v>
       </c>
       <c r="D44" t="s">
         <v>107</v>
@@ -3439,7 +3439,7 @@
         <v>0.875257684590578</v>
       </c>
       <c r="C45" t="n">
-        <v>0.811883233436013</v>
+        <v>0.985506453256331</v>
       </c>
       <c r="D45" t="s">
         <v>110</v>
@@ -3459,7 +3459,7 @@
         <v>1.10185111351294</v>
       </c>
       <c r="C46" t="n">
-        <v>0.839075571607877</v>
+        <v>1.01851393960888</v>
       </c>
       <c r="D46" t="s">
         <v>72</v>
@@ -3479,7 +3479,7 @@
         <v>1.10185111351294</v>
       </c>
       <c r="C47" t="n">
-        <v>0.839075571607877</v>
+        <v>1.01851393960888</v>
       </c>
       <c r="D47" t="s">
         <v>113</v>
@@ -3499,7 +3499,7 @@
         <v>1.14776157657598</v>
       </c>
       <c r="C48" t="n">
-        <v>0.881869874901747</v>
+        <v>1.07045990957334</v>
       </c>
       <c r="D48" t="s">
         <v>63</v>
@@ -3519,7 +3519,7 @@
         <v>1.0488331220302</v>
       </c>
       <c r="C49" t="n">
-        <v>0.56844123277775</v>
+        <v>0.690003783953753</v>
       </c>
       <c r="D49" t="s">
         <v>117</v>
@@ -3539,7 +3539,7 @@
         <v>1.12843336707439</v>
       </c>
       <c r="C50" t="n">
-        <v>0.776833979053902</v>
+        <v>0.94296182990057</v>
       </c>
       <c r="D50" t="s">
         <v>120</v>
@@ -3559,7 +3559,7 @@
         <v>1.12843336707439</v>
       </c>
       <c r="C51" t="n">
-        <v>0.776833979053902</v>
+        <v>0.94296182990057</v>
       </c>
       <c r="D51" t="s">
         <v>122</v>
@@ -3579,7 +3579,7 @@
         <v>1.12843336707439</v>
       </c>
       <c r="C52" t="n">
-        <v>0.776833979053902</v>
+        <v>0.94296182990057</v>
       </c>
       <c r="D52" t="s">
         <v>124</v>
@@ -3599,7 +3599,7 @@
         <v>1.29618313595857</v>
       </c>
       <c r="C53" t="n">
-        <v>0.780172497804118</v>
+        <v>0.947014299069974</v>
       </c>
       <c r="D53" t="s">
         <v>127</v>
@@ -3619,7 +3619,7 @@
         <v>1.29618313595857</v>
       </c>
       <c r="C54" t="n">
-        <v>0.780172497804118</v>
+        <v>0.947014299069974</v>
       </c>
       <c r="D54" t="s">
         <v>129</v>
@@ -3639,7 +3639,7 @@
         <v>1.29618313595857</v>
       </c>
       <c r="C55" t="n">
-        <v>0.780172497804118</v>
+        <v>0.947014299069974</v>
       </c>
       <c r="D55" t="s">
         <v>131</v>
@@ -3659,7 +3659,7 @@
         <v>1.17381886642257</v>
       </c>
       <c r="C56" t="n">
-        <v>0.903972046066545</v>
+        <v>1.0972886842257</v>
       </c>
       <c r="D56" t="s">
         <v>20</v>
@@ -3679,7 +3679,7 @@
         <v>0.942707567954156</v>
       </c>
       <c r="C57" t="n">
-        <v>0.654638725845482</v>
+        <v>0.794634822229115</v>
       </c>
       <c r="D57" t="s">
         <v>135</v>
@@ -3699,7 +3699,7 @@
         <v>1.14403910659789</v>
       </c>
       <c r="C58" t="n">
-        <v>0.831646615348979</v>
+        <v>1.00949628284176</v>
       </c>
       <c r="D58" t="s">
         <v>138</v>
@@ -3719,7 +3719,7 @@
         <v>1.45157239555654</v>
       </c>
       <c r="C59" t="n">
-        <v>0.831813658801912</v>
+        <v>1.00969904894661</v>
       </c>
       <c r="D59" t="s">
         <v>141</v>
@@ -3739,7 +3739,7 @@
         <v>0.919640980483121</v>
       </c>
       <c r="C60" t="n">
-        <v>0.787329414155017</v>
+        <v>0.955701739527854</v>
       </c>
       <c r="D60" t="s">
         <v>12</v>
@@ -3759,7 +3759,7 @@
         <v>1.09459706945308</v>
       </c>
       <c r="C61" t="n">
-        <v>0.699925641761686</v>
+        <v>0.849606456135893</v>
       </c>
       <c r="D61" t="s">
         <v>145</v>
@@ -3779,7 +3779,7 @@
         <v>0.535228871546511</v>
       </c>
       <c r="C62" t="n">
-        <v>0.264012867376024</v>
+        <v>0.320472666297876</v>
       </c>
       <c r="D62" t="s">
         <v>148</v>
@@ -3799,7 +3799,7 @@
         <v>0.192929107041963</v>
       </c>
       <c r="C63" t="n">
-        <v>0.312603381016393</v>
+        <v>0.379454380400976</v>
       </c>
       <c r="D63" t="s">
         <v>151</v>
@@ -3819,7 +3819,7 @@
         <v>0.192929107041963</v>
       </c>
       <c r="C64" t="n">
-        <v>0.312603381016393</v>
+        <v>0.379454380400976</v>
       </c>
       <c r="D64" t="s">
         <v>153</v>
@@ -3839,7 +3839,7 @@
         <v>1.28568386166141</v>
       </c>
       <c r="C65" t="n">
-        <v>1.18480967898827</v>
+        <v>1.43818413342752</v>
       </c>
       <c r="D65" t="s">
         <v>156</v>
@@ -3859,7 +3859,7 @@
         <v>1.07283493727351</v>
       </c>
       <c r="C66" t="n">
-        <v>0.904683370302212</v>
+        <v>1.09815212689299</v>
       </c>
       <c r="D66" t="s">
         <v>117</v>
@@ -3879,7 +3879,7 @@
         <v>1.04437409455063</v>
       </c>
       <c r="C67" t="n">
-        <v>0.70474196069524</v>
+        <v>0.855452756680701</v>
       </c>
       <c r="D67" t="s">
         <v>160</v>
@@ -3899,7 +3899,7 @@
         <v>0.989317982637006</v>
       </c>
       <c r="C68" t="n">
-        <v>0.907221387344872</v>
+        <v>1.10123290510223</v>
       </c>
       <c r="D68" t="s">
         <v>163</v>
@@ -3919,7 +3919,7 @@
         <v>1.13837586167397</v>
       </c>
       <c r="C69" t="n">
-        <v>0.894228732805373</v>
+        <v>1.08546173953768</v>
       </c>
       <c r="D69" t="s">
         <v>94</v>
@@ -3939,7 +3939,7 @@
         <v>1.13837586167397</v>
       </c>
       <c r="C70" t="n">
-        <v>0.894228732805373</v>
+        <v>1.08546173953768</v>
       </c>
       <c r="D70" t="s">
         <v>113</v>
@@ -3959,7 +3959,7 @@
         <v>0.850850280704971</v>
       </c>
       <c r="C71" t="n">
-        <v>0.73151819340975</v>
+        <v>0.887955152403747</v>
       </c>
       <c r="D71" t="s">
         <v>23</v>
@@ -3979,7 +3979,7 @@
         <v>0.931571974002622</v>
       </c>
       <c r="C72" t="n">
-        <v>1.05111778894385</v>
+        <v>1.27590190494842</v>
       </c>
       <c r="D72" t="s">
         <v>168</v>
@@ -3999,7 +3999,7 @@
         <v>1.11419571480778</v>
       </c>
       <c r="C73" t="n">
-        <v>0.869918344624026</v>
+        <v>1.05595251524628</v>
       </c>
       <c r="D73" t="s">
         <v>171</v>
@@ -4019,7 +4019,7 @@
         <v>1.17019184439264</v>
       </c>
       <c r="C74" t="n">
-        <v>0.868112339150522</v>
+        <v>1.05376029107481</v>
       </c>
       <c r="D74" t="s">
         <v>174</v>
@@ -4039,7 +4039,7 @@
         <v>0.990272462118566</v>
       </c>
       <c r="C75" t="n">
-        <v>0.82645917058894</v>
+        <v>1.00319949030265</v>
       </c>
       <c r="D75" t="s">
         <v>141</v>
@@ -4059,7 +4059,7 @@
         <v>0.990272462118566</v>
       </c>
       <c r="C76" t="n">
-        <v>0.82645917058894</v>
+        <v>1.00319949030265</v>
       </c>
       <c r="D76" t="s">
         <v>87</v>
@@ -4079,7 +4079,7 @@
         <v>0.990272462118566</v>
       </c>
       <c r="C77" t="n">
-        <v>0.82645917058894</v>
+        <v>1.00319949030265</v>
       </c>
       <c r="D77" t="s">
         <v>104</v>
@@ -4099,7 +4099,7 @@
         <v>0.18402364404478</v>
       </c>
       <c r="C78" t="n">
-        <v>0.37701559998376</v>
+        <v>0.45764131030252</v>
       </c>
       <c r="D78" t="s">
         <v>178</v>
@@ -4119,7 +4119,7 @@
         <v>1.02472917140288</v>
       </c>
       <c r="C79" t="n">
-        <v>0.696797146101876</v>
+        <v>0.845808924009655</v>
       </c>
       <c r="D79" t="s">
         <v>181</v>
@@ -4139,7 +4139,7 @@
         <v>1.02472917140288</v>
       </c>
       <c r="C80" t="n">
-        <v>0.696797146101876</v>
+        <v>0.845808924009655</v>
       </c>
       <c r="D80" t="s">
         <v>20</v>
@@ -4159,7 +4159,7 @@
         <v>1.09240176664549</v>
       </c>
       <c r="C81" t="n">
-        <v>0.786056374265192</v>
+        <v>0.954156456936704</v>
       </c>
       <c r="D81" t="s">
         <v>78</v>
@@ -4179,7 +4179,7 @@
         <v>1.2188702979522</v>
       </c>
       <c r="C82" t="n">
-        <v>0.777134498142927</v>
+        <v>0.943326615733513</v>
       </c>
       <c r="D82" t="s">
         <v>185</v>
@@ -4199,7 +4199,7 @@
         <v>0.890529356295539</v>
       </c>
       <c r="C83" t="n">
-        <v>0.609605756097918</v>
+        <v>0.739971441501695</v>
       </c>
       <c r="D83" t="s">
         <v>38</v>
@@ -4219,7 +4219,7 @@
         <v>0.890529356295539</v>
       </c>
       <c r="C84" t="n">
-        <v>0.609605756097918</v>
+        <v>0.739971441501695</v>
       </c>
       <c r="D84" t="s">
         <v>40</v>
@@ -4239,7 +4239,7 @@
         <v>0.623190527327444</v>
       </c>
       <c r="C85" t="n">
-        <v>0.411247885561441</v>
+        <v>0.499194254072207</v>
       </c>
       <c r="D85" t="s">
         <v>189</v>
@@ -4259,7 +4259,7 @@
         <v>1.13583058305648</v>
       </c>
       <c r="C86" t="n">
-        <v>0.873377936463129</v>
+        <v>1.06015194928145</v>
       </c>
       <c r="D86" t="s">
         <v>192</v>
@@ -4279,7 +4279,7 @@
         <v>1.13583058305648</v>
       </c>
       <c r="C87" t="n">
-        <v>0.873377936463129</v>
+        <v>1.06015194928145</v>
       </c>
       <c r="D87" t="s">
         <v>194</v>
@@ -4299,7 +4299,7 @@
         <v>1.13583058305648</v>
       </c>
       <c r="C88" t="n">
-        <v>0.873377936463129</v>
+        <v>1.06015194928145</v>
       </c>
       <c r="D88" t="s">
         <v>196</v>
@@ -4319,7 +4319,7 @@
         <v>1.13487610357492</v>
       </c>
       <c r="C89" t="n">
-        <v>1.00610052347659</v>
+        <v>1.22125758690015</v>
       </c>
       <c r="D89" t="s">
         <v>199</v>
@@ -4339,7 +4339,7 @@
         <v>1.24845916188056</v>
       </c>
       <c r="C90" t="n">
-        <v>0.884288415964999</v>
+        <v>1.07339566157208</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -4359,7 +4359,7 @@
         <v>1.24845916188056</v>
       </c>
       <c r="C91" t="n">
-        <v>0.884288415964999</v>
+        <v>1.07339566157208</v>
       </c>
       <c r="D91" t="s">
         <v>202</v>
@@ -4379,7 +4379,7 @@
         <v>1.08906108846003</v>
       </c>
       <c r="C92" t="n">
-        <v>0.805774369358815</v>
+        <v>0.978091193620207</v>
       </c>
       <c r="D92" t="s">
         <v>107</v>
@@ -4399,7 +4399,7 @@
         <v>1.29570589621779</v>
       </c>
       <c r="C93" t="n">
-        <v>1.01351663760077</v>
+        <v>1.23025965521056</v>
       </c>
       <c r="D93" t="s">
         <v>38</v>
@@ -4419,7 +4419,7 @@
         <v>1.42599234545074</v>
       </c>
       <c r="C94" t="n">
-        <v>0.844623746276879</v>
+        <v>1.02524860503232</v>
       </c>
       <c r="D94" t="s">
         <v>207</v>
@@ -4439,7 +4439,7 @@
         <v>1.29481959384205</v>
       </c>
       <c r="C95" t="n">
-        <v>0.813401221308545</v>
+        <v>0.987349066556786</v>
       </c>
       <c r="D95" t="s">
         <v>129</v>
@@ -4459,7 +4459,7 @@
         <v>1.29481959384205</v>
       </c>
       <c r="C96" t="n">
-        <v>0.813401221308545</v>
+        <v>0.987349066556786</v>
       </c>
       <c r="D96" t="s">
         <v>120</v>
@@ -4479,7 +4479,7 @@
         <v>0.916538922168051</v>
       </c>
       <c r="C97" t="n">
-        <v>0.813828389870516</v>
+        <v>0.987867586162948</v>
       </c>
       <c r="D97" t="s">
         <v>211</v>
@@ -4499,7 +4499,7 @@
         <v>1.18482719644323</v>
       </c>
       <c r="C98" t="n">
-        <v>0.599993506910903</v>
+        <v>0.728303589261392</v>
       </c>
       <c r="D98" t="s">
         <v>214</v>
@@ -4519,7 +4519,7 @@
         <v>1.07156229796476</v>
       </c>
       <c r="C99" t="n">
-        <v>0.886937181795123</v>
+        <v>1.07661087246848</v>
       </c>
       <c r="D99" t="s">
         <v>217</v>
@@ -4539,7 +4539,7 @@
         <v>0.911118842254906</v>
       </c>
       <c r="C100" t="n">
-        <v>0.829026517390012</v>
+        <v>1.00631587051104</v>
       </c>
       <c r="D100" t="s">
         <v>220</v>
@@ -4559,7 +4559,7 @@
         <v>1.42981026337698</v>
       </c>
       <c r="C101" t="n">
-        <v>1.06615533474522</v>
+        <v>1.29415526678429</v>
       </c>
       <c r="D101" t="s">
         <v>223</v>
@@ -4579,7 +4579,7 @@
         <v>0.386246030204639</v>
       </c>
       <c r="C102" t="n">
-        <v>0.657611656220838</v>
+        <v>0.798243521053446</v>
       </c>
       <c r="D102" t="s">
         <v>226</v>
@@ -4599,7 +4599,7 @@
         <v>1.26754875151176</v>
       </c>
       <c r="C103" t="n">
-        <v>0.787022657233727</v>
+        <v>0.955329381886925</v>
       </c>
       <c r="D103" t="s">
         <v>229</v>
@@ -4619,7 +4619,7 @@
         <v>1.18482719644323</v>
       </c>
       <c r="C104" t="n">
-        <v>0.94226390698819</v>
+        <v>1.1437693534788</v>
       </c>
       <c r="D104" t="s">
         <v>232</v>
@@ -4639,7 +4639,7 @@
         <v>1.18482719644323</v>
       </c>
       <c r="C105" t="n">
-        <v>0.94226390698819</v>
+        <v>1.1437693534788</v>
       </c>
       <c r="D105" t="s">
         <v>234</v>
@@ -4659,7 +4659,7 @@
         <v>0.288252803431139</v>
       </c>
       <c r="C106" t="n">
-        <v>0.448814684585524</v>
+        <v>0.544794805163443</v>
       </c>
       <c r="D106" t="s">
         <v>237</v>
@@ -4679,7 +4679,7 @@
         <v>0.288252803431139</v>
       </c>
       <c r="C107" t="n">
-        <v>0.448814684585524</v>
+        <v>0.544794805163443</v>
       </c>
       <c r="D107" t="s">
         <v>239</v>
@@ -4699,7 +4699,7 @@
         <v>1.05860451591207</v>
       </c>
       <c r="C108" t="n">
-        <v>0.80944343096333</v>
+        <v>0.982544893043635</v>
       </c>
       <c r="D108" t="s">
         <v>242</v>
@@ -4719,7 +4719,7 @@
         <v>0.845986980489403</v>
       </c>
       <c r="C109" t="n">
-        <v>0.498159323539115</v>
+        <v>0.604691916126753</v>
       </c>
       <c r="D109" t="s">
         <v>245</v>
@@ -4739,7 +4739,7 @@
         <v>0.845986980489403</v>
       </c>
       <c r="C110" t="n">
-        <v>0.498159323539115</v>
+        <v>0.604691916126753</v>
       </c>
       <c r="D110" t="s">
         <v>247</v>
@@ -4759,7 +4759,7 @@
         <v>1.31145480766353</v>
       </c>
       <c r="C111" t="n">
-        <v>0.884562113114552</v>
+        <v>1.07372788952804</v>
       </c>
       <c r="D111" t="s">
         <v>250</v>
@@ -4779,7 +4779,7 @@
         <v>0.95384316190569</v>
       </c>
       <c r="C112" t="n">
-        <v>1.05204728514012</v>
+        <v>1.27703017618495</v>
       </c>
       <c r="D112" t="s">
         <v>253</v>
@@ -4799,7 +4799,7 @@
         <v>1.05183638867919</v>
       </c>
       <c r="C113" t="n">
-        <v>1.43507585892575</v>
+        <v>1.7419703494778</v>
       </c>
       <c r="D113" t="s">
         <v>153</v>
@@ -4819,7 +4819,7 @@
         <v>1.41453859167201</v>
       </c>
       <c r="C114" t="n">
-        <v>0.776673313169241</v>
+        <v>0.942766805222598</v>
       </c>
       <c r="D114" t="s">
         <v>20</v>
@@ -4839,7 +4839,7 @@
         <v>0.25035527385182</v>
       </c>
       <c r="C115" t="n">
-        <v>0.793298367646948</v>
+        <v>0.962947168357058</v>
       </c>
       <c r="D115" t="s">
         <v>20</v>
@@ -4859,7 +4859,7 @@
         <v>1.00506689408275</v>
       </c>
       <c r="C116" t="n">
-        <v>0.764641179758885</v>
+        <v>0.928161570585392</v>
       </c>
       <c r="D116" t="s">
         <v>38</v>
@@ -4879,7 +4879,7 @@
         <v>1.00506689408275</v>
       </c>
       <c r="C117" t="n">
-        <v>0.764641179758885</v>
+        <v>0.928161570585392</v>
       </c>
       <c r="D117" t="s">
         <v>259</v>
@@ -4899,7 +4899,7 @@
         <v>1.26373083358552</v>
       </c>
       <c r="C118" t="n">
-        <v>1.05775789075026</v>
+        <v>1.28396200880448</v>
       </c>
       <c r="D118" t="s">
         <v>262</v>
@@ -4919,7 +4919,7 @@
         <v>1.10210564137469</v>
       </c>
       <c r="C119" t="n">
-        <v>0.877626982851184</v>
+        <v>1.06530966465622</v>
       </c>
       <c r="D119" t="s">
         <v>192</v>
@@ -4939,7 +4939,7 @@
         <v>1.32672647936849</v>
       </c>
       <c r="C120" t="n">
-        <v>0.761365125026382</v>
+        <v>0.92418492351702</v>
       </c>
       <c r="D120" t="s">
         <v>266</v>
@@ -4959,7 +4959,7 @@
         <v>0.418698332577681</v>
       </c>
       <c r="C121" t="n">
-        <v>0.562775665021918</v>
+        <v>0.683126620644069</v>
       </c>
       <c r="D121" t="s">
         <v>269</v>
@@ -4979,7 +4979,7 @@
         <v>1.11292307549903</v>
       </c>
       <c r="C122" t="n">
-        <v>0.927433008452195</v>
+        <v>1.1257668309326</v>
       </c>
       <c r="D122" t="s">
         <v>194</v>
@@ -4999,7 +4999,7 @@
         <v>1.11101411653591</v>
       </c>
       <c r="C123" t="n">
-        <v>0.822805707566389</v>
+        <v>0.99876472525618</v>
       </c>
       <c r="D123" t="s">
         <v>273</v>
@@ -5019,7 +5019,7 @@
         <v>0.824193032327115</v>
       </c>
       <c r="C124" t="n">
-        <v>0.685950414858539</v>
+        <v>0.832642592698925</v>
       </c>
       <c r="D124" t="s">
         <v>276</v>
@@ -5039,7 +5039,7 @@
         <v>1.07601653554538</v>
       </c>
       <c r="C125" t="n">
-        <v>0.78580913568638</v>
+        <v>0.953856345781702</v>
       </c>
       <c r="D125" t="s">
         <v>279</v>
@@ -5059,7 +5059,7 @@
         <v>1.07601653554538</v>
       </c>
       <c r="C126" t="n">
-        <v>0.78580913568638</v>
+        <v>0.953856345781702</v>
       </c>
       <c r="D126" t="s">
         <v>281</v>
@@ -5079,7 +5079,7 @@
         <v>1.1457571696647</v>
       </c>
       <c r="C127" t="n">
-        <v>0.85605752397091</v>
+        <v>1.03912752411638</v>
       </c>
       <c r="D127" t="s">
         <v>284</v>
@@ -5099,7 +5099,7 @@
         <v>1.02892888112175</v>
       </c>
       <c r="C128" t="n">
-        <v>0.886280143921114</v>
+        <v>1.07581332543437</v>
       </c>
       <c r="D128" t="s">
         <v>287</v>
@@ -5119,7 +5119,7 @@
         <v>1.04849571049373</v>
       </c>
       <c r="C129" t="n">
-        <v>0.846652068524507</v>
+        <v>1.02771068896508</v>
       </c>
       <c r="D129" t="s">
         <v>75</v>
@@ -5139,7 +5139,7 @@
         <v>0.854259135996257</v>
       </c>
       <c r="C130" t="n">
-        <v>0.589213035262332</v>
+        <v>0.715217687322205</v>
       </c>
       <c r="D130" t="s">
         <v>291</v>
@@ -5159,7 +5159,7 @@
         <v>1.33818023314721</v>
       </c>
       <c r="C131" t="n">
-        <v>0.766296404622555</v>
+        <v>0.930170769343978</v>
       </c>
       <c r="D131" t="s">
         <v>294</v>
@@ -5179,7 +5179,7 @@
         <v>0.179442142533292</v>
       </c>
       <c r="C132" t="n">
-        <v>0.525265664770607</v>
+        <v>0.637595014882406</v>
       </c>
       <c r="D132" t="s">
         <v>297</v>
@@ -5199,7 +5199,7 @@
         <v>0.179442142533292</v>
       </c>
       <c r="C133" t="n">
-        <v>0.525265664770607</v>
+        <v>0.637595014882406</v>
       </c>
       <c r="D133" t="s">
         <v>299</v>
@@ -5219,7 +5219,7 @@
         <v>1.21600685950752</v>
       </c>
       <c r="C134" t="n">
-        <v>0.883945578187622</v>
+        <v>1.07297950709553</v>
       </c>
       <c r="D134" t="s">
         <v>302</v>
@@ -5239,7 +5239,7 @@
         <v>0.969751153265025</v>
       </c>
       <c r="C135" t="n">
-        <v>0.753140803835784</v>
+        <v>0.914201811077704</v>
       </c>
       <c r="D135" t="s">
         <v>305</v>
@@ -5259,7 +5259,7 @@
         <v>0.969751153265025</v>
       </c>
       <c r="C136" t="n">
-        <v>0.753140803835784</v>
+        <v>0.914201811077704</v>
       </c>
       <c r="D136" t="s">
         <v>307</v>
@@ -5279,7 +5279,7 @@
         <v>0.984386505315612</v>
       </c>
       <c r="C137" t="n">
-        <v>0.722452118851987</v>
+        <v>0.876950275576121</v>
       </c>
       <c r="D137" t="s">
         <v>310</v>
@@ -5299,7 +5299,7 @@
         <v>0.690406824995113</v>
       </c>
       <c r="C138" t="n">
-        <v>1.00256399594042</v>
+        <v>1.21696476428049</v>
       </c>
       <c r="D138" t="s">
         <v>313</v>
@@ -5319,7 +5319,7 @@
         <v>1.59493521368687</v>
       </c>
       <c r="C139" t="n">
-        <v>0.715086627157835</v>
+        <v>0.868009655426505</v>
       </c>
       <c r="D139" t="s">
         <v>131</v>
@@ -5339,7 +5339,7 @@
         <v>1.59493521368687</v>
       </c>
       <c r="C140" t="n">
-        <v>0.715086627157835</v>
+        <v>0.868009655426505</v>
       </c>
       <c r="D140" t="s">
         <v>124</v>
@@ -5359,7 +5359,7 @@
         <v>0.889097637073199</v>
       </c>
       <c r="C141" t="n">
-        <v>0.748293120813006</v>
+        <v>0.908317439156302</v>
       </c>
       <c r="D141" t="s">
         <v>63</v>
@@ -5379,7 +5379,7 @@
         <v>0.889097637073199</v>
       </c>
       <c r="C142" t="n">
-        <v>0.748293120813006</v>
+        <v>0.908317439156302</v>
       </c>
       <c r="D142" t="s">
         <v>65</v>
@@ -5399,7 +5399,7 @@
         <v>0.889097637073199</v>
       </c>
       <c r="C143" t="n">
-        <v>0.748293120813006</v>
+        <v>0.908317439156302</v>
       </c>
       <c r="D143" t="s">
         <v>67</v>
@@ -5419,7 +5419,7 @@
         <v>0.475330781816912</v>
       </c>
       <c r="C144" t="n">
-        <v>0.323523449288753</v>
+        <v>0.392709732044173</v>
       </c>
       <c r="D144" t="s">
         <v>318</v>
@@ -5439,7 +5439,7 @@
         <v>0.475330781816912</v>
       </c>
       <c r="C145" t="n">
-        <v>0.323523449288753</v>
+        <v>0.392709732044173</v>
       </c>
       <c r="D145" t="s">
         <v>320</v>
@@ -5459,7 +5459,7 @@
         <v>1.33818023314721</v>
       </c>
       <c r="C146" t="n">
-        <v>0.866261533689472</v>
+        <v>1.05151368632862</v>
       </c>
       <c r="D146" t="s">
         <v>223</v>
@@ -5479,7 +5479,7 @@
         <v>0.843759861699096</v>
       </c>
       <c r="C147" t="n">
-        <v>0.53939808014696</v>
+        <v>0.654749681932926</v>
       </c>
       <c r="D147" t="s">
         <v>324</v>
@@ -5499,7 +5499,7 @@
         <v>1.21470072969065</v>
       </c>
       <c r="C148" t="n">
-        <v>0.767492666160892</v>
+        <v>0.931622854344951</v>
       </c>
       <c r="D148" t="s">
         <v>327</v>
@@ -5519,7 +5519,7 @@
         <v>0.979295948080625</v>
       </c>
       <c r="C149" t="n">
-        <v>1.11403193606065</v>
+        <v>1.35227039666159</v>
       </c>
       <c r="D149" t="s">
         <v>330</v>
@@ -5539,7 +5539,7 @@
         <v>0.979295948080625</v>
       </c>
       <c r="C150" t="n">
-        <v>1.11403193606065</v>
+        <v>1.35227039666159</v>
       </c>
       <c r="D150" t="s">
         <v>332</v>
@@ -5559,7 +5559,7 @@
         <v>1.42026546856137</v>
       </c>
       <c r="C151" t="n">
-        <v>0.696164480090135</v>
+        <v>0.845040960820308</v>
       </c>
       <c r="D151" t="s">
         <v>207</v>
@@ -5579,7 +5579,7 @@
         <v>1.06201750314916</v>
       </c>
       <c r="C152" t="n">
-        <v>0.707013073137862</v>
+        <v>0.858209552086862</v>
       </c>
       <c r="D152" t="s">
         <v>160</v>
@@ -5599,7 +5599,7 @@
         <v>1.4412640171557</v>
       </c>
       <c r="C153" t="n">
-        <v>0.846673399593913</v>
+        <v>1.02773658173597</v>
       </c>
       <c r="D153" t="s">
         <v>337</v>
@@ -5619,7 +5619,7 @@
         <v>0.672908034499845</v>
       </c>
       <c r="C154" t="n">
-        <v>0.48484761810227</v>
+        <v>0.588533469848293</v>
       </c>
       <c r="D154" t="s">
         <v>340</v>
@@ -5639,7 +5639,7 @@
         <v>1.14442089839052</v>
       </c>
       <c r="C155" t="n">
-        <v>0.745906375323473</v>
+        <v>0.905420282292671</v>
       </c>
       <c r="D155" t="s">
         <v>343</v>
@@ -5659,7 +5659,7 @@
         <v>1.15969257009548</v>
       </c>
       <c r="C156" t="n">
-        <v>0.84393733837977</v>
+        <v>1.02441540712367</v>
       </c>
       <c r="D156" t="s">
         <v>346</v>
@@ -5679,7 +5679,7 @@
         <v>1.28759282062453</v>
       </c>
       <c r="C157" t="n">
-        <v>0.948339559358728</v>
+        <v>1.15114429900337</v>
       </c>
       <c r="D157" t="s">
         <v>245</v>
@@ -5699,7 +5699,7 @@
         <v>0.321977745112928</v>
       </c>
       <c r="C158" t="n">
-        <v>0.433986038344563</v>
+        <v>0.526795016571093</v>
       </c>
       <c r="D158" t="s">
         <v>350</v>
@@ -5719,7 +5719,7 @@
         <v>0.321977745112928</v>
       </c>
       <c r="C159" t="n">
-        <v>0.433986038344563</v>
+        <v>0.526795016571093</v>
       </c>
       <c r="D159" t="s">
         <v>352</v>
@@ -5739,7 +5739,7 @@
         <v>0.637592293682122</v>
       </c>
       <c r="C160" t="n">
-        <v>0.767729175386207</v>
+        <v>0.931909941647907</v>
       </c>
       <c r="D160" t="s">
         <v>355</v>
@@ -5759,7 +5759,7 @@
         <v>0.432379205146709</v>
       </c>
       <c r="C161" t="n">
-        <v>0.415125185338721</v>
+        <v>0.503900723912145</v>
       </c>
       <c r="D161" t="s">
         <v>358</v>
@@ -5779,7 +5779,7 @@
         <v>1.13074002582149</v>
       </c>
       <c r="C162" t="n">
-        <v>0.827773694812288</v>
+        <v>1.00479512875375</v>
       </c>
       <c r="D162" t="s">
         <v>361</v>
@@ -5799,7 +5799,7 @@
         <v>0.630910937311202</v>
       </c>
       <c r="C163" t="n">
-        <v>0.879049840662434</v>
+        <v>1.06703680409857</v>
       </c>
       <c r="D163" t="s">
         <v>364</v>
@@ -5819,7 +5819,7 @@
         <v>0.630910937311202</v>
       </c>
       <c r="C164" t="n">
-        <v>0.879049840662434</v>
+        <v>1.06703680409857</v>
       </c>
       <c r="D164" t="s">
         <v>366</v>
@@ -5839,7 +5839,7 @@
         <v>0.630910937311202</v>
       </c>
       <c r="C165" t="n">
-        <v>0.879049840662434</v>
+        <v>1.06703680409857</v>
       </c>
       <c r="D165" t="s">
         <v>15</v>
@@ -5859,7 +5859,7 @@
         <v>0.630910937311202</v>
       </c>
       <c r="C166" t="n">
-        <v>0.879049840662434</v>
+        <v>1.06703680409857</v>
       </c>
       <c r="D166" t="s">
         <v>17</v>
@@ -5879,7 +5879,7 @@
         <v>1.23652816836106</v>
       </c>
       <c r="C167" t="n">
-        <v>1.07830081418833</v>
+        <v>1.30889808678123</v>
       </c>
       <c r="D167" t="s">
         <v>369</v>
@@ -5899,7 +5899,7 @@
         <v>1.07856181416287</v>
       </c>
       <c r="C168" t="n">
-        <v>0.894234233022679</v>
+        <v>1.08546841598994</v>
       </c>
       <c r="D168" t="s">
         <v>372</v>
@@ -5919,7 +5919,7 @@
         <v>1.1686010452567</v>
       </c>
       <c r="C169" t="n">
-        <v>0.87664758259241</v>
+        <v>1.06412081725108</v>
       </c>
       <c r="D169" t="s">
         <v>375</v>
@@ -5939,7 +5939,7 @@
         <v>1.1686010452567</v>
       </c>
       <c r="C170" t="n">
-        <v>0.87664758259241</v>
+        <v>1.06412081725108</v>
       </c>
       <c r="D170" t="s">
         <v>377</v>
@@ -5959,7 +5959,7 @@
         <v>0.883847999924619</v>
       </c>
       <c r="C171" t="n">
-        <v>0.764347692063462</v>
+        <v>0.92780531982681</v>
       </c>
       <c r="D171" t="s">
         <v>380</v>
@@ -5979,7 +5979,7 @@
         <v>1.03847367593735</v>
       </c>
       <c r="C172" t="n">
-        <v>0.730405080747854</v>
+        <v>0.886603997870284</v>
       </c>
       <c r="D172" t="s">
         <v>171</v>
@@ -5999,7 +5999,7 @@
         <v>0.211894444906334</v>
       </c>
       <c r="C173" t="n">
-        <v>0.395763260498764</v>
+        <v>0.480398203978969</v>
       </c>
       <c r="D173" t="s">
         <v>151</v>
@@ -6019,7 +6019,7 @@
         <v>0.211894444906334</v>
       </c>
       <c r="C174" t="n">
-        <v>0.395763260498764</v>
+        <v>0.480398203978969</v>
       </c>
       <c r="D174" t="s">
         <v>153</v>
@@ -6039,7 +6039,7 @@
         <v>0.872394246145898</v>
       </c>
       <c r="C175" t="n">
-        <v>0.671370390826057</v>
+        <v>0.814944594783839</v>
       </c>
       <c r="D175" t="s">
         <v>385</v>
@@ -6059,7 +6059,7 @@
         <v>0.941116768818223</v>
       </c>
       <c r="C176" t="n">
-        <v>0.666260165897137</v>
+        <v>0.808741535726037</v>
       </c>
       <c r="D176" t="s">
         <v>192</v>
@@ -6079,7 +6079,7 @@
         <v>1.21982477743376</v>
       </c>
       <c r="C177" t="n">
-        <v>0.776107742894113</v>
+        <v>0.942080286357626</v>
       </c>
       <c r="D177" t="s">
         <v>223</v>
@@ -6099,7 +6099,7 @@
         <v>0.74258503665373</v>
       </c>
       <c r="C178" t="n">
-        <v>0.983772819607084</v>
+        <v>1.19415504882128</v>
       </c>
       <c r="D178" t="s">
         <v>390</v>
@@ -6119,7 +6119,7 @@
         <v>0.5998903541605</v>
       </c>
       <c r="C179" t="n">
-        <v>0.607836929320926</v>
+        <v>0.737824346782124</v>
       </c>
       <c r="D179" t="s">
         <v>393</v>
@@ -6139,7 +6139,7 @@
         <v>0.717291330392388</v>
       </c>
       <c r="C180" t="n">
-        <v>0.542488823537749</v>
+        <v>0.658501388374863</v>
       </c>
       <c r="D180" t="s">
         <v>245</v>
@@ -6159,7 +6159,7 @@
         <v>0.931571974002622</v>
       </c>
       <c r="C181" t="n">
-        <v>0.685258762783606</v>
+        <v>0.831803029132166</v>
       </c>
       <c r="D181" t="s">
         <v>232</v>
@@ -6179,7 +6179,7 @@
         <v>0.931571974002622</v>
       </c>
       <c r="C182" t="n">
-        <v>0.685258762783606</v>
+        <v>0.831803029132166</v>
       </c>
       <c r="D182" t="s">
         <v>397</v>
@@ -6199,7 +6199,7 @@
         <v>0.931571974002622</v>
       </c>
       <c r="C183" t="n">
-        <v>0.685258762783606</v>
+        <v>0.831803029132166</v>
       </c>
       <c r="D183" t="s">
         <v>330</v>
@@ -6219,7 +6219,7 @@
         <v>0.931571974002622</v>
       </c>
       <c r="C184" t="n">
-        <v>0.685258762783606</v>
+        <v>0.831803029132166</v>
       </c>
       <c r="D184" t="s">
         <v>399</v>
@@ -6239,7 +6239,7 @@
         <v>1.04229159386359</v>
       </c>
       <c r="C185" t="n">
-        <v>0.809620817427451</v>
+        <v>0.982760214037975</v>
       </c>
       <c r="D185" t="s">
         <v>192</v>
@@ -6259,7 +6259,7 @@
         <v>1.17400976231888</v>
       </c>
       <c r="C186" t="n">
-        <v>0.82907044689723</v>
+        <v>1.00636919445107</v>
       </c>
       <c r="D186" t="s">
         <v>403</v>
@@ -6279,7 +6279,7 @@
         <v>0.757856708358691</v>
       </c>
       <c r="C187" t="n">
-        <v>1.01505571189615</v>
+        <v>1.23212786431708</v>
       </c>
       <c r="D187" t="s">
         <v>406</v>
@@ -6299,7 +6299,7 @@
         <v>1.36108774070465</v>
       </c>
       <c r="C188" t="n">
-        <v>0.841309172372682</v>
+        <v>1.02122520137296</v>
       </c>
       <c r="D188" t="s">
         <v>409</v>
@@ -6319,7 +6319,7 @@
         <v>1.09097004742315</v>
       </c>
       <c r="C189" t="n">
-        <v>0.674350172748632</v>
+        <v>0.81856161037556</v>
       </c>
       <c r="D189" t="s">
         <v>412</v>
@@ -6339,7 +6339,7 @@
         <v>1.39354004307769</v>
       </c>
       <c r="C190" t="n">
-        <v>0.818970913122989</v>
+        <v>0.994109850619973</v>
       </c>
       <c r="D190" t="s">
         <v>415</v>
@@ -6359,7 +6359,7 @@
         <v>1.17782768024512</v>
       </c>
       <c r="C191" t="n">
-        <v>1.156866580415</v>
+        <v>1.40426533472121</v>
       </c>
       <c r="D191" t="s">
         <v>327</v>
@@ -6379,7 +6379,7 @@
         <v>1.19882622883944</v>
       </c>
       <c r="C192" t="n">
-        <v>0.754438818703039</v>
+        <v>0.915777409606435</v>
       </c>
       <c r="D192" t="s">
         <v>419</v>
@@ -6399,7 +6399,7 @@
         <v>1.19882622883944</v>
       </c>
       <c r="C193" t="n">
-        <v>0.754438818703039</v>
+        <v>0.915777409606435</v>
       </c>
       <c r="D193" t="s">
         <v>397</v>
@@ -6419,7 +6419,7 @@
         <v>1.19882622883944</v>
       </c>
       <c r="C194" t="n">
-        <v>0.754438818703039</v>
+        <v>0.915777409606435</v>
       </c>
       <c r="D194" t="s">
         <v>421</v>
@@ -6439,7 +6439,7 @@
         <v>1.19882622883944</v>
       </c>
       <c r="C195" t="n">
-        <v>0.754438818703039</v>
+        <v>0.915777409606435</v>
       </c>
       <c r="D195" t="s">
         <v>399</v>
@@ -6459,7 +6459,7 @@
         <v>1.19882622883944</v>
       </c>
       <c r="C196" t="n">
-        <v>0.754438818703039</v>
+        <v>0.915777409606435</v>
       </c>
       <c r="D196" t="s">
         <v>423</v>
@@ -6479,7 +6479,7 @@
         <v>1.13583058305648</v>
       </c>
       <c r="C197" t="n">
-        <v>0.760426139935753</v>
+        <v>0.923045134162817</v>
       </c>
       <c r="D197" t="s">
         <v>426</v>
@@ -6499,7 +6499,7 @@
         <v>1.13583058305648</v>
       </c>
       <c r="C198" t="n">
-        <v>0.760426139935753</v>
+        <v>0.923045134162817</v>
       </c>
       <c r="D198" t="s">
         <v>428</v>
@@ -6519,7 +6519,7 @@
         <v>1.18737247506072</v>
       </c>
       <c r="C199" t="n">
-        <v>0.668134988266577</v>
+        <v>0.811017293455352</v>
       </c>
       <c r="D199" t="s">
         <v>185</v>
@@ -6539,7 +6539,7 @@
         <v>0.705360336872887</v>
       </c>
       <c r="C200" t="n">
-        <v>0.418295909557244</v>
+        <v>0.507749515277902</v>
       </c>
       <c r="D200" t="s">
         <v>340</v>
@@ -6559,7 +6559,7 @@
         <v>0.767401503174291</v>
       </c>
       <c r="C201" t="n">
-        <v>1.33470305543592</v>
+        <v>1.62013257589548</v>
       </c>
       <c r="D201" t="s">
         <v>433</v>
@@ -6579,7 +6579,7 @@
         <v>1.05756326556855</v>
       </c>
       <c r="C202" t="n">
-        <v>0.802616941402962</v>
+        <v>0.974258541955489</v>
       </c>
       <c r="D202" t="s">
         <v>436</v>
@@ -6599,7 +6599,7 @@
         <v>1.23652816836106</v>
       </c>
       <c r="C203" t="n">
-        <v>0.903297031527028</v>
+        <v>1.09646931617209</v>
       </c>
       <c r="D203" t="s">
         <v>237</v>
@@ -6619,7 +6619,7 @@
         <v>1.23652816836106</v>
       </c>
       <c r="C204" t="n">
-        <v>0.903297031527028</v>
+        <v>1.09646931617209</v>
       </c>
       <c r="D204" t="s">
         <v>239</v>
@@ -6639,7 +6639,7 @@
         <v>0.866667369256538</v>
       </c>
       <c r="C205" t="n">
-        <v>0.588684681339004</v>
+        <v>0.714576343617102</v>
       </c>
       <c r="D205" t="s">
         <v>107</v>
@@ -6659,7 +6659,7 @@
         <v>1.18164559817136</v>
       </c>
       <c r="C206" t="n">
-        <v>1.00769861157149</v>
+        <v>1.2231974300519</v>
       </c>
       <c r="D206" t="s">
         <v>441</v>
@@ -6679,7 +6679,7 @@
         <v>1.10337828068343</v>
       </c>
       <c r="C207" t="n">
-        <v>0.863909011581849</v>
+        <v>1.04865807160102</v>
       </c>
       <c r="D207" t="s">
         <v>250</v>
@@ -6699,7 +6699,7 @@
         <v>0.126063327753216</v>
       </c>
       <c r="C208" t="n">
-        <v>0.319524662176353</v>
+        <v>0.387855794504669</v>
       </c>
       <c r="D208" t="s">
         <v>151</v>
@@ -6719,7 +6719,7 @@
         <v>0.126063327753216</v>
       </c>
       <c r="C209" t="n">
-        <v>0.319524662176353</v>
+        <v>0.387855794504669</v>
       </c>
       <c r="D209" t="s">
         <v>153</v>
@@ -6739,7 +6739,7 @@
         <v>0.439537801258409</v>
       </c>
       <c r="C210" t="n">
-        <v>0.500925787991356</v>
+        <v>0.608049995784155</v>
       </c>
       <c r="D210" t="s">
         <v>127</v>
@@ -6759,7 +6759,7 @@
         <v>0.439537801258409</v>
       </c>
       <c r="C211" t="n">
-        <v>0.500925787991356</v>
+        <v>0.608049995784155</v>
       </c>
       <c r="D211" t="s">
         <v>129</v>
@@ -6779,7 +6779,7 @@
         <v>0.439537801258409</v>
       </c>
       <c r="C212" t="n">
-        <v>0.500925787991356</v>
+        <v>0.608049995784155</v>
       </c>
       <c r="D212" t="s">
         <v>120</v>
@@ -6799,7 +6799,7 @@
         <v>0.439537801258409</v>
       </c>
       <c r="C213" t="n">
-        <v>0.500925787991356</v>
+        <v>0.608049995784155</v>
       </c>
       <c r="D213" t="s">
         <v>122</v>
@@ -6819,7 +6819,7 @@
         <v>0.85012305824283</v>
       </c>
       <c r="C214" t="n">
-        <v>0.623842838946173</v>
+        <v>0.757253159419578</v>
       </c>
       <c r="D214" t="s">
         <v>447</v>
@@ -6839,7 +6839,7 @@
         <v>1.09956036275719</v>
       </c>
       <c r="C215" t="n">
-        <v>0.926089256993261</v>
+        <v>1.12413571492994</v>
       </c>
       <c r="D215" t="s">
         <v>450</v>
@@ -6859,7 +6859,7 @@
         <v>1.1854635160976</v>
       </c>
       <c r="C216" t="n">
-        <v>0.985423504653401</v>
+        <v>1.19615873691144</v>
       </c>
       <c r="D216" t="s">
         <v>242</v>
@@ -6879,7 +6879,7 @@
         <v>0.216169437513885</v>
       </c>
       <c r="C217" t="n">
-        <v>0.378846336836367</v>
+        <v>0.45986355471915</v>
       </c>
       <c r="D217" t="s">
         <v>151</v>
@@ -6899,7 +6899,7 @@
         <v>0.216169437513885</v>
       </c>
       <c r="C218" t="n">
-        <v>0.378846336836367</v>
+        <v>0.45986355471915</v>
       </c>
       <c r="D218" t="s">
         <v>153</v>
@@ -6919,7 +6919,7 @@
         <v>1.18355455713448</v>
       </c>
       <c r="C219" t="n">
-        <v>0.873618192795342</v>
+        <v>1.0604435850193</v>
       </c>
       <c r="D219" t="s">
         <v>455</v>
@@ -6939,7 +6939,7 @@
         <v>1.40499379685641</v>
       </c>
       <c r="C220" t="n">
-        <v>1.07346874976891</v>
+        <v>1.3030326735398</v>
       </c>
       <c r="D220" t="s">
         <v>458</v>
@@ -6959,7 +6959,7 @@
         <v>1.12437682927775</v>
       </c>
       <c r="C221" t="n">
-        <v>0.815419794554726</v>
+        <v>0.98979931664024</v>
       </c>
       <c r="D221" t="s">
         <v>461</v>
@@ -6979,7 +6979,7 @@
         <v>1.12437682927775</v>
       </c>
       <c r="C222" t="n">
-        <v>0.815419794554726</v>
+        <v>0.98979931664024</v>
       </c>
       <c r="D222" t="s">
         <v>463</v>
@@ -6999,7 +6999,7 @@
         <v>1.25036812084368</v>
       </c>
       <c r="C223" t="n">
-        <v>1.11647128870508</v>
+        <v>1.35523141084916</v>
       </c>
       <c r="D223" t="s">
         <v>466</v>
@@ -7019,7 +7019,7 @@
         <v>0.524591839735349</v>
       </c>
       <c r="C224" t="n">
-        <v>0.689170455566436</v>
+        <v>0.836551247006207</v>
       </c>
       <c r="D224" t="s">
         <v>469</v>
@@ -7039,7 +7039,7 @@
         <v>0.519236837968675</v>
       </c>
       <c r="C225" t="n">
-        <v>0.71307213347863</v>
+        <v>0.865564357335426</v>
       </c>
       <c r="D225" t="s">
         <v>472</v>
@@ -7059,7 +7059,7 @@
         <v>0.761674626284931</v>
       </c>
       <c r="C226" t="n">
-        <v>0.86072272658443</v>
+        <v>1.04479039174565</v>
       </c>
       <c r="D226" t="s">
         <v>475</v>
@@ -7079,7 +7079,7 @@
         <v>0.761674626284931</v>
       </c>
       <c r="C227" t="n">
-        <v>0.86072272658443</v>
+        <v>1.04479039174565</v>
       </c>
       <c r="D227" t="s">
         <v>477</v>
@@ -7099,7 +7099,7 @@
         <v>0.74449399561685</v>
       </c>
       <c r="C228" t="n">
-        <v>0.639239882246271</v>
+        <v>0.7759428981756</v>
       </c>
       <c r="D228" t="s">
         <v>480</v>
@@ -7119,7 +7119,7 @@
         <v>1.4412640171557</v>
       </c>
       <c r="C229" t="n">
-        <v>0.981641531167542</v>
+        <v>1.19156797912404</v>
       </c>
       <c r="D229" t="s">
         <v>483</v>
@@ -7139,7 +7139,7 @@
         <v>1.4412640171557</v>
       </c>
       <c r="C230" t="n">
-        <v>0.981641531167542</v>
+        <v>1.19156797912404</v>
       </c>
       <c r="D230" t="s">
         <v>485</v>
@@ -7159,7 +7159,7 @@
         <v>1.34104367159189</v>
       </c>
       <c r="C231" t="n">
-        <v>0.707837152443811</v>
+        <v>0.859209862772637</v>
       </c>
       <c r="D231" t="s">
         <v>361</v>
@@ -7179,7 +7179,7 @@
         <v>1.33054439729473</v>
       </c>
       <c r="C232" t="n">
-        <v>0.790587362697871</v>
+        <v>0.959656408353532</v>
       </c>
       <c r="D232" t="s">
         <v>361</v>
@@ -7199,7 +7199,7 @@
         <v>0.160548343564975</v>
       </c>
       <c r="C233" t="n">
-        <v>0.553526694703766</v>
+        <v>0.671899735349321</v>
       </c>
       <c r="D233" t="s">
         <v>20</v>
@@ -7219,7 +7219,7 @@
         <v>1.20433562939123</v>
       </c>
       <c r="C234" t="n">
-        <v>0.728670577749332</v>
+        <v>0.884498567153355</v>
       </c>
       <c r="D234" t="s">
         <v>491</v>
@@ -7239,7 +7239,7 @@
         <v>1.05819958522292</v>
       </c>
       <c r="C235" t="n">
-        <v>0.813622933644024</v>
+        <v>0.987618192618741</v>
       </c>
       <c r="D235" t="s">
         <v>491</v>
@@ -7259,7 +7259,7 @@
         <v>0.9010286305927</v>
       </c>
       <c r="C236" t="n">
-        <v>0.73690055834466</v>
+        <v>0.894488549274977</v>
       </c>
       <c r="D236" t="s">
         <v>495</v>
@@ -7279,7 +7279,7 @@
         <v>0.94860576167354</v>
       </c>
       <c r="C237" t="n">
-        <v>0.566701296890267</v>
+        <v>0.68789175851124</v>
       </c>
       <c r="D237" t="s">
         <v>20</v>
@@ -7299,7 +7299,7 @@
         <v>0.833260587401936</v>
       </c>
       <c r="C238" t="n">
-        <v>0.608107838120163</v>
+        <v>0.738153190092218</v>
       </c>
       <c r="D238" t="s">
         <v>343</v>
@@ -7319,7 +7319,7 @@
         <v>1.35249742537061</v>
       </c>
       <c r="C239" t="n">
-        <v>0.888101791766342</v>
+        <v>1.07802453713711</v>
       </c>
       <c r="D239" t="s">
         <v>500</v>
@@ -7339,7 +7339,7 @@
         <v>1.10242380120187</v>
       </c>
       <c r="C240" t="n">
-        <v>0.841396787800446</v>
+        <v>1.02133155357474</v>
       </c>
       <c r="D240" t="s">
         <v>503</v>
@@ -7359,7 +7359,7 @@
         <v>0.977386989117505</v>
       </c>
       <c r="C241" t="n">
-        <v>0.685376747718879</v>
+        <v>0.831946245435091</v>
       </c>
       <c r="D241" t="s">
         <v>506</v>
@@ -7379,7 +7379,7 @@
         <v>0.981204907043745</v>
       </c>
       <c r="C242" t="n">
-        <v>1.171852887951</v>
+        <v>1.42245650086306</v>
       </c>
       <c r="D242" t="s">
         <v>509</v>
@@ -7399,7 +7399,7 @@
         <v>0.471512863890671</v>
       </c>
       <c r="C243" t="n">
-        <v>0.972647100461969</v>
+        <v>1.18065006736203</v>
       </c>
       <c r="D243" t="s">
         <v>512</v>
@@ -7419,7 +7419,7 @@
         <v>0.471512863890671</v>
       </c>
       <c r="C244" t="n">
-        <v>0.972647100461969</v>
+        <v>1.18065006736203</v>
       </c>
       <c r="D244" t="s">
         <v>514</v>
@@ -7439,7 +7439,7 @@
         <v>0.471512863890671</v>
       </c>
       <c r="C245" t="n">
-        <v>0.972647100461969</v>
+        <v>1.18065006736203</v>
       </c>
       <c r="D245" t="s">
         <v>516</v>
@@ -7459,7 +7459,7 @@
         <v>0.471512863890671</v>
       </c>
       <c r="C246" t="n">
-        <v>0.972647100461969</v>
+        <v>1.18065006736203</v>
       </c>
       <c r="D246" t="s">
         <v>518</v>
@@ -7479,7 +7479,7 @@
         <v>0.471512863890671</v>
       </c>
       <c r="C247" t="n">
-        <v>0.972647100461969</v>
+        <v>1.18065006736203</v>
       </c>
       <c r="D247" t="s">
         <v>520</v>
@@ -7499,7 +7499,7 @@
         <v>0.471512863890671</v>
       </c>
       <c r="C248" t="n">
-        <v>0.972647100461969</v>
+        <v>1.18065006736203</v>
       </c>
       <c r="D248" t="s">
         <v>522</v>
@@ -7519,7 +7519,7 @@
         <v>0.471512863890671</v>
       </c>
       <c r="C249" t="n">
-        <v>0.972647100461969</v>
+        <v>1.18065006736203</v>
       </c>
       <c r="D249" t="s">
         <v>524</v>
@@ -7539,7 +7539,7 @@
         <v>0.471512863890671</v>
       </c>
       <c r="C250" t="n">
-        <v>0.972647100461969</v>
+        <v>1.18065006736203</v>
       </c>
       <c r="D250" t="s">
         <v>526</v>
@@ -7559,7 +7559,7 @@
         <v>0.471512863890671</v>
       </c>
       <c r="C251" t="n">
-        <v>0.972647100461969</v>
+        <v>1.18065006736203</v>
       </c>
       <c r="D251" t="s">
         <v>528</v>
@@ -7579,7 +7579,7 @@
         <v>0.471512863890671</v>
       </c>
       <c r="C252" t="n">
-        <v>0.972647100461969</v>
+        <v>1.18065006736203</v>
       </c>
       <c r="D252" t="s">
         <v>530</v>
@@ -7599,7 +7599,7 @@
         <v>0.772173900582092</v>
       </c>
       <c r="C253" t="n">
-        <v>0.708556546639866</v>
+        <v>0.86008310118113</v>
       </c>
       <c r="D253" t="s">
         <v>138</v>
@@ -7619,7 +7619,7 @@
         <v>0.914391343334541</v>
       </c>
       <c r="C254" t="n">
-        <v>0.866130300281177</v>
+        <v>1.05135438833424</v>
       </c>
       <c r="D254" t="s">
         <v>534</v>
@@ -7639,7 +7639,7 @@
         <v>1.05947222453167</v>
       </c>
       <c r="C255" t="n">
-        <v>0.770823443759821</v>
+        <v>0.935665926898887</v>
       </c>
       <c r="D255" t="s">
         <v>346</v>
@@ -7659,7 +7659,7 @@
         <v>0.853304656514697</v>
       </c>
       <c r="C256" t="n">
-        <v>1.0161903313269</v>
+        <v>1.23350512489464</v>
       </c>
       <c r="D256" t="s">
         <v>189</v>
@@ -7679,7 +7679,7 @@
         <v>0.74449399561685</v>
       </c>
       <c r="C257" t="n">
-        <v>0.698709070358607</v>
+        <v>0.848129717955813</v>
       </c>
       <c r="D257" t="s">
         <v>539</v>
@@ -7699,7 +7699,7 @@
         <v>0.968796673783465</v>
       </c>
       <c r="C258" t="n">
-        <v>0.739139744283286</v>
+        <v>0.897206590615993</v>
       </c>
       <c r="D258" t="s">
         <v>447</v>
@@ -7719,7 +7719,7 @@
         <v>1.00983929149055</v>
       </c>
       <c r="C259" t="n">
-        <v>0.722950859654846</v>
+        <v>0.877555673322345</v>
       </c>
       <c r="D259" t="s">
         <v>543</v>
@@ -7739,7 +7739,7 @@
         <v>1.00983929149055</v>
       </c>
       <c r="C260" t="n">
-        <v>0.722950859654846</v>
+        <v>0.877555673322345</v>
       </c>
       <c r="D260" t="s">
         <v>545</v>
@@ -7759,7 +7759,7 @@
         <v>1.00983929149055</v>
       </c>
       <c r="C261" t="n">
-        <v>0.722950859654846</v>
+        <v>0.877555673322345</v>
       </c>
       <c r="D261" t="s">
         <v>547</v>
@@ -7779,7 +7779,7 @@
         <v>0.461968069075071</v>
       </c>
       <c r="C262" t="n">
-        <v>0.49918811526289</v>
+        <v>0.605940717482764</v>
       </c>
       <c r="D262" t="s">
         <v>291</v>
@@ -7799,7 +7799,7 @@
         <v>0.289635153025123</v>
       </c>
       <c r="C263" t="n">
-        <v>0.499309307304545</v>
+        <v>0.606087826739631</v>
       </c>
       <c r="D263" t="s">
         <v>358</v>
@@ -7819,7 +7819,7 @@
         <v>1.18737247506072</v>
       </c>
       <c r="C264" t="n">
-        <v>0.62018300336159</v>
+        <v>0.752810659023063</v>
       </c>
       <c r="D264" t="s">
         <v>552</v>
@@ -7839,7 +7839,7 @@
         <v>0.429515766702029</v>
       </c>
       <c r="C265" t="n">
-        <v>0.828381448011425</v>
+        <v>1.00553285146444</v>
       </c>
       <c r="D265" t="s">
         <v>555</v>
@@ -7859,7 +7859,7 @@
         <v>0.657318202967697</v>
       </c>
       <c r="C266" t="n">
-        <v>0.671725407663103</v>
+        <v>0.81537553284182</v>
       </c>
       <c r="D266" t="s">
         <v>512</v>
@@ -7879,7 +7879,7 @@
         <v>0.994567619785586</v>
       </c>
       <c r="C267" t="n">
-        <v>0.832388815206832</v>
+        <v>1.01039720395874</v>
       </c>
       <c r="D267" t="s">
         <v>151</v>
@@ -7899,7 +7899,7 @@
         <v>1.03179231956643</v>
       </c>
       <c r="C268" t="n">
-        <v>0.820841691997674</v>
+        <v>0.996380700143266</v>
       </c>
       <c r="D268" t="s">
         <v>375</v>
@@ -7919,7 +7919,7 @@
         <v>0.912482384371421</v>
       </c>
       <c r="C269" t="n">
-        <v>0.676729934192495</v>
+        <v>0.821450289638231</v>
       </c>
       <c r="D269" t="s">
         <v>561</v>
@@ -7939,7 +7939,7 @@
         <v>1.15754844952096</v>
       </c>
       <c r="C270" t="n">
-        <v>0.975351295117452</v>
+        <v>1.18393256067398</v>
       </c>
       <c r="D270" t="s">
         <v>81</v>
@@ -7959,7 +7959,7 @@
         <v>1.10337828068343</v>
       </c>
       <c r="C271" t="n">
-        <v>0.873576693244109</v>
+        <v>1.0603932106873</v>
       </c>
       <c r="D271" t="s">
         <v>565</v>
@@ -7979,7 +7979,7 @@
         <v>0.971660112228145</v>
       </c>
       <c r="C272" t="n">
-        <v>0.878110113664596</v>
+        <v>1.06589611417848</v>
       </c>
       <c r="D272" t="s">
         <v>20</v>
@@ -7999,7 +7999,7 @@
         <v>1.08047077312599</v>
       </c>
       <c r="C273" t="n">
-        <v>0.483077333189976</v>
+        <v>0.586384605167612</v>
       </c>
       <c r="D273" t="s">
         <v>569</v>
@@ -8019,7 +8019,7 @@
         <v>0.986931783933106</v>
       </c>
       <c r="C274" t="n">
-        <v>0.593923383201874</v>
+        <v>0.720935354716141</v>
       </c>
       <c r="D274" t="s">
         <v>189</v>
@@ -8039,7 +8039,7 @@
         <v>1.00411241460119</v>
       </c>
       <c r="C275" t="n">
-        <v>0.721526060968055</v>
+        <v>0.875826177943458</v>
       </c>
       <c r="D275" t="s">
         <v>573</v>
@@ -8059,7 +8059,7 @@
         <v>1.09345169407521</v>
       </c>
       <c r="C276" t="n">
-        <v>0.679465219924238</v>
+        <v>0.824770522929322</v>
       </c>
       <c r="D276" t="s">
         <v>237</v>
@@ -8079,7 +8079,7 @@
         <v>0.922408970979645</v>
       </c>
       <c r="C277" t="n">
-        <v>0.69145912629269</v>
+        <v>0.839329355577999</v>
       </c>
       <c r="D277" t="s">
         <v>569</v>
@@ -8099,7 +8099,7 @@
         <v>1.05183638867919</v>
       </c>
       <c r="C278" t="n">
-        <v>1.12019640954929</v>
+        <v>1.35975315791813</v>
       </c>
       <c r="D278" t="s">
         <v>43</v>
@@ -8119,7 +8119,7 @@
         <v>1.03656471697423</v>
       </c>
       <c r="C279" t="n">
-        <v>0.991107192524647</v>
+        <v>1.20305789536764</v>
       </c>
       <c r="D279" t="s">
         <v>163</v>
@@ -8139,7 +8139,7 @@
         <v>1.03465575801111</v>
       </c>
       <c r="C280" t="n">
-        <v>0.831771767955143</v>
+        <v>1.00964819963957</v>
       </c>
       <c r="D280" t="s">
         <v>580</v>
@@ -8159,7 +8159,7 @@
         <v>0.674498833635778</v>
       </c>
       <c r="C281" t="n">
-        <v>1.04654327151968</v>
+        <v>1.27034911575856</v>
       </c>
       <c r="D281" t="s">
         <v>364</v>
@@ -8179,7 +8179,7 @@
         <v>0.674498833635778</v>
       </c>
       <c r="C282" t="n">
-        <v>1.04654327151968</v>
+        <v>1.27034911575856</v>
       </c>
       <c r="D282" t="s">
         <v>583</v>
@@ -8199,7 +8199,7 @@
         <v>0.947798125189143</v>
       </c>
       <c r="C283" t="n">
-        <v>0.687581330470791</v>
+        <v>0.834622283613083</v>
       </c>
       <c r="D283" t="s">
         <v>181</v>
@@ -8219,7 +8219,7 @@
         <v>0.947798125189143</v>
       </c>
       <c r="C284" t="n">
-        <v>0.687581330470791</v>
+        <v>0.834622283613083</v>
       </c>
       <c r="D284" t="s">
         <v>20</v>
@@ -8239,7 +8239,7 @@
         <v>0.939207809855103</v>
       </c>
       <c r="C285" t="n">
-        <v>0.734804997547035</v>
+        <v>0.891944847663465</v>
       </c>
       <c r="D285" t="s">
         <v>181</v>
@@ -8259,7 +8259,7 @@
         <v>0.939207809855103</v>
       </c>
       <c r="C286" t="n">
-        <v>0.734804997547035</v>
+        <v>0.891944847663465</v>
       </c>
       <c r="D286" t="s">
         <v>20</v>
@@ -8279,7 +8279,7 @@
         <v>1.08428869105223</v>
       </c>
       <c r="C287" t="n">
-        <v>0.767906814137633</v>
+        <v>0.932125568881811</v>
       </c>
       <c r="D287" t="s">
         <v>500</v>
@@ -8299,7 +8299,7 @@
         <v>0.413289615515508</v>
       </c>
       <c r="C288" t="n">
-        <v>0.644919080324552</v>
+        <v>0.782836606685604</v>
       </c>
       <c r="D288" t="s">
         <v>181</v>
@@ -8319,7 +8319,7 @@
         <v>0.413289615515508</v>
       </c>
       <c r="C289" t="n">
-        <v>0.644919080324552</v>
+        <v>0.782836606685604</v>
       </c>
       <c r="D289" t="s">
         <v>20</v>
@@ -8339,7 +8339,7 @@
         <v>0.139990323962143</v>
       </c>
       <c r="C290" t="n">
-        <v>0.618873687734322</v>
+        <v>0.751221343039087</v>
       </c>
       <c r="D290" t="s">
         <v>20</v>
@@ -8359,7 +8359,7 @@
         <v>0.959251878967864</v>
       </c>
       <c r="C291" t="n">
-        <v>0.753692916138411</v>
+        <v>0.914871993949764</v>
       </c>
       <c r="D291" t="s">
         <v>393</v>
@@ -8379,7 +8379,7 @@
         <v>1.13010370616712</v>
       </c>
       <c r="C292" t="n">
-        <v>0.745918321938052</v>
+        <v>0.905434783720066</v>
       </c>
       <c r="D292" t="s">
         <v>592</v>
@@ -8399,7 +8399,7 @@
         <v>1.15587465216924</v>
       </c>
       <c r="C293" t="n">
-        <v>0.872527856832504</v>
+        <v>1.05912007803782</v>
       </c>
       <c r="D293" t="s">
         <v>595</v>
@@ -8419,7 +8419,7 @@
         <v>0.8914838357771</v>
       </c>
       <c r="C294" t="n">
-        <v>0.991983377743166</v>
+        <v>1.20412145494313</v>
       </c>
       <c r="D294" t="s">
         <v>43</v>
@@ -8439,7 +8439,7 @@
         <v>1.07856181416287</v>
       </c>
       <c r="C295" t="n">
-        <v>0.630811440181013</v>
+        <v>0.765712013112172</v>
       </c>
       <c r="D295" t="s">
         <v>599</v>
@@ -8459,7 +8459,7 @@
         <v>1.07856181416287</v>
       </c>
       <c r="C296" t="n">
-        <v>0.630811440181013</v>
+        <v>0.765712013112172</v>
       </c>
       <c r="D296" t="s">
         <v>569</v>
@@ -8479,7 +8479,7 @@
         <v>0.862849451330298</v>
       </c>
       <c r="C297" t="n">
-        <v>0.93550747888244</v>
+        <v>1.1355680466591</v>
       </c>
       <c r="D297" t="s">
         <v>279</v>
@@ -8499,7 +8499,7 @@
         <v>1.03656471697423</v>
       </c>
       <c r="C298" t="n">
-        <v>0.72607820441754</v>
+        <v>0.881351808429298</v>
       </c>
       <c r="D298" t="s">
         <v>603</v>
@@ -8519,7 +8519,7 @@
         <v>0.870485287182778</v>
       </c>
       <c r="C299" t="n">
-        <v>0.634698554003312</v>
+        <v>0.770430395754716</v>
       </c>
       <c r="D299" t="s">
         <v>343</v>
@@ -8539,7 +8539,7 @@
         <v>1.09478796534939</v>
       </c>
       <c r="C300" t="n">
-        <v>0.758177119220383</v>
+        <v>0.920315154853941</v>
       </c>
       <c r="D300" t="s">
         <v>75</v>
@@ -8559,7 +8559,7 @@
         <v>0.761674626284931</v>
       </c>
       <c r="C301" t="n">
-        <v>1.23355069800751</v>
+        <v>1.49734853885372</v>
       </c>
       <c r="D301" t="s">
         <v>608</v>
@@ -8579,7 +8579,7 @@
         <v>0.75212983146933</v>
       </c>
       <c r="C302" t="n">
-        <v>0.531595046267442</v>
+        <v>0.645277950128959</v>
       </c>
       <c r="D302" t="s">
         <v>189</v>
@@ -8599,7 +8599,7 @@
         <v>0.691043144649486</v>
       </c>
       <c r="C303" t="n">
-        <v>0.673727801940819</v>
+        <v>0.817806144044739</v>
       </c>
       <c r="D303" t="s">
         <v>612</v>
@@ -8619,7 +8619,7 @@
         <v>0.933480932965742</v>
       </c>
       <c r="C304" t="n">
-        <v>0.812370789000049</v>
+        <v>0.98609827377299</v>
       </c>
       <c r="D304" t="s">
         <v>343</v>
@@ -8639,7 +8639,7 @@
         <v>0.824670272067895</v>
       </c>
       <c r="C305" t="n">
-        <v>0.908091173330377</v>
+        <v>1.10228869695304</v>
       </c>
       <c r="D305" t="s">
         <v>75</v>
@@ -8659,7 +8659,7 @@
         <v>0.824670272067895</v>
       </c>
       <c r="C306" t="n">
-        <v>0.908091173330377</v>
+        <v>1.10228869695304</v>
       </c>
       <c r="D306" t="s">
         <v>211</v>
@@ -8679,7 +8679,7 @@
         <v>1.04229159386359</v>
       </c>
       <c r="C307" t="n">
-        <v>0.648339210969694</v>
+        <v>0.786988140653737</v>
       </c>
       <c r="D307" t="s">
         <v>617</v>
@@ -8699,7 +8699,7 @@
         <v>0.763583585248051</v>
       </c>
       <c r="C308" t="n">
-        <v>0.778066198967647</v>
+        <v>0.944457563063684</v>
       </c>
       <c r="D308" t="s">
         <v>620</v>
@@ -8719,7 +8719,7 @@
         <v>0.763583585248051</v>
       </c>
       <c r="C309" t="n">
-        <v>0.778066198967647</v>
+        <v>0.944457563063684</v>
       </c>
       <c r="D309" t="s">
         <v>622</v>
@@ -8739,7 +8739,7 @@
         <v>0.570729782307197</v>
       </c>
       <c r="C310" t="n">
-        <v>0.697689839699978</v>
+        <v>0.84689252232217</v>
       </c>
       <c r="D310" t="s">
         <v>101</v>
@@ -8759,7 +8759,7 @@
         <v>1.04515503230827</v>
       </c>
       <c r="C311" t="n">
-        <v>0.693593220272634</v>
+        <v>0.841919830787333</v>
       </c>
       <c r="D311" t="s">
         <v>327</v>
@@ -8779,7 +8779,7 @@
         <v>0.914391343334541</v>
       </c>
       <c r="C312" t="n">
-        <v>0.74186858794887</v>
+        <v>0.900519004189283</v>
       </c>
       <c r="D312" t="s">
         <v>627</v>
@@ -8799,7 +8799,7 @@
         <v>0.811307559326054</v>
       </c>
       <c r="C313" t="n">
-        <v>0.675846275986519</v>
+        <v>0.820377658958599</v>
       </c>
       <c r="D313" t="s">
         <v>569</v>
@@ -8819,7 +8819,7 @@
         <v>1.25609499773304</v>
       </c>
       <c r="C314" t="n">
-        <v>0.687667954306187</v>
+        <v>0.834727432168039</v>
       </c>
       <c r="D314" t="s">
         <v>631</v>
@@ -8839,7 +8839,7 @@
         <v>1.02511096319551</v>
       </c>
       <c r="C315" t="n">
-        <v>0.816725802608127</v>
+        <v>0.99138461771757</v>
       </c>
       <c r="D315" t="s">
         <v>634</v>
@@ -8859,7 +8859,7 @@
         <v>1.02701992215863</v>
       </c>
       <c r="C316" t="n">
-        <v>0.749071843391402</v>
+        <v>0.909262693467144</v>
       </c>
       <c r="D316" t="s">
         <v>156</v>
@@ -8879,7 +8879,7 @@
         <v>0.788400051768612</v>
       </c>
       <c r="C317" t="n">
-        <v>0.794721224515951</v>
+        <v>0.964674306655663</v>
       </c>
       <c r="D317" t="s">
         <v>185</v>
@@ -8899,7 +8899,7 @@
         <v>1.05183638867919</v>
       </c>
       <c r="C318" t="n">
-        <v>0.725811903186457</v>
+        <v>0.881028558027104</v>
       </c>
       <c r="D318" t="s">
         <v>450</v>
@@ -8919,7 +8919,7 @@
         <v>0.60132207338284</v>
       </c>
       <c r="C319" t="n">
-        <v>0.526251573887728</v>
+        <v>0.638791763081201</v>
       </c>
       <c r="D319" t="s">
         <v>43</v>
@@ -8939,7 +8939,7 @@
         <v>0.771219421100531</v>
       </c>
       <c r="C320" t="n">
-        <v>1.08539973012874</v>
+        <v>1.31751512329865</v>
       </c>
       <c r="D320" t="s">
         <v>599</v>
@@ -8959,7 +8959,7 @@
         <v>0.771219421100531</v>
       </c>
       <c r="C321" t="n">
-        <v>1.08539973012874</v>
+        <v>1.31751512329865</v>
       </c>
       <c r="D321" t="s">
         <v>641</v>
@@ -8979,7 +8979,7 @@
         <v>0.440969520480749</v>
       </c>
       <c r="C322" t="n">
-        <v>0.62825601311979</v>
+        <v>0.76261010170922</v>
       </c>
       <c r="D322" t="s">
         <v>644</v>
@@ -8999,7 +8999,7 @@
         <v>1.01747512734303</v>
       </c>
       <c r="C323" t="n">
-        <v>1.00067778890636</v>
+        <v>1.21467518724812</v>
       </c>
       <c r="D323" t="s">
         <v>433</v>
@@ -9019,7 +9019,7 @@
         <v>1.07665285519975</v>
       </c>
       <c r="C324" t="n">
-        <v>0.883475432088611</v>
+        <v>1.07240881910068</v>
       </c>
       <c r="D324" t="s">
         <v>648</v>
@@ -9039,7 +9039,7 @@
         <v>0.90484654851894</v>
       </c>
       <c r="C325" t="n">
-        <v>1.43781524586491</v>
+        <v>1.74529556102956</v>
       </c>
       <c r="D325" t="s">
         <v>491</v>
@@ -9059,7 +9059,7 @@
         <v>1.00793033252743</v>
       </c>
       <c r="C326" t="n">
-        <v>0.952508967035993</v>
+        <v>1.15620534473382</v>
       </c>
       <c r="D326" t="s">
         <v>652</v>
@@ -9079,7 +9079,7 @@
         <v>0.162261511865211</v>
       </c>
       <c r="C327" t="n">
-        <v>0.560660882028015</v>
+        <v>0.680559586122482</v>
       </c>
       <c r="D327" t="s">
         <v>652</v>
@@ -9099,7 +9099,7 @@
         <v>0.528781632784275</v>
       </c>
       <c r="C328" t="n">
-        <v>0.953991749747812</v>
+        <v>1.15800522416364</v>
       </c>
       <c r="D328" t="s">
         <v>652</v>
@@ -9119,7 +9119,7 @@
         <v>0.618502704050921</v>
       </c>
       <c r="C329" t="n">
-        <v>0.925512992702761</v>
+        <v>1.12343621510819</v>
       </c>
       <c r="D329" t="s">
         <v>652</v>
@@ -9139,7 +9139,7 @@
         <v>0.763583585248051</v>
       </c>
       <c r="C330" t="n">
-        <v>0.704243178338893</v>
+        <v>0.854847308494674</v>
       </c>
       <c r="D330" t="s">
         <v>253</v>
@@ -9159,7 +9159,7 @@
         <v>1.12437682927775</v>
       </c>
       <c r="C331" t="n">
-        <v>0.892738834618782</v>
+        <v>1.08365322297136</v>
       </c>
       <c r="D331" t="s">
         <v>659</v>
@@ -9179,7 +9179,7 @@
         <v>0.614684786124681</v>
       </c>
       <c r="C332" t="n">
-        <v>0.487976092494056</v>
+        <v>0.592330976158288</v>
       </c>
       <c r="D332" t="s">
         <v>415</v>
@@ -9199,7 +9199,7 @@
         <v>0.736858159764369</v>
       </c>
       <c r="C333" t="n">
-        <v>0.582080421111257</v>
+        <v>0.706559746149158</v>
       </c>
       <c r="D333" t="s">
         <v>663</v>
@@ -9219,7 +9219,7 @@
         <v>1.01556616837991</v>
       </c>
       <c r="C334" t="n">
-        <v>0.599524230093244</v>
+        <v>0.727733956445833</v>
       </c>
       <c r="D334" t="s">
         <v>43</v>
@@ -9239,7 +9239,7 @@
         <v>0.830397148957255</v>
       </c>
       <c r="C335" t="n">
-        <v>1.17212201106126</v>
+        <v>1.42278317661022</v>
       </c>
       <c r="D335" t="s">
         <v>276</v>
@@ -9259,7 +9259,7 @@
         <v>1.06901701934727</v>
       </c>
       <c r="C336" t="n">
-        <v>1.00823280197116</v>
+        <v>1.22384585837811</v>
       </c>
       <c r="D336" t="s">
         <v>668</v>
@@ -9279,7 +9279,7 @@
         <v>1.06901701934727</v>
       </c>
       <c r="C337" t="n">
-        <v>1.00823280197116</v>
+        <v>1.22384585837811</v>
       </c>
       <c r="D337" t="s">
         <v>355</v>
@@ -9299,7 +9299,7 @@
         <v>1.18260007765292</v>
       </c>
       <c r="C338" t="n">
-        <v>0.864476851587946</v>
+        <v>1.04934734558449</v>
       </c>
       <c r="D338" t="s">
         <v>671</v>
@@ -9319,7 +9319,7 @@
         <v>0.806535161918254</v>
       </c>
       <c r="C339" t="n">
-        <v>0.808754794010101</v>
+        <v>0.981708989389749</v>
       </c>
       <c r="D339" t="s">
         <v>674</v>
@@ -9339,7 +9339,7 @@
         <v>1.02701992215863</v>
       </c>
       <c r="C340" t="n">
-        <v>0.613378592852399</v>
+        <v>0.744551108645316</v>
       </c>
       <c r="D340" t="s">
         <v>677</v>
@@ -9359,7 +9359,7 @@
         <v>1.02701992215863</v>
       </c>
       <c r="C341" t="n">
-        <v>0.613378592852399</v>
+        <v>0.744551108645316</v>
       </c>
       <c r="D341" t="s">
         <v>679</v>
@@ -9379,7 +9379,7 @@
         <v>1.02797440164019</v>
       </c>
       <c r="C342" t="n">
-        <v>0.787414123926961</v>
+        <v>0.955804564692196</v>
       </c>
       <c r="D342" t="s">
         <v>547</v>
@@ -9399,7 +9399,7 @@
         <v>0.264240109105576</v>
       </c>
       <c r="C343" t="n">
-        <v>0.353373204401041</v>
+        <v>0.428942930464571</v>
       </c>
       <c r="D343" t="s">
         <v>683</v>
@@ -9419,7 +9419,7 @@
         <v>1.28568386166141</v>
       </c>
       <c r="C344" t="n">
-        <v>1.23723867956945</v>
+        <v>1.50182520431386</v>
       </c>
       <c r="D344" t="s">
         <v>377</v>
@@ -9439,7 +9439,7 @@
         <v>1.08047077312599</v>
       </c>
       <c r="C345" t="n">
-        <v>1.74349304123258</v>
+        <v>2.11634330231262</v>
       </c>
       <c r="D345" t="s">
         <v>565</v>
@@ -9459,7 +9459,7 @@
         <v>1.05374534764231</v>
       </c>
       <c r="C346" t="n">
-        <v>0.921412493444545</v>
+        <v>1.11845881403114</v>
       </c>
       <c r="D346" t="s">
         <v>688</v>
@@ -9479,7 +9479,7 @@
         <v>0.914773135127165</v>
       </c>
       <c r="C347" t="n">
-        <v>0.816811013762477</v>
+        <v>0.991488051486174</v>
       </c>
       <c r="D347" t="s">
         <v>691</v>
@@ -9499,7 +9499,7 @@
         <v>0.87353962152377</v>
       </c>
       <c r="C348" t="n">
-        <v>0.723893939306947</v>
+        <v>0.878700432870029</v>
       </c>
       <c r="D348" t="s">
         <v>694</v>
@@ -9519,7 +9519,7 @@
         <v>0.957533815901056</v>
       </c>
       <c r="C349" t="n">
-        <v>0.581888130721356</v>
+        <v>0.706326333987973</v>
       </c>
       <c r="D349" t="s">
         <v>697</v>
@@ -9539,7 +9539,7 @@
         <v>1.04543576156755</v>
       </c>
       <c r="C350" t="n">
-        <v>0.451030712712832</v>
+        <v>0.547484736338419</v>
       </c>
       <c r="D350" t="s">
         <v>700</v>
@@ -9559,7 +9559,7 @@
         <v>1.28892909189871</v>
       </c>
       <c r="C351" t="n">
-        <v>0.705781540735103</v>
+        <v>0.856714653460643</v>
       </c>
       <c r="D351" t="s">
         <v>703</v>
@@ -9579,7 +9579,7 @@
         <v>1.16522855108853</v>
       </c>
       <c r="C352" t="n">
-        <v>0.709134196173487</v>
+        <v>0.860784282483637</v>
       </c>
       <c r="D352" t="s">
         <v>706</v>
@@ -9599,7 +9599,7 @@
         <v>0.293813683888924</v>
       </c>
       <c r="C353" t="n">
-        <v>0.31456963710387</v>
+        <v>0.381841125173081</v>
       </c>
       <c r="D353" t="s">
         <v>709</v>
@@ -9619,7 +9619,7 @@
         <v>0.958297399486304</v>
       </c>
       <c r="C354" t="n">
-        <v>0.780833972450944</v>
+        <v>0.947817231691644</v>
       </c>
       <c r="D354" t="s">
         <v>712</v>
@@ -9639,7 +9639,7 @@
         <v>0.994567619785586</v>
       </c>
       <c r="C355" t="n">
-        <v>0.600910115095261</v>
+        <v>0.72941621635306</v>
       </c>
       <c r="D355" t="s">
         <v>715</v>
@@ -9659,7 +9659,7 @@
         <v>0.345203412497556</v>
       </c>
       <c r="C356" t="n">
-        <v>0.590405625001366</v>
+        <v>0.716665315300591</v>
       </c>
       <c r="D356" t="s">
         <v>178</v>
@@ -9679,7 +9679,7 @@
         <v>0.713555695180075</v>
       </c>
       <c r="C357" t="n">
-        <v>0.864313062569099</v>
+        <v>1.04914852988243</v>
       </c>
       <c r="D357" t="s">
         <v>652</v>
@@ -9699,7 +9699,7 @@
         <v>0.118779668816363</v>
       </c>
       <c r="C358" t="n">
-        <v>0.397919366464278</v>
+        <v>0.483015398490951</v>
       </c>
       <c r="D358" t="s">
         <v>151</v>
@@ -9719,7 +9719,7 @@
         <v>0.118779668816363</v>
       </c>
       <c r="C359" t="n">
-        <v>0.397919366464278</v>
+        <v>0.483015398490951</v>
       </c>
       <c r="D359" t="s">
         <v>153</v>
@@ -9739,7 +9739,7 @@
         <v>0.450196155469163</v>
       </c>
       <c r="C360" t="n">
-        <v>0.427059076961884</v>
+        <v>0.518386707515126</v>
       </c>
       <c r="D360" t="s">
         <v>706</v>
@@ -9759,7 +9759,7 @@
         <v>0.931571974002622</v>
       </c>
       <c r="C361" t="n">
-        <v>0.680231117746813</v>
+        <v>0.82570020987887</v>
       </c>
       <c r="D361" t="s">
         <v>722</v>
@@ -9779,7 +9779,7 @@
         <v>1.02129304526927</v>
       </c>
       <c r="C362" t="n">
-        <v>0.698661864837192</v>
+        <v>0.848072417417919</v>
       </c>
       <c r="D362" t="s">
         <v>725</v>
@@ -9799,7 +9799,7 @@
         <v>0.845668820662216</v>
       </c>
       <c r="C363" t="n">
-        <v>0.753536146808781</v>
+        <v>0.914681699114669</v>
       </c>
       <c r="D363" t="s">
         <v>528</v>
@@ -9819,7 +9819,7 @@
         <v>0.675771472944525</v>
       </c>
       <c r="C364" t="n">
-        <v>0.71524364116792</v>
+        <v>0.86820024726757</v>
       </c>
       <c r="D364" t="s">
         <v>729</v>
@@ -9839,7 +9839,7 @@
         <v>0.236710911426896</v>
       </c>
       <c r="C365" t="n">
-        <v>0.290187802494818</v>
+        <v>0.352245175460267</v>
       </c>
       <c r="D365" t="s">
         <v>151</v>
@@ -9859,7 +9859,7 @@
         <v>0.236710911426896</v>
       </c>
       <c r="C366" t="n">
-        <v>0.290187802494818</v>
+        <v>0.352245175460267</v>
       </c>
       <c r="D366" t="s">
         <v>153</v>
@@ -9879,7 +9879,7 @@
         <v>0.20264333608506</v>
       </c>
       <c r="C367" t="n">
-        <v>0.448586962664169</v>
+        <v>0.544518384350941</v>
       </c>
       <c r="D367" t="s">
         <v>151</v>
@@ -9899,7 +9899,7 @@
         <v>0.20264333608506</v>
       </c>
       <c r="C368" t="n">
-        <v>0.448586962664169</v>
+        <v>0.544518384350941</v>
       </c>
       <c r="D368" t="s">
         <v>153</v>
@@ -9919,7 +9919,7 @@
         <v>0.18698008305433</v>
       </c>
       <c r="C369" t="n">
-        <v>0.416863783143874</v>
+        <v>0.506011125120142</v>
       </c>
       <c r="D369" t="s">
         <v>151</v>
@@ -9939,7 +9939,7 @@
         <v>0.18698008305433</v>
       </c>
       <c r="C370" t="n">
-        <v>0.416863783143874</v>
+        <v>0.506011125120142</v>
       </c>
       <c r="D370" t="s">
         <v>153</v>
@@ -9959,7 +9959,7 @@
         <v>1.19882622883944</v>
       </c>
       <c r="C371" t="n">
-        <v>0.975433880164265</v>
+        <v>1.18403280673551</v>
       </c>
       <c r="D371" t="s">
         <v>735</v>
